--- a/Acceptance_test_corrosion_and_parameterisation_size.xlsx
+++ b/Acceptance_test_corrosion_and_parameterisation_size.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jens1\Documents\GitHub\Robotteknologi-5.-semester\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jens\Documents\GitHub\Robotteknologi-5.-semester\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6279824D-607F-40FB-BD66-B68044EE359D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B47825DC-B5FC-4F8D-96BC-1FAD47E956E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{634B6407-AD3C-4DC4-BF9C-C1397938D912}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{634B6407-AD3C-4DC4-BF9C-C1397938D912}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="28">
   <si>
     <t>Test NR</t>
   </si>
@@ -106,6 +106,21 @@
   <si>
     <t>CorCheck</t>
   </si>
+  <si>
+    <t>Paracheck</t>
+  </si>
+  <si>
+    <t>X_dif</t>
+  </si>
+  <si>
+    <t>Y_dif</t>
+  </si>
+  <si>
+    <t>U_Dif</t>
+  </si>
+  <si>
+    <t>V_Dif</t>
+  </si>
 </sst>
 </file>
 
@@ -148,9 +163,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -485,10 +501,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5706F927-AB27-401A-990D-9D8E7271204D}">
-  <dimension ref="A1:V26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:AB56"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:22" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" ht="16" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -546,8 +562,21 @@
       <c r="V1" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AB1" s="1"/>
+    </row>
+    <row r="2" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>1</v>
       </c>
@@ -604,20 +633,46 @@
         <f>L2-K2</f>
         <v>121.75800000000001</v>
       </c>
-      <c r="V2" t="str">
+      <c r="W2" t="b">
         <f>IF(N2="Sblob",
-     IF(AND(O$23 - O$23*0.05 &gt; 0, Q$23 - Q$23*0.05 &gt; 0),"Y","X"),
-     IF(N2="Lblob",
-         IF(AND(O$24 - O$24*0.05 &gt; 0, Q$24 - Q$24*0.05 &gt; 0),"Y","X"),
-         IF(N2="Rec",
-             IF(AND(O$25 - O$25*0.05 &gt; 0, Q$25 - Q$25*0.05 &gt; 0),"Y","X"),
-         )
-     )
-)</f>
-        <v>Y</v>
-      </c>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+    AND(O2 &gt;= O$23*(1-0.05), O2 &lt;= O$23*(1+0.05)),
+IF(N2="Lblob",
+    AND(O2 &gt;= O$24*(1-0.05), O2 &lt;= O$24*(1+0.05)),
+IF(N2="Rec",
+    AND(O2 &gt;= O$25*(1-0.05), O2 &lt;= O$25*(1+0.05)),
+""
+)))</f>
+        <v>1</v>
+      </c>
+      <c r="X2" t="b">
+        <f>IF(N2="Sblob",
+    AND(Q2 &gt;= Q$23*(1-0.05), Q2 &lt;= Q$23*(1+0.05)),
+IF(N2="Lblob",
+    AND(Q2 &gt;= Q$24*(1-0.05), Q2 &lt;= Q$24*(1+0.05)),
+IF(N2="Rec",
+    AND(Q2 &gt;= Q$25*(1-0.05), Q2 &lt;= Q$25*(1+0.05)),
+""
+)))</f>
+        <v>1</v>
+      </c>
+      <c r="Z2" s="2">
+        <f>IF(N2="Sblob", 1-O2/O$23,
+   IF(N2="Lblob", 1-O2/O$24,
+   IF(N2="Rec", 1-O2/O$25,
+""
+)))</f>
+        <v>-7.6470588235295622E-3</v>
+      </c>
+      <c r="AA2" s="2">
+        <f>IF(N2="Sblob", 1-Q2/Q$23,
+   IF(N2="Lblob", 1-Q2/Q$24,
+   IF(N2="Rec", 1-Q2/Q$25,
+""
+)))</f>
+        <v>3.2800000000000051E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>2</v>
       </c>
@@ -674,20 +729,46 @@
         <f t="shared" ref="T3:T21" si="4">L3-K3</f>
         <v>121.68899999999999</v>
       </c>
-      <c r="V3" t="str">
-        <f t="shared" ref="V3:V21" si="5">IF(N3="Sblob",
-     IF(AND(O$23 - O$23*0.05 &gt; 0, Q$23 - Q$23*0.05 &gt; 0),"Y","X"),
-     IF(N3="Lblob",
-         IF(AND(O$24 - O$24*0.05 &gt; 0, Q$24 - Q$24*0.05 &gt; 0),"Y","X"),
-         IF(N3="Rec",
-             IF(AND(O$25 - O$25*0.05 &gt; 0, Q$25 - Q$25*0.05 &gt; 0),"Y","X"),
-         )
-     )
-)</f>
-        <v>Y</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="W3" t="b">
+        <f t="shared" ref="W3:W21" si="5">IF(N3="Sblob",
+    AND(O3 &gt;= O$23*(1-0.05), O3 &lt;= O$23*(1+0.05)),
+IF(N3="Lblob",
+    AND(O3 &gt;= O$24*(1-0.05), O3 &lt;= O$24*(1+0.05)),
+IF(N3="Rec",
+    AND(O3 &gt;= O$25*(1-0.05), O3 &lt;= O$25*(1+0.05)),
+""
+)))</f>
+        <v>1</v>
+      </c>
+      <c r="X3" t="b">
+        <f t="shared" ref="X3:X21" si="6">IF(N3="Sblob",
+    AND(Q3 &gt;= Q$23*(1-0.05), Q3 &lt;= Q$23*(1+0.05)),
+IF(N3="Lblob",
+    AND(Q3 &gt;= Q$24*(1-0.05), Q3 &lt;= Q$24*(1+0.05)),
+IF(N3="Rec",
+    AND(Q3 &gt;= Q$25*(1-0.05), Q3 &lt;= Q$25*(1+0.05)),
+""
+)))</f>
+        <v>1</v>
+      </c>
+      <c r="Z3" s="2">
+        <f t="shared" ref="Z3:Z21" si="7">IF(N3="Sblob", 1-O3/O$23,
+   IF(N3="Lblob", 1-O3/O$24,
+   IF(N3="Rec", 1-O3/O$25,
+""
+)))</f>
+        <v>-4.7058823529413374E-3</v>
+      </c>
+      <c r="AA3" s="2">
+        <f t="shared" ref="AA3:AA21" si="8">IF(N3="Sblob", 1-Q3/Q$23,
+   IF(N3="Lblob", 1-Q3/Q$24,
+   IF(N3="Rec", 1-Q3/Q$25,
+""
+)))</f>
+        <v>2.8800000000000048E-2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>3</v>
       </c>
@@ -744,12 +825,24 @@
         <f t="shared" si="4"/>
         <v>72.296999999999997</v>
       </c>
-      <c r="V4" t="str">
+      <c r="W4" t="b">
         <f t="shared" si="5"/>
-        <v>Y</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="X4" t="b">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="Z4" s="2">
+        <f t="shared" si="7"/>
+        <v>-8.6086956521739033E-2</v>
+      </c>
+      <c r="AA4" s="2">
+        <f t="shared" si="8"/>
+        <v>5.7692307692307709E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>4</v>
       </c>
@@ -806,12 +899,24 @@
         <f t="shared" si="4"/>
         <v>72.840999999999994</v>
       </c>
-      <c r="V5" t="str">
+      <c r="W5" t="b">
         <f t="shared" si="5"/>
-        <v>Y</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="X5" t="b">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="Z5" s="2">
+        <f t="shared" si="7"/>
+        <v>-6.4347826086956328E-2</v>
+      </c>
+      <c r="AA5" s="2">
+        <f t="shared" si="8"/>
+        <v>2.051282051282044E-2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>5</v>
       </c>
@@ -868,12 +973,24 @@
         <f t="shared" si="4"/>
         <v>81.916999999999987</v>
       </c>
-      <c r="V6" t="str">
+      <c r="W6" t="b">
         <f t="shared" si="5"/>
-        <v>Y</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="X6" t="b">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="Z6" s="2">
+        <f t="shared" si="7"/>
+        <v>-8.3478260869565446E-2</v>
+      </c>
+      <c r="AA6" s="2">
+        <f t="shared" si="8"/>
+        <v>-9.6153846153846256E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>6</v>
       </c>
@@ -930,12 +1047,24 @@
         <f t="shared" si="4"/>
         <v>77.694999999999993</v>
       </c>
-      <c r="V7" t="str">
+      <c r="W7" t="b">
         <f t="shared" si="5"/>
-        <v>Y</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="X7" t="b">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="Z7" s="2">
+        <f t="shared" si="7"/>
+        <v>-0.12695652173913063</v>
+      </c>
+      <c r="AA7" s="2">
+        <f t="shared" si="8"/>
+        <v>-5.12820512820511E-3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>7</v>
       </c>
@@ -992,12 +1121,24 @@
         <f t="shared" si="4"/>
         <v>90.581999999999994</v>
       </c>
-      <c r="V8" t="str">
+      <c r="W8" t="b">
         <f t="shared" si="5"/>
-        <v>Y</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="X8" t="b">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="Z8" s="2">
+        <f t="shared" si="7"/>
+        <v>-0.28869565217391302</v>
+      </c>
+      <c r="AA8" s="2">
+        <f t="shared" si="8"/>
+        <v>-0.25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1054,12 +1195,24 @@
         <f t="shared" si="4"/>
         <v>93.245999999999981</v>
       </c>
-      <c r="V9" t="str">
+      <c r="W9" t="b">
         <f t="shared" si="5"/>
-        <v>Y</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="X9" t="b">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="Z9" s="2">
+        <f t="shared" si="7"/>
+        <v>-0.22608695652173938</v>
+      </c>
+      <c r="AA9" s="2">
+        <f t="shared" si="8"/>
+        <v>-0.21153846153846145</v>
+      </c>
+    </row>
+    <row r="10" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1116,12 +1269,24 @@
         <f t="shared" si="4"/>
         <v>80.262999999999991</v>
       </c>
-      <c r="V10" t="str">
+      <c r="W10" t="b">
         <f t="shared" si="5"/>
-        <v>Y</v>
-      </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="X10" t="b">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="Z10" s="2">
+        <f t="shared" si="7"/>
+        <v>-1.6216216216216051E-2</v>
+      </c>
+      <c r="AA10" s="2">
+        <f t="shared" si="8"/>
+        <v>-9.3167701863354768E-3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>10</v>
       </c>
@@ -1178,12 +1343,24 @@
         <f t="shared" si="4"/>
         <v>83.952999999999989</v>
       </c>
-      <c r="V11">
+      <c r="W11" t="str">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+        <v/>
+      </c>
+      <c r="X11" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="Z11" s="2" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="AA11" s="2" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="12" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>11</v>
       </c>
@@ -1240,12 +1417,24 @@
         <f t="shared" si="4"/>
         <v>81.073000000000008</v>
       </c>
-      <c r="V12">
+      <c r="W12" t="str">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+        <v/>
+      </c>
+      <c r="X12" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="Z12" s="2" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="AA12" s="2" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>12</v>
       </c>
@@ -1302,12 +1491,24 @@
         <f t="shared" si="4"/>
         <v>83.3</v>
       </c>
-      <c r="V13">
+      <c r="W13" t="str">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+        <v/>
+      </c>
+      <c r="X13" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="Z13" s="2" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="AA13" s="2" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1364,12 +1565,24 @@
         <f t="shared" si="4"/>
         <v>79.75800000000001</v>
       </c>
-      <c r="V14" t="str">
+      <c r="W14" t="b">
         <f t="shared" si="5"/>
-        <v>Y</v>
-      </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="X14" t="b">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="Z14" s="2">
+        <f t="shared" si="7"/>
+        <v>-1.3513513513513598E-2</v>
+      </c>
+      <c r="AA14" s="2">
+        <f t="shared" si="8"/>
+        <v>-8.0745341614907318E-3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1426,12 +1639,24 @@
         <f t="shared" si="4"/>
         <v>79.664000000000016</v>
       </c>
-      <c r="V15" t="str">
+      <c r="W15" t="b">
         <f t="shared" si="5"/>
-        <v>Y</v>
-      </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="X15" t="b">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="Z15" s="2">
+        <f t="shared" si="7"/>
+        <v>-1.3513513513513598E-2</v>
+      </c>
+      <c r="AA15" s="2">
+        <f t="shared" si="8"/>
+        <v>-1.055900621118E-2</v>
+      </c>
+    </row>
+    <row r="16" spans="1:28" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1488,12 +1713,24 @@
         <f t="shared" si="4"/>
         <v>121.87899999999999</v>
       </c>
-      <c r="V16" t="str">
+      <c r="W16" t="b">
         <f t="shared" si="5"/>
-        <v>Y</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="X16" t="b">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="Z16" s="2">
+        <f t="shared" si="7"/>
+        <v>-6.4705882352940058E-3</v>
+      </c>
+      <c r="AA16" s="2">
+        <f t="shared" si="8"/>
+        <v>2.2400000000000087E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1550,12 +1787,24 @@
         <f t="shared" si="4"/>
         <v>88.076999999999998</v>
       </c>
-      <c r="V17">
+      <c r="W17" t="str">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
+        <v/>
+      </c>
+      <c r="X17" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="Z17" s="2" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="AA17" s="2" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1612,12 +1861,24 @@
         <f t="shared" si="4"/>
         <v>87.885999999999996</v>
       </c>
-      <c r="V18">
+      <c r="W18" t="str">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
+        <v/>
+      </c>
+      <c r="X18" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="Z18" s="2" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="AA18" s="2" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1674,12 +1935,24 @@
         <f t="shared" si="4"/>
         <v>87.887999999999991</v>
       </c>
-      <c r="V19">
+      <c r="W19" t="str">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
+        <v/>
+      </c>
+      <c r="X19" t="str">
+        <f t="shared" si="6"/>
+        <v/>
+      </c>
+      <c r="Z19" s="2" t="str">
+        <f t="shared" si="7"/>
+        <v/>
+      </c>
+      <c r="AA19" s="2" t="str">
+        <f t="shared" si="8"/>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1736,12 +2009,24 @@
         <f t="shared" si="4"/>
         <v>121.95100000000001</v>
       </c>
-      <c r="V20" t="str">
+      <c r="W20" t="b">
         <f t="shared" si="5"/>
-        <v>Y</v>
-      </c>
-    </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="X20" t="b">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="Z20" s="2">
+        <f t="shared" si="7"/>
+        <v>-3.529411764705781E-3</v>
+      </c>
+      <c r="AA20" s="2">
+        <f t="shared" si="8"/>
+        <v>2.959999999999996E-2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:27" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1798,12 +2083,24 @@
         <f t="shared" si="4"/>
         <v>121.76400000000001</v>
       </c>
-      <c r="V21" t="str">
+      <c r="W21" t="b">
         <f t="shared" si="5"/>
-        <v>Y</v>
-      </c>
-    </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
+        <v>1</v>
+      </c>
+      <c r="X21" t="b">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="Z21" s="2">
+        <f t="shared" si="7"/>
+        <v>-5.8823529411764497E-3</v>
+      </c>
+      <c r="AA21" s="2">
+        <f t="shared" si="8"/>
+        <v>2.7999999999999914E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:27" x14ac:dyDescent="0.35">
       <c r="N23" t="s">
         <v>18</v>
       </c>
@@ -1814,7 +2111,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:27" ht="16" x14ac:dyDescent="0.4">
       <c r="N24" t="s">
         <v>17</v>
       </c>
@@ -1824,8 +2121,23 @@
       <c r="Q24">
         <v>78</v>
       </c>
-    </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="V24" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="W24" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="X24" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Z24" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA24" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="25" spans="1:27" x14ac:dyDescent="0.35">
       <c r="N25" t="s">
         <v>19</v>
       </c>
@@ -1835,8 +2147,49 @@
       <c r="Q25">
         <v>161</v>
       </c>
-    </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="V25">
+        <v>1</v>
+      </c>
+      <c r="W25" t="b">
+        <f>IF(N2="Sblob",
+    AND(S2 &gt;= O$23*(1-0.05), S2 &lt;= O$23*(1+0.05)),
+IF(N2="Lblob",
+    AND(S2 &gt;= O$24*(1-0.05), S2 &lt;= O$24*(1+0.05)),
+IF(N2="Rec",
+    AND(S2 &gt;= O$25*(1-0.05), S2 &lt;= O$25*(1+0.05)),
+""
+)))</f>
+        <v>1</v>
+      </c>
+      <c r="X25" t="b">
+        <f>IF(N2="Sblob",
+    AND(T2 &gt;= Q$23*(1-0.05), T2 &lt;= Q$23*(1+0.05)),
+IF(N2="Lblob",
+    AND(T2 &gt;= Q$24*(1-0.05), T2 &lt;= Q$24*(1+0.05)),
+IF(N2="Rec",
+    AND(T2 &gt;= Q$25*(1-0.05), T2 &lt;= Q$25*(1+0.05)),
+""
+)))</f>
+        <v>1</v>
+      </c>
+      <c r="Z25">
+        <f>IF(N2="Sblob", 1-S2/O$23,
+   IF(N2="Lblob", 1-S2/O$24,
+   IF(N2="Rec", 1-S2/O$25,
+""
+)))</f>
+        <v>1.6470588235294459E-3</v>
+      </c>
+      <c r="AA25">
+        <f>IF(N2="Sblob", 1-T2/Q$23,
+   IF(N2="Lblob", 1-T2/Q$24,
+   IF(N2="Rec", 1-T2/Q$25,
+""
+)))</f>
+        <v>2.5935999999999959E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:27" x14ac:dyDescent="0.35">
       <c r="N26" t="s">
         <v>21</v>
       </c>
@@ -1845,6 +2198,575 @@
       </c>
       <c r="Q26" t="s">
         <v>20</v>
+      </c>
+      <c r="V26">
+        <v>2</v>
+      </c>
+      <c r="W26" t="b">
+        <f t="shared" ref="W26:W31" si="9">IF(N3="Sblob",
+    AND(S3 &gt;= O$23*(1-0.05), S3 &lt;= O$23*(1+0.05)),
+IF(N3="Lblob",
+    AND(S3 &gt;= O$24*(1-0.05), S3 &lt;= O$24*(1+0.05)),
+IF(N3="Rec",
+    AND(S3 &gt;= O$25*(1-0.05), S3 &lt;= O$25*(1+0.05)),
+""
+)))</f>
+        <v>1</v>
+      </c>
+      <c r="X26" t="b">
+        <f t="shared" ref="X26:X31" si="10">IF(N3="Sblob",
+    AND(T3 &gt;= Q$23*(1-0.05), T3 &lt;= Q$23*(1+0.05)),
+IF(N3="Lblob",
+    AND(T3 &gt;= Q$24*(1-0.05), T3 &lt;= Q$24*(1+0.05)),
+IF(N3="Rec",
+    AND(T3 &gt;= Q$25*(1-0.05), T3 &lt;= Q$25*(1+0.05)),
+""
+)))</f>
+        <v>1</v>
+      </c>
+      <c r="Z26">
+        <f t="shared" ref="Z26:Z44" si="11">IF(N3="Sblob", 1-S3/O$23,
+   IF(N3="Lblob", 1-S3/O$24,
+   IF(N3="Rec", 1-S3/O$25,
+""
+)))</f>
+        <v>-3.4176470588234142E-3</v>
+      </c>
+      <c r="AA26">
+        <f t="shared" ref="AA26:AA44" si="12">IF(N3="Sblob", 1-T3/Q$23,
+   IF(N3="Lblob", 1-T3/Q$24,
+   IF(N3="Rec", 1-T3/Q$25,
+""
+)))</f>
+        <v>2.6488000000000067E-2</v>
+      </c>
+    </row>
+    <row r="27" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="V27">
+        <v>3</v>
+      </c>
+      <c r="W27" t="b">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X27" t="b">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="Z27">
+        <f t="shared" si="11"/>
+        <v>-9.648695652173922E-2</v>
+      </c>
+      <c r="AA27">
+        <f t="shared" si="12"/>
+        <v>7.3115384615384693E-2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="V28">
+        <v>4</v>
+      </c>
+      <c r="W28" t="b">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X28" t="b">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="Z28">
+        <f t="shared" si="11"/>
+        <v>-8.0147826086956364E-2</v>
+      </c>
+      <c r="AA28">
+        <f t="shared" si="12"/>
+        <v>6.6141025641025752E-2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="V29">
+        <v>5</v>
+      </c>
+      <c r="W29" t="b">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X29" t="b">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="Z29">
+        <f t="shared" si="11"/>
+        <v>-9.2208695652173933E-2</v>
+      </c>
+      <c r="AA29">
+        <f t="shared" si="12"/>
+        <v>-5.0217948717948602E-2</v>
+      </c>
+    </row>
+    <row r="30" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="V30">
+        <v>6</v>
+      </c>
+      <c r="W30" t="b">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X30" t="b">
+        <f t="shared" si="10"/>
+        <v>1</v>
+      </c>
+      <c r="Z30">
+        <f t="shared" si="11"/>
+        <v>-0.13169565217391299</v>
+      </c>
+      <c r="AA30">
+        <f t="shared" si="12"/>
+        <v>3.9102564102565518E-3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="V31">
+        <v>7</v>
+      </c>
+      <c r="W31" t="b">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="X31" t="b">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+      <c r="Z31">
+        <f t="shared" si="11"/>
+        <v>-0.35697391304347814</v>
+      </c>
+      <c r="AA31">
+        <f t="shared" si="12"/>
+        <v>-0.16130769230769215</v>
+      </c>
+    </row>
+    <row r="32" spans="1:27" x14ac:dyDescent="0.35">
+      <c r="V32">
+        <v>8</v>
+      </c>
+      <c r="W32" t="b">
+        <f t="shared" ref="W32:W42" si="13">IF(N9="Sblob",
+    AND(S9 &gt;= O$23*(1-0.05), S9 &lt;= O$23*(1+0.05)),
+IF(N9="Lblob",
+    AND(S9 &gt;= O$24*(1-0.05), S9 &lt;= O$24*(1+0.05)),
+IF(N9="Rec",
+    AND(S9 &gt;= O$25*(1-0.05), S9 &lt;= O$25*(1+0.05)),
+""
+)))</f>
+        <v>0</v>
+      </c>
+      <c r="X32" t="b">
+        <f t="shared" ref="X32:X42" si="14">IF(N9="Sblob",
+    AND(T9 &gt;= Q$23*(1-0.05), T9 &lt;= Q$23*(1+0.05)),
+IF(N9="Lblob",
+    AND(T9 &gt;= Q$24*(1-0.05), T9 &lt;= Q$24*(1+0.05)),
+IF(N9="Rec",
+    AND(T9 &gt;= Q$25*(1-0.05), T9 &lt;= Q$25*(1+0.05)),
+""
+)))</f>
+        <v>0</v>
+      </c>
+      <c r="Z32">
+        <f t="shared" si="11"/>
+        <v>-0.22838260869565219</v>
+      </c>
+      <c r="AA32">
+        <f t="shared" si="12"/>
+        <v>-0.19546153846153813</v>
+      </c>
+    </row>
+    <row r="33" spans="22:27" x14ac:dyDescent="0.35">
+      <c r="V33">
+        <v>9</v>
+      </c>
+      <c r="W33" t="b">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="X33" t="b">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="Z33">
+        <f t="shared" si="11"/>
+        <v>-1.2418513513513512</v>
+      </c>
+      <c r="AA33">
+        <f t="shared" si="12"/>
+        <v>0.50147204968944104</v>
+      </c>
+    </row>
+    <row r="34" spans="22:27" x14ac:dyDescent="0.35">
+      <c r="V34">
+        <v>10</v>
+      </c>
+      <c r="W34" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="X34" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="Z34" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="AA34" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="35" spans="22:27" x14ac:dyDescent="0.35">
+      <c r="V35">
+        <v>11</v>
+      </c>
+      <c r="W35" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="X35" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="Z35" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="AA35" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="36" spans="22:27" x14ac:dyDescent="0.35">
+      <c r="V36">
+        <v>12</v>
+      </c>
+      <c r="W36" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="X36" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="Z36" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="AA36" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="37" spans="22:27" x14ac:dyDescent="0.35">
+      <c r="V37">
+        <v>13</v>
+      </c>
+      <c r="W37" t="b">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="X37" t="b">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="Z37">
+        <f t="shared" si="11"/>
+        <v>-1.235702702702703</v>
+      </c>
+      <c r="AA37">
+        <f t="shared" si="12"/>
+        <v>0.50460869565217381</v>
+      </c>
+    </row>
+    <row r="38" spans="22:27" x14ac:dyDescent="0.35">
+      <c r="V38">
+        <v>14</v>
+      </c>
+      <c r="W38" t="b">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="X38" t="b">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="Z38">
+        <f t="shared" si="11"/>
+        <v>-1.2435540540540542</v>
+      </c>
+      <c r="AA38">
+        <f t="shared" si="12"/>
+        <v>0.50519254658385082</v>
+      </c>
+    </row>
+    <row r="39" spans="22:27" x14ac:dyDescent="0.35">
+      <c r="V39">
+        <v>15</v>
+      </c>
+      <c r="W39" t="b">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="X39" t="b">
+        <f t="shared" si="14"/>
+        <v>1</v>
+      </c>
+      <c r="Z39">
+        <f t="shared" si="11"/>
+        <v>-5.3058823529410493E-3</v>
+      </c>
+      <c r="AA39">
+        <f t="shared" si="12"/>
+        <v>2.4968000000000101E-2</v>
+      </c>
+    </row>
+    <row r="40" spans="22:27" x14ac:dyDescent="0.35">
+      <c r="V40">
+        <v>16</v>
+      </c>
+      <c r="W40" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="X40" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="Z40" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="AA40" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="41" spans="22:27" x14ac:dyDescent="0.35">
+      <c r="V41">
+        <v>17</v>
+      </c>
+      <c r="W41" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="X41" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="Z41" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="AA41" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="42" spans="22:27" x14ac:dyDescent="0.35">
+      <c r="V42">
+        <v>18</v>
+      </c>
+      <c r="W42" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="X42" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="Z42" t="str">
+        <f t="shared" si="11"/>
+        <v/>
+      </c>
+      <c r="AA42" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+    </row>
+    <row r="43" spans="22:27" x14ac:dyDescent="0.35">
+      <c r="V43">
+        <v>19</v>
+      </c>
+      <c r="W43" t="b">
+        <f>IF(N20="Sblob",
+    AND(S20 &gt;= O$23*(1-0.05), S20 &lt;= O$23*(1+0.05)),
+IF(N20="Lblob",
+    AND(S20 &gt;= O$24*(1-0.05), S20 &lt;= O$24*(1+0.05)),
+IF(N20="Rec",
+    AND(S20 &gt;= O$25*(1-0.05), S20 &lt;= O$25*(1+0.05)),
+""
+)))</f>
+        <v>1</v>
+      </c>
+      <c r="X43" t="b">
+        <f>IF(N20="Sblob",
+    AND(T20 &gt;= Q$23*(1-0.05), T20 &lt;= Q$23*(1+0.05)),
+IF(N20="Lblob",
+    AND(T20 &gt;= Q$24*(1-0.05), T20 &lt;= Q$24*(1+0.05)),
+IF(N20="Rec",
+    AND(T20 &gt;= Q$25*(1-0.05), T20 &lt;= Q$25*(1+0.05)),
+""
+)))</f>
+        <v>1</v>
+      </c>
+      <c r="Z43">
+        <f t="shared" si="11"/>
+        <v>-6.2411764705883055E-3</v>
+      </c>
+      <c r="AA43">
+        <f t="shared" si="12"/>
+        <v>2.4391999999999969E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="22:27" x14ac:dyDescent="0.35">
+      <c r="V44">
+        <v>20</v>
+      </c>
+      <c r="W44" t="b">
+        <f t="shared" ref="W44:W45" si="15">IF(N21="Sblob",
+    AND(S21 &gt;= O$23*(1-0.05), S21 &lt;= O$23*(1+0.05)),
+IF(N21="Lblob",
+    AND(S21 &gt;= O$24*(1-0.05), S21 &lt;= O$24*(1+0.05)),
+IF(N21="Rec",
+    AND(S21 &gt;= O$25*(1-0.05), S21 &lt;= O$25*(1+0.05)),
+""
+)))</f>
+        <v>1</v>
+      </c>
+      <c r="X44" t="b">
+        <f t="shared" ref="X44:X45" si="16">IF(N21="Sblob",
+    AND(T21 &gt;= Q$23*(1-0.05), T21 &lt;= Q$23*(1+0.05)),
+IF(N21="Lblob",
+    AND(T21 &gt;= Q$24*(1-0.05), T21 &lt;= Q$24*(1+0.05)),
+IF(N21="Rec",
+    AND(T21 &gt;= Q$25*(1-0.05), T21 &lt;= Q$25*(1+0.05)),
+""
+)))</f>
+        <v>1</v>
+      </c>
+      <c r="Z44">
+        <f t="shared" si="11"/>
+        <v>-3.9882352941176258E-3</v>
+      </c>
+      <c r="AA44">
+        <f t="shared" si="12"/>
+        <v>2.5887999999999911E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="23:24" x14ac:dyDescent="0.35">
+      <c r="W49" t="str">
+        <f>IF(N26="Sblob",
+    AND(S26 &gt;= O$23*(1-0.05), S26 &lt;= O$23*(1+0.05)),
+IF(N26="Lblob",
+    AND(S26 &gt;= O$24*(1-0.05), S26 &lt;= O$24*(1+0.05)),
+IF(N26="Rec",
+    AND(S26 &gt;= O$25*(1-0.05), S26 &lt;= O$25*(1+0.05)),
+""
+)))</f>
+        <v/>
+      </c>
+      <c r="X49" t="str">
+        <f>IF(N26="Sblob",
+    AND(T26 &gt;= Q$23*(1-0.05), T26 &lt;= Q$23*(1+0.05)),
+IF(N26="Lblob",
+    AND(T26 &gt;= Q$24*(1-0.05), T26 &lt;= Q$24*(1+0.05)),
+IF(N26="Rec",
+    AND(T26 &gt;= Q$25*(1-0.05), T26 &lt;= Q$25*(1+0.05)),
+""
+)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50" spans="23:24" x14ac:dyDescent="0.35">
+      <c r="W50" t="str">
+        <f t="shared" ref="W50:W56" si="17">IF(N27="Sblob",
+    AND(S27 &gt;= O$23*(1-0.05), S27 &lt;= O$23*(1+0.05)),
+IF(N27="Lblob",
+    AND(S27 &gt;= O$24*(1-0.05), S27 &lt;= O$24*(1+0.05)),
+IF(N27="Rec",
+    AND(S27 &gt;= O$25*(1-0.05), S27 &lt;= O$25*(1+0.05)),
+""
+)))</f>
+        <v/>
+      </c>
+      <c r="X50" t="str">
+        <f t="shared" ref="X50:X56" si="18">IF(N27="Sblob",
+    AND(T27 &gt;= Q$23*(1-0.05), T27 &lt;= Q$23*(1+0.05)),
+IF(N27="Lblob",
+    AND(T27 &gt;= Q$24*(1-0.05), T27 &lt;= Q$24*(1+0.05)),
+IF(N27="Rec",
+    AND(T27 &gt;= Q$25*(1-0.05), T27 &lt;= Q$25*(1+0.05)),
+""
+)))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51" spans="23:24" x14ac:dyDescent="0.35">
+      <c r="W51" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="X51" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+    </row>
+    <row r="52" spans="23:24" x14ac:dyDescent="0.35">
+      <c r="W52" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="X52" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+    </row>
+    <row r="53" spans="23:24" x14ac:dyDescent="0.35">
+      <c r="W53" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="X53" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+    </row>
+    <row r="54" spans="23:24" x14ac:dyDescent="0.35">
+      <c r="W54" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="X54" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+    </row>
+    <row r="55" spans="23:24" x14ac:dyDescent="0.35">
+      <c r="W55" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="X55" t="str">
+        <f t="shared" si="18"/>
+        <v/>
+      </c>
+    </row>
+    <row r="56" spans="23:24" x14ac:dyDescent="0.35">
+      <c r="W56" t="str">
+        <f t="shared" si="17"/>
+        <v/>
+      </c>
+      <c r="X56" t="str">
+        <f t="shared" si="18"/>
+        <v/>
       </c>
     </row>
   </sheetData>

--- a/Acceptance_test_corrosion_and_parameterisation_size.xlsx
+++ b/Acceptance_test_corrosion_and_parameterisation_size.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Jens\Documents\GitHub\Robotteknologi-5.-semester\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jens1\Documents\GitHub\Robotteknologi-5.-semester\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B47825DC-B5FC-4F8D-96BC-1FAD47E956E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C139C01-69EB-42E2-B197-7979C1FEB4E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{634B6407-AD3C-4DC4-BF9C-C1397938D912}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{634B6407-AD3C-4DC4-BF9C-C1397938D912}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,8 +35,30 @@
 </workbook>
 </file>
 
+<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+  <metadataTypes count="1">
+    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
+  </metadataTypes>
+  <futureMetadata name="XLDAPR" count="1">
+    <bk>
+      <extLst>
+        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
+          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
+        </ext>
+      </extLst>
+    </bk>
+  </futureMetadata>
+  <cellMetadata count="1">
+    <bk>
+      <rc t="1" v="0"/>
+    </bk>
+  </cellMetadata>
+</metadata>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="40">
   <si>
     <t>Test NR</t>
   </si>
@@ -121,6 +143,42 @@
   <si>
     <t>V_Dif</t>
   </si>
+  <si>
+    <t>Lblob1</t>
+  </si>
+  <si>
+    <t>Lblob2</t>
+  </si>
+  <si>
+    <t>Lblob3</t>
+  </si>
+  <si>
+    <t>x adjust</t>
+  </si>
+  <si>
+    <t>z adjust</t>
+  </si>
+  <si>
+    <t>y adjust</t>
+  </si>
+  <si>
+    <t>Max offset</t>
+  </si>
+  <si>
+    <t>X offset</t>
+  </si>
+  <si>
+    <t>Y offset</t>
+  </si>
+  <si>
+    <t>Z offset</t>
+  </si>
+  <si>
+    <t>TRUE</t>
+  </si>
+  <si>
+    <t>False</t>
+  </si>
 </sst>
 </file>
 
@@ -143,12 +201,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -163,10 +227,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="10" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -501,10 +567,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5706F927-AB27-401A-990D-9D8E7271204D}">
-  <dimension ref="A1:AB56"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:AB69"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:28" ht="16" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:28" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -576,7 +642,7 @@
       </c>
       <c r="AB1" s="1"/>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
@@ -633,46 +699,49 @@
         <f>L2-K2</f>
         <v>121.75800000000001</v>
       </c>
+      <c r="V2" t="s">
+        <v>18</v>
+      </c>
       <c r="W2" t="b">
         <f>IF(N2="Sblob",
-    AND(O2 &gt;= O$23*(1-0.05), O2 &lt;= O$23*(1+0.05)),
+    AND(O2 &gt;= O$28*(1-0.05), O2 &lt;= O$28*(1+0.05)),
 IF(N2="Lblob",
-    AND(O2 &gt;= O$24*(1-0.05), O2 &lt;= O$24*(1+0.05)),
+    AND(O2 &gt;= O$29*(1-0.05), O2 &lt;= O$29*(1+0.05)),
 IF(N2="Rec",
-    AND(O2 &gt;= O$25*(1-0.05), O2 &lt;= O$25*(1+0.05)),
+    AND(O2 &gt;= O$30*(1-0.05), O2 &lt;= O$30*(1+0.05)),
 ""
 )))</f>
         <v>1</v>
       </c>
       <c r="X2" t="b">
         <f>IF(N2="Sblob",
-    AND(Q2 &gt;= Q$23*(1-0.05), Q2 &lt;= Q$23*(1+0.05)),
+    AND(Q2 &gt;= Q$28*(1-0.05), Q2 &lt;= Q$28*(1+0.05)),
 IF(N2="Lblob",
-    AND(Q2 &gt;= Q$24*(1-0.05), Q2 &lt;= Q$24*(1+0.05)),
+    AND(Q2 &gt;= Q$29*(1-0.05), Q2 &lt;= Q$29*(1+0.05)),
 IF(N2="Rec",
-    AND(Q2 &gt;= Q$25*(1-0.05), Q2 &lt;= Q$25*(1+0.05)),
+    AND(Q2 &gt;= Q$30*(1-0.05), Q2 &lt;= Q$30*(1+0.05)),
 ""
 )))</f>
         <v>1</v>
       </c>
       <c r="Z2" s="2">
-        <f>IF(N2="Sblob", 1-O2/O$23,
-   IF(N2="Lblob", 1-O2/O$24,
-   IF(N2="Rec", 1-O2/O$25,
+        <f>IF(N2="Sblob", 1-O2/O$28,
+   IF(N2="Lblob", 1-O2/O$29,
+   IF(N2="Rec", 1-O2/O$30,
 ""
 )))</f>
         <v>-7.6470588235295622E-3</v>
       </c>
       <c r="AA2" s="2">
-        <f>IF(N2="Sblob", 1-Q2/Q$23,
-   IF(N2="Lblob", 1-Q2/Q$24,
-   IF(N2="Rec", 1-Q2/Q$25,
+        <f>IF(N2="Sblob", 1-Q2/Q$28,
+   IF(N2="Lblob", 1-Q2/Q$29,
+   IF(N2="Rec", 1-Q2/Q$30,
 ""
 )))</f>
         <v>3.2800000000000051E-2</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
@@ -710,509 +779,560 @@
         <v>18</v>
       </c>
       <c r="O3">
-        <f t="shared" ref="O3:O21" si="0">C3-B3</f>
+        <f t="shared" ref="O3:O22" si="0">C3-B3</f>
         <v>170.8</v>
       </c>
       <c r="P3">
-        <f t="shared" ref="P3:P21" si="1">E3-D3</f>
+        <f t="shared" ref="P3:P22" si="1">E3-D3</f>
         <v>7.6000000000000085</v>
       </c>
       <c r="Q3">
-        <f t="shared" ref="Q3:Q21" si="2">G3-F3</f>
+        <f t="shared" ref="Q3:Q22" si="2">G3-F3</f>
         <v>121.39999999999999</v>
       </c>
       <c r="S3">
-        <f t="shared" ref="S3:S21" si="3">J3-I3</f>
+        <f t="shared" ref="S3:S24" si="3">J3-I3</f>
         <v>170.58099999999999</v>
       </c>
       <c r="T3">
-        <f t="shared" ref="T3:T21" si="4">L3-K3</f>
+        <f t="shared" ref="T3:T24" si="4">L3-K3</f>
         <v>121.68899999999999</v>
       </c>
+      <c r="V3" t="s">
+        <v>18</v>
+      </c>
       <c r="W3" t="b">
-        <f t="shared" ref="W3:W21" si="5">IF(N3="Sblob",
-    AND(O3 &gt;= O$23*(1-0.05), O3 &lt;= O$23*(1+0.05)),
+        <f t="shared" ref="W3:W24" si="5">IF(N3="Sblob",
+    AND(O3 &gt;= O$28*(1-0.05), O3 &lt;= O$28*(1+0.05)),
 IF(N3="Lblob",
-    AND(O3 &gt;= O$24*(1-0.05), O3 &lt;= O$24*(1+0.05)),
+    AND(O3 &gt;= O$29*(1-0.05), O3 &lt;= O$29*(1+0.05)),
 IF(N3="Rec",
-    AND(O3 &gt;= O$25*(1-0.05), O3 &lt;= O$25*(1+0.05)),
+    AND(O3 &gt;= O$30*(1-0.05), O3 &lt;= O$30*(1+0.05)),
 ""
 )))</f>
         <v>1</v>
       </c>
       <c r="X3" t="b">
-        <f t="shared" ref="X3:X21" si="6">IF(N3="Sblob",
-    AND(Q3 &gt;= Q$23*(1-0.05), Q3 &lt;= Q$23*(1+0.05)),
+        <f t="shared" ref="X3:X24" si="6">IF(N3="Sblob",
+    AND(Q3 &gt;= Q$28*(1-0.05), Q3 &lt;= Q$28*(1+0.05)),
 IF(N3="Lblob",
-    AND(Q3 &gt;= Q$24*(1-0.05), Q3 &lt;= Q$24*(1+0.05)),
+    AND(Q3 &gt;= Q$29*(1-0.05), Q3 &lt;= Q$29*(1+0.05)),
 IF(N3="Rec",
-    AND(Q3 &gt;= Q$25*(1-0.05), Q3 &lt;= Q$25*(1+0.05)),
+    AND(Q3 &gt;= Q$30*(1-0.05), Q3 &lt;= Q$30*(1+0.05)),
 ""
 )))</f>
         <v>1</v>
       </c>
       <c r="Z3" s="2">
-        <f t="shared" ref="Z3:Z21" si="7">IF(N3="Sblob", 1-O3/O$23,
-   IF(N3="Lblob", 1-O3/O$24,
-   IF(N3="Rec", 1-O3/O$25,
+        <f t="shared" ref="Z3:Z24" si="7">IF(N3="Sblob", 1-O3/O$28,
+   IF(N3="Lblob", 1-O3/O$29,
+   IF(N3="Rec", 1-O3/O$30,
 ""
 )))</f>
         <v>-4.7058823529413374E-3</v>
       </c>
       <c r="AA3" s="2">
-        <f t="shared" ref="AA3:AA21" si="8">IF(N3="Sblob", 1-Q3/Q$23,
-   IF(N3="Lblob", 1-Q3/Q$24,
-   IF(N3="Rec", 1-Q3/Q$25,
+        <f t="shared" ref="AA3:AA24" si="8">IF(N3="Sblob", 1-Q3/Q$28,
+   IF(N3="Lblob", 1-Q3/Q$29,
+   IF(N3="Rec", 1-Q3/Q$30,
 ""
 )))</f>
         <v>2.8800000000000048E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="A4">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A4" s="3">
         <v>3</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="3">
         <v>249.5</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="3">
         <v>374.4</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="3">
         <v>-99.4</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="3">
         <v>-90.4</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="3">
         <v>-62.8</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="3">
         <v>10.7</v>
       </c>
-      <c r="I4">
+      <c r="H4" s="3"/>
+      <c r="I4" s="3">
         <v>62.49</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="3">
         <v>188.58600000000001</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="3">
         <v>59.487000000000002</v>
       </c>
-      <c r="L4">
+      <c r="L4" s="3">
         <v>131.78399999999999</v>
       </c>
-      <c r="N4" t="s">
+      <c r="M4" s="3"/>
+      <c r="N4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="O4">
+      <c r="O4" s="3">
         <f t="shared" si="0"/>
         <v>124.89999999999998</v>
       </c>
-      <c r="P4">
+      <c r="P4" s="3">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="Q4">
+      <c r="Q4" s="3">
         <f t="shared" si="2"/>
         <v>73.5</v>
       </c>
-      <c r="S4">
+      <c r="R4" s="3"/>
+      <c r="S4" s="3">
         <f t="shared" si="3"/>
         <v>126.096</v>
       </c>
-      <c r="T4">
+      <c r="T4" s="3">
         <f t="shared" si="4"/>
         <v>72.296999999999997</v>
       </c>
-      <c r="W4" t="b">
+      <c r="U4" s="3"/>
+      <c r="V4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="W4" s="3" t="b">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="X4" t="b">
+      <c r="X4" s="3" t="b">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Z4" s="2">
+      <c r="Y4" s="3"/>
+      <c r="Z4" s="4">
         <f t="shared" si="7"/>
         <v>-8.6086956521739033E-2</v>
       </c>
-      <c r="AA4" s="2">
+      <c r="AA4" s="4">
         <f t="shared" si="8"/>
         <v>5.7692307692307709E-2</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="A5">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A5" s="3">
         <v>4</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="3">
         <v>257</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="3">
         <v>379.4</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="3">
         <v>-99.4</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="3">
         <v>-90.6</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="3">
         <v>-66.2</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="3">
         <v>10.199999999999999</v>
       </c>
-      <c r="I5">
+      <c r="H5" s="3"/>
+      <c r="I5" s="3">
         <v>63.008000000000003</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="3">
         <v>187.22499999999999</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="3">
         <v>58.801000000000002</v>
       </c>
-      <c r="L5">
+      <c r="L5" s="3">
         <v>131.642</v>
       </c>
-      <c r="N5" t="s">
+      <c r="M5" s="3"/>
+      <c r="N5" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="O5">
+      <c r="O5" s="3">
         <f t="shared" si="0"/>
         <v>122.39999999999998</v>
       </c>
-      <c r="P5">
+      <c r="P5" s="3">
         <f t="shared" si="1"/>
         <v>8.8000000000000114</v>
       </c>
-      <c r="Q5">
+      <c r="Q5" s="3">
         <f t="shared" si="2"/>
         <v>76.400000000000006</v>
       </c>
-      <c r="S5">
+      <c r="R5" s="3"/>
+      <c r="S5" s="3">
         <f t="shared" si="3"/>
         <v>124.21699999999998</v>
       </c>
-      <c r="T5">
+      <c r="T5" s="3">
         <f t="shared" si="4"/>
         <v>72.840999999999994</v>
       </c>
-      <c r="W5" t="b">
+      <c r="U5" s="3"/>
+      <c r="V5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="W5" s="3" t="b">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="X5" t="b">
+      <c r="X5" s="3" t="b">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="Z5" s="2">
+      <c r="Y5" s="3"/>
+      <c r="Z5" s="4">
         <f t="shared" si="7"/>
         <v>-6.4347826086956328E-2</v>
       </c>
-      <c r="AA5" s="2">
+      <c r="AA5" s="4">
         <f t="shared" si="8"/>
         <v>2.051282051282044E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="A6">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A6" s="3">
         <v>5</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="3">
         <v>257.5</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="3">
         <v>382.1</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="3">
         <v>-99</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="3">
         <v>-90.4</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="3">
         <v>-75.7</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="3">
         <v>9.8000000000000007</v>
       </c>
-      <c r="I6">
+      <c r="H6" s="3"/>
+      <c r="I6" s="3">
         <v>62.932000000000002</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="3">
         <v>188.536</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="3">
         <v>59.402000000000001</v>
       </c>
-      <c r="L6">
+      <c r="L6" s="3">
         <v>141.31899999999999</v>
       </c>
-      <c r="N6" t="s">
+      <c r="M6" s="3"/>
+      <c r="N6" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="O6">
+      <c r="O6" s="3">
         <f t="shared" si="0"/>
         <v>124.60000000000002</v>
       </c>
-      <c r="P6">
+      <c r="P6" s="3">
         <f t="shared" si="1"/>
         <v>8.5999999999999943</v>
       </c>
-      <c r="Q6">
+      <c r="Q6" s="3">
         <f t="shared" si="2"/>
         <v>85.5</v>
       </c>
-      <c r="S6">
+      <c r="R6" s="3"/>
+      <c r="S6" s="3">
         <f t="shared" si="3"/>
         <v>125.604</v>
       </c>
-      <c r="T6">
+      <c r="T6" s="3">
         <f t="shared" si="4"/>
         <v>81.916999999999987</v>
       </c>
-      <c r="W6" t="b">
+      <c r="U6" s="3"/>
+      <c r="V6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="W6" s="3" t="b">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="X6" t="b">
+      <c r="X6" s="3" t="b">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Z6" s="2">
+      <c r="Y6" s="3"/>
+      <c r="Z6" s="4">
         <f t="shared" si="7"/>
         <v>-8.3478260869565446E-2</v>
       </c>
-      <c r="AA6" s="2">
+      <c r="AA6" s="4">
         <f t="shared" si="8"/>
         <v>-9.6153846153846256E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="A7">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A7" s="3">
         <v>6</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="3">
         <v>257.5</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="3">
         <v>387.1</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="3">
         <v>-99.1</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="3">
         <v>-91.3</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="3">
         <v>-68.3</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="3">
         <v>10.1</v>
       </c>
-      <c r="I7">
+      <c r="H7" s="3"/>
+      <c r="I7" s="3">
         <v>62.758000000000003</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="3">
         <v>192.90299999999999</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="3">
         <v>59.091000000000001</v>
       </c>
-      <c r="L7">
+      <c r="L7" s="3">
         <v>136.786</v>
       </c>
-      <c r="N7" t="s">
+      <c r="M7" s="3"/>
+      <c r="N7" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="O7">
+      <c r="O7" s="3">
         <f t="shared" si="0"/>
         <v>129.60000000000002</v>
       </c>
-      <c r="P7">
+      <c r="P7" s="3">
         <f t="shared" si="1"/>
         <v>7.7999999999999972</v>
       </c>
-      <c r="Q7">
+      <c r="Q7" s="3">
         <f t="shared" si="2"/>
         <v>78.399999999999991</v>
       </c>
-      <c r="S7">
+      <c r="R7" s="3"/>
+      <c r="S7" s="3">
         <f t="shared" si="3"/>
         <v>130.14499999999998</v>
       </c>
-      <c r="T7">
+      <c r="T7" s="3">
         <f t="shared" si="4"/>
         <v>77.694999999999993</v>
       </c>
-      <c r="W7" t="b">
+      <c r="U7" s="3"/>
+      <c r="V7" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="W7" s="3" t="b">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="X7" t="b">
+      <c r="X7" s="3" t="b">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="Y7" s="3"/>
+      <c r="Z7" s="4">
         <f t="shared" si="7"/>
         <v>-0.12695652173913063</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AA7" s="4">
         <f t="shared" si="8"/>
         <v>-5.12820512820511E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="A8">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A8" s="3">
         <v>7</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="3">
         <v>231.8</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="3">
         <v>380</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="3">
         <v>-100.5</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="3">
         <v>-90.1</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="3">
         <v>-87</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="3">
         <v>10.5</v>
       </c>
-      <c r="I8">
+      <c r="H8" s="3"/>
+      <c r="I8" s="3">
         <v>61.5</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="3">
         <v>217.55199999999999</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="3">
         <v>59.65</v>
       </c>
-      <c r="L8">
+      <c r="L8" s="3">
         <v>150.232</v>
       </c>
-      <c r="N8" t="s">
+      <c r="M8" s="3"/>
+      <c r="N8" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="O8">
+      <c r="O8" s="3">
         <f t="shared" si="0"/>
         <v>148.19999999999999</v>
       </c>
-      <c r="P8">
+      <c r="P8" s="3">
         <f t="shared" si="1"/>
         <v>10.400000000000006</v>
       </c>
-      <c r="Q8">
+      <c r="Q8" s="3">
         <f t="shared" si="2"/>
         <v>97.5</v>
       </c>
-      <c r="S8">
+      <c r="R8" s="3"/>
+      <c r="S8" s="3">
         <f t="shared" si="3"/>
         <v>156.05199999999999</v>
       </c>
-      <c r="T8">
+      <c r="T8" s="3">
         <f t="shared" si="4"/>
         <v>90.581999999999994</v>
       </c>
-      <c r="W8" t="b">
+      <c r="U8" s="3"/>
+      <c r="V8" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="W8" s="3" t="b">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="X8" t="b">
+      <c r="X8" s="3" t="b">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Z8" s="2">
+      <c r="Y8" s="3"/>
+      <c r="Z8" s="4">
         <f t="shared" si="7"/>
         <v>-0.28869565217391302</v>
       </c>
-      <c r="AA8" s="2">
+      <c r="AA8" s="4">
         <f t="shared" si="8"/>
         <v>-0.25</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="A9">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A9" s="3">
         <v>8</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="3">
         <v>246.1</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="3">
         <v>387.1</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="3">
         <v>-99.2</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="3">
         <v>-91.9</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="3">
         <v>-75.2</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="3">
         <v>19.3</v>
       </c>
-      <c r="I9">
+      <c r="H9" s="3"/>
+      <c r="I9" s="3">
         <v>63.619</v>
       </c>
-      <c r="J9">
+      <c r="J9" s="3">
         <v>204.88300000000001</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="3">
         <v>58.65</v>
       </c>
-      <c r="L9">
+      <c r="L9" s="3">
         <v>151.89599999999999</v>
       </c>
-      <c r="N9" t="s">
+      <c r="M9" s="3"/>
+      <c r="N9" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="O9">
+      <c r="O9" s="3">
         <f t="shared" si="0"/>
         <v>141.00000000000003</v>
       </c>
-      <c r="P9">
+      <c r="P9" s="3">
         <f t="shared" si="1"/>
         <v>7.2999999999999972</v>
       </c>
-      <c r="Q9">
+      <c r="Q9" s="3">
         <f t="shared" si="2"/>
         <v>94.5</v>
       </c>
-      <c r="S9">
+      <c r="R9" s="3"/>
+      <c r="S9" s="3">
         <f t="shared" si="3"/>
         <v>141.26400000000001</v>
       </c>
-      <c r="T9">
+      <c r="T9" s="3">
         <f t="shared" si="4"/>
         <v>93.245999999999981</v>
       </c>
-      <c r="W9" t="b">
+      <c r="U9" s="3"/>
+      <c r="V9" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="W9" s="3" t="b">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="X9" t="b">
+      <c r="X9" s="3" t="b">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="Z9" s="2">
+      <c r="Y9" s="3"/>
+      <c r="Z9" s="4">
         <f t="shared" si="7"/>
         <v>-0.22608695652173938</v>
       </c>
-      <c r="AA9" s="2">
+      <c r="AA9" s="4">
         <f t="shared" si="8"/>
         <v>-0.21153846153846145</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1269,6 +1389,9 @@
         <f t="shared" si="4"/>
         <v>80.262999999999991</v>
       </c>
+      <c r="V10" t="s">
+        <v>19</v>
+      </c>
       <c r="W10" t="b">
         <f t="shared" si="5"/>
         <v>1</v>
@@ -1286,229 +1409,253 @@
         <v>-9.3167701863354768E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="A11">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A11" s="3">
         <v>10</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="3">
         <v>85.7</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="3">
         <v>161.19999999999999</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="3">
         <v>-99.3</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="3">
         <v>-94.6</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="3">
         <v>-139.5</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="3">
         <v>-13.5</v>
       </c>
-      <c r="I11">
+      <c r="H11" s="3"/>
+      <c r="I11" s="3">
         <v>59.027999999999999</v>
       </c>
-      <c r="J11">
+      <c r="J11" s="3">
         <v>188.89400000000001</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="3">
         <v>58.817999999999998</v>
       </c>
-      <c r="L11">
+      <c r="L11" s="3">
         <v>142.77099999999999</v>
       </c>
-      <c r="N11" t="s">
+      <c r="M11" s="3"/>
+      <c r="N11" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="O11">
+      <c r="O11" s="3">
         <f t="shared" si="0"/>
         <v>75.499999999999986</v>
       </c>
-      <c r="P11">
+      <c r="P11" s="3">
         <f t="shared" si="1"/>
         <v>4.7000000000000028</v>
       </c>
-      <c r="Q11">
+      <c r="Q11" s="3">
         <f t="shared" si="2"/>
         <v>126</v>
       </c>
-      <c r="S11">
+      <c r="R11" s="3"/>
+      <c r="S11" s="3">
         <f t="shared" si="3"/>
         <v>129.86600000000001</v>
       </c>
-      <c r="T11">
+      <c r="T11" s="3">
         <f t="shared" si="4"/>
         <v>83.952999999999989</v>
       </c>
-      <c r="W11" t="str">
+      <c r="U11" s="3"/>
+      <c r="V11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="W11" s="3" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="X11" t="str">
+      <c r="X11" s="3" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="Z11" s="2" t="str">
+      <c r="Y11" s="3"/>
+      <c r="Z11" s="4" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AA11" s="2" t="str">
+      <c r="AA11" s="4" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="A12">
+    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A12" s="3">
         <v>11</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="3">
         <v>85.7</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="3">
         <v>161.1</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="3">
         <v>-99</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="3">
         <v>-95.5</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="3">
         <v>-139.4</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="3">
         <v>-24</v>
       </c>
-      <c r="I12">
+      <c r="H12" s="3"/>
+      <c r="I12" s="3">
         <v>59.106000000000002</v>
       </c>
-      <c r="J12">
+      <c r="J12" s="3">
         <v>175.53100000000001</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="3">
         <v>58.820999999999998</v>
       </c>
-      <c r="L12">
+      <c r="L12" s="3">
         <v>139.89400000000001</v>
       </c>
-      <c r="N12" t="s">
+      <c r="M12" s="3"/>
+      <c r="N12" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="O12">
+      <c r="O12" s="3">
         <f t="shared" si="0"/>
         <v>75.399999999999991</v>
       </c>
-      <c r="P12">
+      <c r="P12" s="3">
         <f t="shared" si="1"/>
         <v>3.5</v>
       </c>
-      <c r="Q12">
+      <c r="Q12" s="3">
         <f t="shared" si="2"/>
         <v>115.4</v>
       </c>
-      <c r="S12">
+      <c r="R12" s="3"/>
+      <c r="S12" s="3">
         <f t="shared" si="3"/>
         <v>116.42500000000001</v>
       </c>
-      <c r="T12">
+      <c r="T12" s="3">
         <f t="shared" si="4"/>
         <v>81.073000000000008</v>
       </c>
-      <c r="W12" t="str">
+      <c r="U12" s="3"/>
+      <c r="V12" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="W12" s="3" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="X12" t="str">
+      <c r="X12" s="3" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="Z12" s="2" t="str">
+      <c r="Y12" s="3"/>
+      <c r="Z12" s="4" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AA12" s="2" t="str">
+      <c r="AA12" s="4" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.35">
-      <c r="A13">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
+      <c r="A13" s="3">
         <v>12</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="3">
         <v>86.3</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="3">
         <v>161.30000000000001</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="3">
         <v>-98.6</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="3">
         <v>-94.9</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="3">
         <v>-139</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="3">
         <v>-26</v>
       </c>
-      <c r="I13">
+      <c r="H13" s="3"/>
+      <c r="I13" s="3">
         <v>58.655000000000001</v>
       </c>
-      <c r="J13">
+      <c r="J13" s="3">
         <v>177.50899999999999</v>
       </c>
-      <c r="K13">
+      <c r="K13" s="3">
         <v>58.7</v>
       </c>
-      <c r="L13">
+      <c r="L13" s="3">
         <v>142</v>
       </c>
-      <c r="N13" t="s">
+      <c r="M13" s="3"/>
+      <c r="N13" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="O13">
+      <c r="O13" s="3">
         <f t="shared" si="0"/>
         <v>75.000000000000014</v>
       </c>
-      <c r="P13">
+      <c r="P13" s="3">
         <f t="shared" si="1"/>
         <v>3.6999999999999886</v>
       </c>
-      <c r="Q13">
+      <c r="Q13" s="3">
         <f t="shared" si="2"/>
         <v>113</v>
       </c>
-      <c r="S13">
+      <c r="R13" s="3"/>
+      <c r="S13" s="3">
         <f t="shared" si="3"/>
         <v>118.85399999999998</v>
       </c>
-      <c r="T13">
+      <c r="T13" s="3">
         <f t="shared" si="4"/>
         <v>83.3</v>
       </c>
-      <c r="W13" t="str">
+      <c r="U13" s="3"/>
+      <c r="V13" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="W13" s="3" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="X13" t="str">
+      <c r="X13" s="3" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="Z13" s="2" t="str">
+      <c r="Y13" s="3"/>
+      <c r="Z13" s="4" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AA13" s="2" t="str">
+      <c r="AA13" s="4" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1565,6 +1712,9 @@
         <f t="shared" si="4"/>
         <v>79.75800000000001</v>
       </c>
+      <c r="V14" t="s">
+        <v>19</v>
+      </c>
       <c r="W14" t="b">
         <f t="shared" si="5"/>
         <v>1</v>
@@ -1582,7 +1732,7 @@
         <v>-8.0745341614907318E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1639,6 +1789,9 @@
         <f t="shared" si="4"/>
         <v>79.664000000000016</v>
       </c>
+      <c r="V15" t="s">
+        <v>19</v>
+      </c>
       <c r="W15" t="b">
         <f t="shared" si="5"/>
         <v>1</v>
@@ -1656,7 +1809,7 @@
         <v>-1.055900621118E-2</v>
       </c>
     </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1713,6 +1866,9 @@
         <f t="shared" si="4"/>
         <v>121.87899999999999</v>
       </c>
+      <c r="V16" t="s">
+        <v>18</v>
+      </c>
       <c r="W16" t="b">
         <f t="shared" si="5"/>
         <v>1</v>
@@ -1730,1043 +1886,3196 @@
         <v>2.2400000000000087E-2</v>
       </c>
     </row>
-    <row r="17" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A17">
+    <row r="17" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A17" s="3">
         <v>16</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="3">
         <v>212.1</v>
       </c>
-      <c r="C17">
+      <c r="C17" s="3">
         <v>374.9</v>
       </c>
-      <c r="D17">
+      <c r="D17" s="3">
         <v>-129.80000000000001</v>
       </c>
-      <c r="E17">
+      <c r="E17" s="3">
         <v>-94.3</v>
       </c>
-      <c r="F17">
+      <c r="F17" s="3">
         <v>-162.19999999999999</v>
       </c>
-      <c r="G17">
+      <c r="G17" s="3">
         <v>-69.599999999999994</v>
       </c>
-      <c r="I17">
+      <c r="H17" s="3"/>
+      <c r="I17" s="3">
         <v>57.219000000000001</v>
       </c>
-      <c r="J17">
+      <c r="J17" s="3">
         <v>222.655</v>
       </c>
-      <c r="K17">
+      <c r="K17" s="3">
         <v>61.201999999999998</v>
       </c>
-      <c r="L17">
+      <c r="L17" s="3">
         <v>149.279</v>
       </c>
-      <c r="N17" t="s">
+      <c r="M17" s="3"/>
+      <c r="N17" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="O17">
+      <c r="O17" s="3">
         <f t="shared" si="0"/>
         <v>162.79999999999998</v>
       </c>
-      <c r="P17">
+      <c r="P17" s="3">
         <f t="shared" si="1"/>
         <v>35.500000000000014</v>
       </c>
-      <c r="Q17">
+      <c r="Q17" s="3">
         <f t="shared" si="2"/>
         <v>92.6</v>
       </c>
-      <c r="S17">
+      <c r="R17" s="3"/>
+      <c r="S17" s="3">
         <f t="shared" si="3"/>
         <v>165.43600000000001</v>
       </c>
-      <c r="T17">
+      <c r="T17" s="3">
         <f t="shared" si="4"/>
         <v>88.076999999999998</v>
       </c>
-      <c r="W17" t="str">
+      <c r="U17" s="3"/>
+      <c r="V17" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="W17" s="3" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="X17" t="str">
+      <c r="X17" s="3" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="Z17" s="2" t="str">
+      <c r="Y17" s="3"/>
+      <c r="Z17" s="4" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AA17" s="2" t="str">
+      <c r="AA17" s="4" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A18">
+    <row r="18" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A18" s="3">
         <v>17</v>
       </c>
-      <c r="B18">
+      <c r="B18" s="3">
         <v>211.8</v>
       </c>
-      <c r="C18">
+      <c r="C18" s="3">
         <v>374.1</v>
       </c>
-      <c r="D18">
+      <c r="D18" s="3">
         <v>-128.6</v>
       </c>
-      <c r="E18">
+      <c r="E18" s="3">
         <v>-94.5</v>
       </c>
-      <c r="F18">
+      <c r="F18" s="3">
         <v>-162.69999999999999</v>
       </c>
-      <c r="G18">
+      <c r="G18" s="3">
         <v>-69.099999999999994</v>
       </c>
-      <c r="I18">
+      <c r="H18" s="3"/>
+      <c r="I18" s="3">
         <v>58.011000000000003</v>
       </c>
-      <c r="J18">
+      <c r="J18" s="3">
         <v>223.191</v>
       </c>
-      <c r="K18">
+      <c r="K18" s="3">
         <v>60.99</v>
       </c>
-      <c r="L18">
+      <c r="L18" s="3">
         <v>148.876</v>
       </c>
-      <c r="N18" t="s">
+      <c r="M18" s="3"/>
+      <c r="N18" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="O18">
+      <c r="O18" s="3">
         <f t="shared" si="0"/>
         <v>162.30000000000001</v>
       </c>
-      <c r="P18">
+      <c r="P18" s="3">
         <f t="shared" si="1"/>
         <v>34.099999999999994</v>
       </c>
-      <c r="Q18">
+      <c r="Q18" s="3">
         <f t="shared" si="2"/>
         <v>93.6</v>
       </c>
-      <c r="S18">
+      <c r="R18" s="3"/>
+      <c r="S18" s="3">
         <f t="shared" si="3"/>
         <v>165.18</v>
       </c>
-      <c r="T18">
+      <c r="T18" s="3">
         <f t="shared" si="4"/>
         <v>87.885999999999996</v>
       </c>
-      <c r="W18" t="str">
+      <c r="U18" s="3"/>
+      <c r="V18" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="W18" s="3" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="X18" t="str">
+      <c r="X18" s="3" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="Z18" s="2" t="str">
+      <c r="Y18" s="3"/>
+      <c r="Z18" s="4" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AA18" s="2" t="str">
+      <c r="AA18" s="4" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A19">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A19" s="3">
         <v>18</v>
       </c>
-      <c r="B19">
+      <c r="B19" s="3">
         <v>211.7</v>
       </c>
-      <c r="C19">
+      <c r="C19" s="3">
         <v>375.1</v>
       </c>
-      <c r="D19">
+      <c r="D19" s="3">
         <v>-129.6</v>
       </c>
-      <c r="E19">
+      <c r="E19" s="3">
         <v>-94.5</v>
       </c>
-      <c r="F19">
+      <c r="F19" s="3">
         <v>-162.69999999999999</v>
       </c>
-      <c r="G19">
+      <c r="G19" s="3">
         <v>-69.2</v>
       </c>
-      <c r="I19">
+      <c r="H19" s="3"/>
+      <c r="I19" s="3">
         <v>57.895000000000003</v>
       </c>
-      <c r="J19">
+      <c r="J19" s="3">
         <v>224.11500000000001</v>
       </c>
-      <c r="K19">
+      <c r="K19" s="3">
         <v>61.313000000000002</v>
       </c>
-      <c r="L19">
+      <c r="L19" s="3">
         <v>149.20099999999999</v>
       </c>
-      <c r="N19" t="s">
+      <c r="M19" s="3"/>
+      <c r="N19" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="O19">
+      <c r="O19" s="3">
         <f t="shared" si="0"/>
         <v>163.40000000000003</v>
       </c>
-      <c r="P19">
+      <c r="P19" s="3">
         <f t="shared" si="1"/>
         <v>35.099999999999994</v>
       </c>
-      <c r="Q19">
+      <c r="Q19" s="3">
         <f t="shared" si="2"/>
         <v>93.499999999999986</v>
       </c>
-      <c r="S19">
+      <c r="R19" s="3"/>
+      <c r="S19" s="3">
         <f t="shared" si="3"/>
         <v>166.22</v>
       </c>
-      <c r="T19">
+      <c r="T19" s="3">
         <f t="shared" si="4"/>
         <v>87.887999999999991</v>
       </c>
-      <c r="W19" t="str">
+      <c r="U19" s="3"/>
+      <c r="V19" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="W19" s="3" t="str">
         <f t="shared" si="5"/>
         <v/>
       </c>
-      <c r="X19" t="str">
+      <c r="X19" s="3" t="str">
         <f t="shared" si="6"/>
         <v/>
       </c>
-      <c r="Z19" s="2" t="str">
+      <c r="Y19" s="3"/>
+      <c r="Z19" s="4" t="str">
         <f t="shared" si="7"/>
         <v/>
       </c>
-      <c r="AA19" s="2" t="str">
+      <c r="AA19" s="4" t="str">
         <f t="shared" si="8"/>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A20">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A20" s="3">
         <v>19</v>
       </c>
-      <c r="B20">
+      <c r="B20" s="3">
         <v>211.3</v>
       </c>
-      <c r="C20">
+      <c r="C20" s="3">
         <v>381.9</v>
       </c>
-      <c r="D20">
+      <c r="D20" s="3">
         <v>-101</v>
       </c>
-      <c r="E20">
+      <c r="E20" s="3">
         <v>-90.1</v>
       </c>
-      <c r="F20">
+      <c r="F20" s="3">
         <v>-212.9</v>
       </c>
-      <c r="G20">
+      <c r="G20" s="3">
         <v>-91.6</v>
       </c>
-      <c r="I20">
+      <c r="H20" s="3"/>
+      <c r="I20" s="3">
         <v>58.957000000000001</v>
       </c>
-      <c r="J20">
+      <c r="J20" s="3">
         <v>230.018</v>
       </c>
-      <c r="K20">
+      <c r="K20" s="3">
         <v>58.753</v>
       </c>
-      <c r="L20">
+      <c r="L20" s="3">
         <v>180.70400000000001</v>
       </c>
-      <c r="N20" t="s">
+      <c r="M20" s="3"/>
+      <c r="N20" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="O20">
+      <c r="O20" s="3">
         <f t="shared" si="0"/>
         <v>170.59999999999997</v>
       </c>
-      <c r="P20">
+      <c r="P20" s="3">
         <f t="shared" si="1"/>
         <v>10.900000000000006</v>
       </c>
-      <c r="Q20">
+      <c r="Q20" s="3">
         <f t="shared" si="2"/>
         <v>121.30000000000001</v>
       </c>
-      <c r="S20">
+      <c r="R20" s="3"/>
+      <c r="S20" s="3">
         <f t="shared" si="3"/>
         <v>171.06100000000001</v>
       </c>
-      <c r="T20">
+      <c r="T20" s="3">
         <f t="shared" si="4"/>
         <v>121.95100000000001</v>
       </c>
-      <c r="W20" t="b">
+      <c r="U20" s="3"/>
+      <c r="V20" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W20" s="3" t="b">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="X20" t="b">
+      <c r="X20" s="3" t="b">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="Z20" s="2">
+      <c r="Y20" s="3"/>
+      <c r="Z20" s="4">
         <f t="shared" si="7"/>
         <v>-3.529411764705781E-3</v>
       </c>
-      <c r="AA20" s="2">
+      <c r="AA20" s="4">
         <f t="shared" si="8"/>
         <v>2.959999999999996E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="A21">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A21" s="3">
         <v>20</v>
       </c>
-      <c r="B21">
+      <c r="B21" s="3">
         <v>212</v>
       </c>
-      <c r="C21">
+      <c r="C21" s="3">
         <v>383</v>
       </c>
-      <c r="D21">
+      <c r="D21" s="3">
         <v>-100</v>
       </c>
-      <c r="E21">
+      <c r="E21" s="3">
         <v>-92.4</v>
       </c>
-      <c r="F21">
+      <c r="F21" s="3">
         <v>-213.3</v>
       </c>
-      <c r="G21">
+      <c r="G21" s="3">
         <v>-91.8</v>
       </c>
-      <c r="I21">
+      <c r="H21" s="3"/>
+      <c r="I21" s="3">
         <v>58.283999999999999</v>
       </c>
-      <c r="J21">
+      <c r="J21" s="3">
         <v>228.96199999999999</v>
       </c>
-      <c r="K21">
+      <c r="K21" s="3">
         <v>57.643000000000001</v>
       </c>
-      <c r="L21">
+      <c r="L21" s="3">
         <v>179.40700000000001</v>
       </c>
-      <c r="N21" t="s">
+      <c r="M21" s="3"/>
+      <c r="N21" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="O21">
+      <c r="O21" s="3">
         <f t="shared" si="0"/>
         <v>171</v>
       </c>
-      <c r="P21">
+      <c r="P21" s="3">
         <f t="shared" si="1"/>
         <v>7.5999999999999943</v>
       </c>
-      <c r="Q21">
+      <c r="Q21" s="3">
         <f t="shared" si="2"/>
         <v>121.50000000000001</v>
       </c>
-      <c r="S21">
+      <c r="R21" s="3"/>
+      <c r="S21" s="3">
         <f t="shared" si="3"/>
         <v>170.678</v>
       </c>
-      <c r="T21">
+      <c r="T21" s="3">
         <f t="shared" si="4"/>
         <v>121.76400000000001</v>
       </c>
-      <c r="W21" t="b">
+      <c r="U21" s="3"/>
+      <c r="V21" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="W21" s="3" t="b">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="X21" t="b">
+      <c r="X21" s="3" t="b">
         <f t="shared" si="6"/>
         <v>1</v>
       </c>
-      <c r="Z21" s="2">
+      <c r="Y21" s="3"/>
+      <c r="Z21" s="4">
         <f t="shared" si="7"/>
         <v>-5.8823529411764497E-3</v>
       </c>
-      <c r="AA21" s="2">
+      <c r="AA21" s="4">
         <f t="shared" si="8"/>
         <v>2.7999999999999914E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:27" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>28</v>
+      </c>
+      <c r="B22">
+        <v>256.3</v>
+      </c>
+      <c r="C22">
+        <v>367.9</v>
+      </c>
+      <c r="D22">
+        <v>-98.2</v>
+      </c>
+      <c r="E22">
+        <v>-91.3</v>
+      </c>
+      <c r="F22">
+        <v>-63.5</v>
+      </c>
+      <c r="G22">
+        <v>11.9</v>
+      </c>
+      <c r="I22">
+        <v>62.457000000000001</v>
+      </c>
+      <c r="J22">
+        <v>174.20500000000001</v>
+      </c>
+      <c r="K22">
+        <v>59.051000000000002</v>
+      </c>
+      <c r="L22">
+        <v>134.238</v>
+      </c>
+      <c r="N22" t="s">
+        <v>17</v>
+      </c>
+      <c r="O22">
+        <f t="shared" si="0"/>
+        <v>111.59999999999997</v>
+      </c>
+      <c r="P22">
+        <f t="shared" si="1"/>
+        <v>6.9000000000000057</v>
+      </c>
+      <c r="Q22">
+        <f t="shared" si="2"/>
+        <v>75.400000000000006</v>
+      </c>
+      <c r="S22">
+        <f t="shared" si="3"/>
+        <v>111.74800000000002</v>
+      </c>
+      <c r="T22">
+        <f t="shared" si="4"/>
+        <v>75.186999999999998</v>
+      </c>
+      <c r="V22" t="s">
+        <v>17</v>
+      </c>
+      <c r="W22" t="b">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="X22" t="b">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="Z22" s="2">
+        <f t="shared" si="7"/>
+        <v>2.9565217391304688E-2</v>
+      </c>
+      <c r="AA22" s="2">
+        <f t="shared" si="8"/>
+        <v>3.3333333333333215E-2</v>
+      </c>
+    </row>
+    <row r="23" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>29</v>
+      </c>
+      <c r="B23">
+        <v>255.3</v>
+      </c>
+      <c r="C23">
+        <v>368.6</v>
+      </c>
+      <c r="D23">
+        <v>-99.1</v>
+      </c>
+      <c r="E23">
+        <v>-92.1</v>
+      </c>
+      <c r="F23">
+        <v>-63</v>
+      </c>
+      <c r="G23">
+        <v>12</v>
+      </c>
+      <c r="I23">
+        <v>62.268000000000001</v>
+      </c>
+      <c r="J23">
+        <v>175.666</v>
+      </c>
+      <c r="K23">
+        <v>59.048000000000002</v>
+      </c>
+      <c r="L23">
+        <v>133.364</v>
+      </c>
       <c r="N23" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="O23">
-        <v>170</v>
+        <f t="shared" ref="O23:O24" si="9">C23-B23</f>
+        <v>113.30000000000001</v>
+      </c>
+      <c r="P23">
+        <f t="shared" ref="P23:P24" si="10">E23-D23</f>
+        <v>7</v>
       </c>
       <c r="Q23">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="24" spans="1:27" ht="16" x14ac:dyDescent="0.4">
+        <f t="shared" ref="Q23:Q24" si="11">G23-F23</f>
+        <v>75</v>
+      </c>
+      <c r="S23">
+        <f t="shared" si="3"/>
+        <v>113.398</v>
+      </c>
+      <c r="T23">
+        <f t="shared" si="4"/>
+        <v>74.316000000000003</v>
+      </c>
+      <c r="V23" t="s">
+        <v>17</v>
+      </c>
+      <c r="W23" t="b">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="X23" t="b">
+        <f t="shared" si="6"/>
+        <v>1</v>
+      </c>
+      <c r="Z23" s="2">
+        <f t="shared" si="7"/>
+        <v>1.4782608695652066E-2</v>
+      </c>
+      <c r="AA23" s="2">
+        <f t="shared" si="8"/>
+        <v>3.8461538461538436E-2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>30</v>
+      </c>
+      <c r="B24">
+        <v>256.2</v>
+      </c>
+      <c r="C24">
+        <v>367.5</v>
+      </c>
+      <c r="D24">
+        <v>-99</v>
+      </c>
+      <c r="E24">
+        <v>-92.2</v>
+      </c>
+      <c r="F24">
+        <v>-63</v>
+      </c>
+      <c r="G24">
+        <v>10</v>
+      </c>
+      <c r="I24">
+        <v>62.220999999999997</v>
+      </c>
+      <c r="J24">
+        <v>173.79900000000001</v>
+      </c>
+      <c r="K24">
+        <v>58.951000000000001</v>
+      </c>
+      <c r="L24">
+        <v>131.56200000000001</v>
+      </c>
       <c r="N24" t="s">
         <v>17</v>
       </c>
       <c r="O24">
-        <v>115</v>
+        <f t="shared" si="9"/>
+        <v>111.30000000000001</v>
+      </c>
+      <c r="P24">
+        <f t="shared" si="10"/>
+        <v>6.7999999999999972</v>
       </c>
       <c r="Q24">
-        <v>78</v>
-      </c>
-      <c r="V24" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="W24" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="X24" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Z24" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="AA24" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="25" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="N25" t="s">
-        <v>19</v>
-      </c>
-      <c r="O25">
-        <v>74</v>
-      </c>
-      <c r="Q25">
-        <v>161</v>
-      </c>
-      <c r="V25">
-        <v>1</v>
-      </c>
-      <c r="W25" t="b">
-        <f>IF(N2="Sblob",
-    AND(S2 &gt;= O$23*(1-0.05), S2 &lt;= O$23*(1+0.05)),
-IF(N2="Lblob",
-    AND(S2 &gt;= O$24*(1-0.05), S2 &lt;= O$24*(1+0.05)),
-IF(N2="Rec",
-    AND(S2 &gt;= O$25*(1-0.05), S2 &lt;= O$25*(1+0.05)),
+        <f t="shared" si="11"/>
+        <v>73</v>
+      </c>
+      <c r="S24">
+        <f t="shared" si="3"/>
+        <v>111.578</v>
+      </c>
+      <c r="T24">
+        <f t="shared" si="4"/>
+        <v>72.611000000000018</v>
+      </c>
+      <c r="V24" t="s">
+        <v>17</v>
+      </c>
+      <c r="W24" t="b">
+        <f>IF(N24="Sblob",
+    AND(O24 &gt;= O$28*(1-0.05), O24 &lt;= O$28*(1+0.05)),
+IF(N24="Lblob",
+    AND(O24 &gt;= O$29*(1-0.05), O24 &lt;= O$29*(1+0.05)),
+IF(N24="Rec",
+    AND(O24 &gt;= O$30*(1-0.05), O24 &lt;= O$30*(1+0.05)),
 ""
 )))</f>
         <v>1</v>
       </c>
-      <c r="X25" t="b">
+      <c r="X24" t="b">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="Z24" s="2">
+        <f t="shared" si="7"/>
+        <v>3.2173913043478164E-2</v>
+      </c>
+      <c r="AA24" s="2">
+        <f t="shared" si="8"/>
+        <v>6.4102564102564097E-2</v>
+      </c>
+    </row>
+    <row r="26" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C26" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E26" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G26" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H26" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I26" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="J26" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="K26" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="L26" s="1" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="27" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="C27" s="3">
+        <v>200</v>
+      </c>
+      <c r="D27" s="3"/>
+      <c r="E27" s="3">
+        <v>218</v>
+      </c>
+      <c r="F27" s="3"/>
+      <c r="G27" s="3">
+        <v>-250</v>
+      </c>
+      <c r="I27">
+        <v>-197.8665</v>
+      </c>
+      <c r="J27" s="3">
+        <v>25</v>
+      </c>
+      <c r="K27" s="3">
+        <f>(500-364)</f>
+        <v>136</v>
+      </c>
+      <c r="L27" s="3">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B28" t="s">
+        <v>18</v>
+      </c>
+      <c r="C28">
+        <f>800-220-170</f>
+        <v>410</v>
+      </c>
+      <c r="D28">
+        <f>800-220</f>
+        <v>580</v>
+      </c>
+      <c r="E28">
+        <v>60.5</v>
+      </c>
+      <c r="F28">
+        <v>55</v>
+      </c>
+      <c r="G28">
+        <v>320</v>
+      </c>
+      <c r="H28">
+        <v>195</v>
+      </c>
+      <c r="N28" t="s">
+        <v>18</v>
+      </c>
+      <c r="O28">
+        <v>170</v>
+      </c>
+      <c r="P28" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q28">
+        <v>125</v>
+      </c>
+      <c r="V28" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="W28" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="X28" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Z28" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AA28" s="1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="29" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="B29" t="s">
+        <v>17</v>
+      </c>
+      <c r="C29">
+        <f>800-235-115</f>
+        <v>450</v>
+      </c>
+      <c r="D29">
+        <f>800-235</f>
+        <v>565</v>
+      </c>
+      <c r="E29">
+        <v>59.5</v>
+      </c>
+      <c r="F29">
+        <v>55.5</v>
+      </c>
+      <c r="G29">
+        <v>173</v>
+      </c>
+      <c r="H29">
+        <v>95</v>
+      </c>
+      <c r="N29" t="s">
+        <v>17</v>
+      </c>
+      <c r="O29">
+        <v>115</v>
+      </c>
+      <c r="P29" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q29">
+        <v>78</v>
+      </c>
+      <c r="U29" t="s">
+        <v>18</v>
+      </c>
+      <c r="V29">
+        <v>1</v>
+      </c>
+      <c r="W29" t="b">
         <f>IF(N2="Sblob",
-    AND(T2 &gt;= Q$23*(1-0.05), T2 &lt;= Q$23*(1+0.05)),
+    AND(S2 &gt;= O$28*(1-0.05), S2 &lt;= O$28*(1+0.05)),
 IF(N2="Lblob",
-    AND(T2 &gt;= Q$24*(1-0.05), T2 &lt;= Q$24*(1+0.05)),
+    AND(S2 &gt;= O$29*(1-0.05), S2 &lt;= O$29*(1+0.05)),
 IF(N2="Rec",
-    AND(T2 &gt;= Q$25*(1-0.05), T2 &lt;= Q$25*(1+0.05)),
+    AND(S2 &gt;= O$30*(1-0.05), S2 &lt;= O$30*(1+0.05)),
 ""
 )))</f>
         <v>1</v>
       </c>
-      <c r="Z25">
-        <f>IF(N2="Sblob", 1-S2/O$23,
-   IF(N2="Lblob", 1-S2/O$24,
-   IF(N2="Rec", 1-S2/O$25,
+      <c r="X29" t="b">
+        <f>IF(N2="Sblob",
+    AND(T2 &gt;= Q$28*(1-0.05), T2 &lt;= Q$28*(1+0.05)),
+IF(N2="Lblob",
+    AND(T2 &gt;= Q$29*(1-0.05), T2 &lt;= Q$29*(1+0.05)),
+IF(N2="Rec",
+    AND(T2 &gt;= Q$30*(1-0.05), T2 &lt;= Q$30*(1+0.05)),
+""
+)))</f>
+        <v>1</v>
+      </c>
+      <c r="Z29">
+        <f>IF(N2="Sblob", 1-S2/O$28,
+   IF(N2="Lblob", 1-S2/O$29,
+   IF(N2="Rec", 1-S2/O$30,
 ""
 )))</f>
         <v>1.6470588235294459E-3</v>
       </c>
-      <c r="AA25">
-        <f>IF(N2="Sblob", 1-T2/Q$23,
-   IF(N2="Lblob", 1-T2/Q$24,
-   IF(N2="Rec", 1-T2/Q$25,
+      <c r="AA29">
+        <f>IF(N2="Sblob", 1-T2/Q$28,
+   IF(N2="Lblob", 1-T2/Q$29,
+   IF(N2="Rec", 1-T2/Q$30,
 ""
 )))</f>
         <v>2.5935999999999959E-2</v>
       </c>
     </row>
-    <row r="26" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="N26" t="s">
-        <v>21</v>
-      </c>
-      <c r="O26" t="s">
+    <row r="30" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="B30" t="s">
+        <v>19</v>
+      </c>
+      <c r="C30">
+        <v>285</v>
+      </c>
+      <c r="D30">
+        <f>C30+74</f>
+        <v>359</v>
+      </c>
+      <c r="E30">
+        <v>60</v>
+      </c>
+      <c r="F30">
+        <v>58</v>
+      </c>
+      <c r="G30">
+        <v>246</v>
+      </c>
+      <c r="H30">
+        <v>85</v>
+      </c>
+      <c r="N30" t="s">
+        <v>19</v>
+      </c>
+      <c r="O30">
+        <v>74</v>
+      </c>
+      <c r="P30" t="s">
         <v>20</v>
       </c>
-      <c r="Q26" t="s">
-        <v>20</v>
-      </c>
-      <c r="V26">
+      <c r="Q30">
+        <v>161</v>
+      </c>
+      <c r="U30" t="s">
+        <v>18</v>
+      </c>
+      <c r="V30">
         <v>2</v>
       </c>
-      <c r="W26" t="b">
-        <f t="shared" ref="W26:W31" si="9">IF(N3="Sblob",
-    AND(S3 &gt;= O$23*(1-0.05), S3 &lt;= O$23*(1+0.05)),
+      <c r="W30" t="b">
+        <f t="shared" ref="W30:W53" si="12">IF(N3="Sblob",
+    AND(S3 &gt;= O$28*(1-0.05), S3 &lt;= O$28*(1+0.05)),
 IF(N3="Lblob",
-    AND(S3 &gt;= O$24*(1-0.05), S3 &lt;= O$24*(1+0.05)),
+    AND(S3 &gt;= O$29*(1-0.05), S3 &lt;= O$29*(1+0.05)),
 IF(N3="Rec",
-    AND(S3 &gt;= O$25*(1-0.05), S3 &lt;= O$25*(1+0.05)),
+    AND(S3 &gt;= O$30*(1-0.05), S3 &lt;= O$30*(1+0.05)),
 ""
 )))</f>
         <v>1</v>
       </c>
-      <c r="X26" t="b">
-        <f t="shared" ref="X26:X31" si="10">IF(N3="Sblob",
-    AND(T3 &gt;= Q$23*(1-0.05), T3 &lt;= Q$23*(1+0.05)),
+      <c r="X30" t="b">
+        <f t="shared" ref="X30:X53" si="13">IF(N3="Sblob",
+    AND(T3 &gt;= Q$28*(1-0.05), T3 &lt;= Q$28*(1+0.05)),
 IF(N3="Lblob",
-    AND(T3 &gt;= Q$24*(1-0.05), T3 &lt;= Q$24*(1+0.05)),
+    AND(T3 &gt;= Q$29*(1-0.05), T3 &lt;= Q$29*(1+0.05)),
 IF(N3="Rec",
-    AND(T3 &gt;= Q$25*(1-0.05), T3 &lt;= Q$25*(1+0.05)),
+    AND(T3 &gt;= Q$30*(1-0.05), T3 &lt;= Q$30*(1+0.05)),
 ""
 )))</f>
         <v>1</v>
       </c>
-      <c r="Z26">
-        <f t="shared" ref="Z26:Z44" si="11">IF(N3="Sblob", 1-S3/O$23,
-   IF(N3="Lblob", 1-S3/O$24,
-   IF(N3="Rec", 1-S3/O$25,
+      <c r="Z30">
+        <f t="shared" ref="Z30:Z51" si="14">IF(N3="Sblob", 1-S3/O$28,
+   IF(N3="Lblob", 1-S3/O$29,
+   IF(N3="Rec", 1-S3/O$30,
 ""
 )))</f>
         <v>-3.4176470588234142E-3</v>
       </c>
-      <c r="AA26">
-        <f t="shared" ref="AA26:AA44" si="12">IF(N3="Sblob", 1-T3/Q$23,
-   IF(N3="Lblob", 1-T3/Q$24,
-   IF(N3="Rec", 1-T3/Q$25,
+      <c r="AA30">
+        <f t="shared" ref="AA30:AA51" si="15">IF(N3="Sblob", 1-T3/Q$28,
+   IF(N3="Lblob", 1-T3/Q$29,
+   IF(N3="Rec", 1-T3/Q$30,
 ""
 )))</f>
         <v>2.6488000000000067E-2</v>
       </c>
     </row>
-    <row r="27" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="V27">
+    <row r="31" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="N31" t="s">
+        <v>21</v>
+      </c>
+      <c r="O31" t="s">
+        <v>20</v>
+      </c>
+      <c r="P31" t="s">
+        <v>20</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>20</v>
+      </c>
+      <c r="U31" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="V31" s="3">
         <v>3</v>
       </c>
-      <c r="W27" t="b">
-        <f t="shared" si="9"/>
+      <c r="W31" s="3" t="b">
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="X27" t="b">
-        <f t="shared" si="10"/>
+      <c r="X31" s="3" t="b">
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="Z27">
-        <f t="shared" si="11"/>
+      <c r="Y31" s="3"/>
+      <c r="Z31" s="3">
+        <f t="shared" si="14"/>
         <v>-9.648695652173922E-2</v>
       </c>
-      <c r="AA27">
+      <c r="AA31" s="3">
+        <f t="shared" si="15"/>
+        <v>7.3115384615384693E-2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A32" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E32" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F32" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G32" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H32" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I32" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="J32" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="K32" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="L32" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M32" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N32" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="U32" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="V32" s="3">
+        <v>4</v>
+      </c>
+      <c r="W32" s="3" t="b">
         <f t="shared" si="12"/>
-        <v>7.3115384615384693E-2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="V28">
-        <v>4</v>
-      </c>
-      <c r="W28" t="b">
-        <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="X28" t="b">
-        <f t="shared" si="10"/>
+      <c r="X32" s="3" t="b">
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="Z28">
-        <f t="shared" si="11"/>
+      <c r="Y32" s="3"/>
+      <c r="Z32" s="3">
+        <f t="shared" si="14"/>
         <v>-8.0147826086956364E-2</v>
       </c>
-      <c r="AA28">
-        <f t="shared" si="12"/>
+      <c r="AA32" s="3">
+        <f t="shared" si="15"/>
         <v>6.6141025641025752E-2</v>
       </c>
     </row>
-    <row r="29" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="V29">
-        <v>5</v>
-      </c>
-      <c r="W29" t="b">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="X29" t="b">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="Z29">
-        <f t="shared" si="11"/>
-        <v>-9.2208695652173933E-2</v>
-      </c>
-      <c r="AA29">
-        <f t="shared" si="12"/>
-        <v>-5.0217948717948602E-2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="V30">
-        <v>6</v>
-      </c>
-      <c r="W30" t="b">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="X30" t="b">
-        <f t="shared" si="10"/>
+    <row r="33" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>18</v>
+      </c>
+      <c r="B33">
         <v>1</v>
       </c>
-      <c r="Z30">
-        <f t="shared" si="11"/>
-        <v>-0.13169565217391299</v>
-      </c>
-      <c r="AA30">
-        <f t="shared" si="12"/>
-        <v>3.9102564102565518E-3</v>
-      </c>
-    </row>
-    <row r="31" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="V31">
-        <v>7</v>
-      </c>
-      <c r="W31" t="b">
-        <f t="shared" si="9"/>
-        <v>0</v>
-      </c>
-      <c r="X31" t="b">
-        <f t="shared" si="10"/>
-        <v>0</v>
-      </c>
-      <c r="Z31">
-        <f t="shared" si="11"/>
-        <v>-0.35697391304347814</v>
-      </c>
-      <c r="AA31">
-        <f t="shared" si="12"/>
-        <v>-0.16130769230769215</v>
-      </c>
-    </row>
-    <row r="32" spans="1:27" x14ac:dyDescent="0.35">
-      <c r="V32">
-        <v>8</v>
-      </c>
-      <c r="W32" t="b">
-        <f t="shared" ref="W32:W42" si="13">IF(N9="Sblob",
-    AND(S9 &gt;= O$23*(1-0.05), S9 &lt;= O$23*(1+0.05)),
-IF(N9="Lblob",
-    AND(S9 &gt;= O$24*(1-0.05), S9 &lt;= O$24*(1+0.05)),
-IF(N9="Rec",
-    AND(S9 &gt;= O$25*(1-0.05), S9 &lt;= O$25*(1+0.05)),
+      <c r="C33">
+        <f>B2-$I$27</f>
+        <v>410.06650000000002</v>
+      </c>
+      <c r="D33">
+        <f>C2-$I$27</f>
+        <v>581.36649999999997</v>
+      </c>
+      <c r="E33">
+        <f>ABS(J$27+D2)</f>
+        <v>75.7</v>
+      </c>
+      <c r="F33">
+        <f>ABS(J$27+E2)</f>
+        <v>65.3</v>
+      </c>
+      <c r="G33">
+        <f>ABS(F2-K$27)</f>
+        <v>349.6</v>
+      </c>
+      <c r="H33">
+        <f>ABS(G2-K$27)</f>
+        <v>228.7</v>
+      </c>
+      <c r="I33">
+        <f>IF($A33="Sblob", C$28-C33,
+   IF($A33="Lblob", C$29-C33,
+   IF($A33="Rec", C$30-C33,
 ""
 )))</f>
-        <v>0</v>
-      </c>
-      <c r="X32" t="b">
-        <f t="shared" ref="X32:X42" si="14">IF(N9="Sblob",
-    AND(T9 &gt;= Q$23*(1-0.05), T9 &lt;= Q$23*(1+0.05)),
-IF(N9="Lblob",
-    AND(T9 &gt;= Q$24*(1-0.05), T9 &lt;= Q$24*(1+0.05)),
-IF(N9="Rec",
-    AND(T9 &gt;= Q$25*(1-0.05), T9 &lt;= Q$25*(1+0.05)),
+        <v>-6.6500000000019099E-2</v>
+      </c>
+      <c r="J33">
+        <f>IF($A33="Sblob", E$28-E33,
+   IF($A33="Lblob", E$29-E33,
+   IF($A33="Rec", E$30-E33,
 ""
 )))</f>
+        <v>-15.200000000000003</v>
+      </c>
+      <c r="K33">
+        <f>IF($A33="Sblob", G$28-G33,
+   IF($A33="Lblob", G$29-G33,
+   IF($A33="Rec", G$30-G33,
+""
+)))</f>
+        <v>-29.600000000000023</v>
+      </c>
+      <c r="L33" t="str">
+        <f>IF(ABS(I33)&lt;$L$27,"TRUE","False")</f>
+        <v>TRUE</v>
+      </c>
+      <c r="M33" t="str">
+        <f t="shared" ref="M33:N33" si="16">IF(ABS(J33)&lt;$L$27,"TRUE","False")</f>
+        <v>False</v>
+      </c>
+      <c r="N33" t="str">
+        <f t="shared" si="16"/>
+        <v>False</v>
+      </c>
+      <c r="U33" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="V33" s="3">
+        <v>5</v>
+      </c>
+      <c r="W33" s="3" t="b">
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="Z32">
-        <f t="shared" si="11"/>
-        <v>-0.22838260869565219</v>
-      </c>
-      <c r="AA32">
-        <f t="shared" si="12"/>
-        <v>-0.19546153846153813</v>
-      </c>
-    </row>
-    <row r="33" spans="22:27" x14ac:dyDescent="0.35">
-      <c r="V33">
-        <v>9</v>
-      </c>
-      <c r="W33" t="b">
+      <c r="X33" s="3" t="b">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="X33" t="b">
+      <c r="Y33" s="3"/>
+      <c r="Z33" s="3">
         <f t="shared" si="14"/>
+        <v>-9.2208695652173933E-2</v>
+      </c>
+      <c r="AA33" s="3">
+        <f t="shared" si="15"/>
+        <v>-5.0217948717948602E-2</v>
+      </c>
+    </row>
+    <row r="34" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>18</v>
+      </c>
+      <c r="B34">
+        <v>2</v>
+      </c>
+      <c r="C34">
+        <f t="shared" ref="C34:D34" si="17">B3-$I$27</f>
+        <v>410.56650000000002</v>
+      </c>
+      <c r="D34">
+        <f t="shared" si="17"/>
+        <v>581.36649999999997</v>
+      </c>
+      <c r="E34">
+        <f t="shared" ref="E34:E52" si="18">ABS(J$27+D3)</f>
+        <v>74.900000000000006</v>
+      </c>
+      <c r="F34">
+        <f t="shared" ref="F34:F52" si="19">ABS(J$27+E3)</f>
+        <v>67.3</v>
+      </c>
+      <c r="G34">
+        <f t="shared" ref="G34:G52" si="20">ABS(F3-K$27)</f>
+        <v>349.6</v>
+      </c>
+      <c r="H34">
+        <f t="shared" ref="H34:H52" si="21">ABS(G3-K$27)</f>
+        <v>228.2</v>
+      </c>
+      <c r="I34">
+        <f t="shared" ref="I34:I52" si="22">IF($A34="Sblob", C$28-C34,
+   IF($A34="Lblob", C$29-C34,
+   IF($A34="Rec", C$30-C34,
+""
+)))</f>
+        <v>-0.5665000000000191</v>
+      </c>
+      <c r="J34">
+        <f t="shared" ref="J34:J52" si="23">IF($A34="Sblob", E$28-E34,
+   IF($A34="Lblob", E$29-E34,
+   IF($A34="Rec", E$30-E34,
+""
+)))</f>
+        <v>-14.400000000000006</v>
+      </c>
+      <c r="K34">
+        <f t="shared" ref="K34:K52" si="24">IF($A34="Sblob", G$28-G34,
+   IF($A34="Lblob", G$29-G34,
+   IF($A34="Rec", G$30-G34,
+""
+)))</f>
+        <v>-29.600000000000023</v>
+      </c>
+      <c r="L34" t="str">
+        <f t="shared" ref="L34:L56" si="25">IF(ABS(I34)&lt;$L$27,"TRUE","False")</f>
+        <v>TRUE</v>
+      </c>
+      <c r="M34" t="str">
+        <f t="shared" ref="M34:M56" si="26">IF(ABS(J34)&lt;$L$27,"TRUE","False")</f>
+        <v>False</v>
+      </c>
+      <c r="N34" t="str">
+        <f t="shared" ref="N34:N56" si="27">IF(ABS(K34)&lt;$L$27,"TRUE","False")</f>
+        <v>False</v>
+      </c>
+      <c r="U34" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="V34" s="3">
+        <v>6</v>
+      </c>
+      <c r="W34" s="3" t="b">
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="Z33">
-        <f t="shared" si="11"/>
-        <v>-1.2418513513513512</v>
-      </c>
-      <c r="AA33">
+      <c r="X34" s="3" t="b">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="Y34" s="3"/>
+      <c r="Z34" s="3">
+        <f t="shared" si="14"/>
+        <v>-0.13169565217391299</v>
+      </c>
+      <c r="AA34" s="3">
+        <f t="shared" si="15"/>
+        <v>3.9102564102565518E-3</v>
+      </c>
+    </row>
+    <row r="35" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A35" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B35" s="3">
+        <v>3</v>
+      </c>
+      <c r="C35" s="3">
+        <f t="shared" ref="C35:D35" si="28">B4-$I$27</f>
+        <v>447.36649999999997</v>
+      </c>
+      <c r="D35" s="3">
+        <f t="shared" si="28"/>
+        <v>572.26649999999995</v>
+      </c>
+      <c r="E35" s="3">
+        <f t="shared" si="18"/>
+        <v>74.400000000000006</v>
+      </c>
+      <c r="F35" s="3">
+        <f t="shared" si="19"/>
+        <v>65.400000000000006</v>
+      </c>
+      <c r="G35" s="3">
+        <f t="shared" si="20"/>
+        <v>198.8</v>
+      </c>
+      <c r="H35" s="3">
+        <f t="shared" si="21"/>
+        <v>125.3</v>
+      </c>
+      <c r="I35" s="3">
+        <f t="shared" si="22"/>
+        <v>2.6335000000000264</v>
+      </c>
+      <c r="J35" s="3">
+        <f t="shared" si="23"/>
+        <v>-14.900000000000006</v>
+      </c>
+      <c r="K35" s="3">
+        <f t="shared" si="24"/>
+        <v>-25.800000000000011</v>
+      </c>
+      <c r="L35" t="str">
+        <f t="shared" si="25"/>
+        <v>TRUE</v>
+      </c>
+      <c r="M35" t="str">
+        <f t="shared" si="26"/>
+        <v>False</v>
+      </c>
+      <c r="N35" t="str">
+        <f t="shared" si="27"/>
+        <v>False</v>
+      </c>
+      <c r="U35" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="V35" s="3">
+        <v>7</v>
+      </c>
+      <c r="W35" s="3" t="b">
         <f t="shared" si="12"/>
-        <v>0.50147204968944104</v>
-      </c>
-    </row>
-    <row r="34" spans="22:27" x14ac:dyDescent="0.35">
-      <c r="V34">
-        <v>10</v>
-      </c>
-      <c r="W34" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="X34" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="Z34" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="AA34" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-    </row>
-    <row r="35" spans="22:27" x14ac:dyDescent="0.35">
-      <c r="V35">
-        <v>11</v>
-      </c>
-      <c r="W35" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="X35" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="Z35" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="AA35" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-    </row>
-    <row r="36" spans="22:27" x14ac:dyDescent="0.35">
-      <c r="V36">
-        <v>12</v>
-      </c>
-      <c r="W36" t="str">
-        <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="X36" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="Z36" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="AA36" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-    </row>
-    <row r="37" spans="22:27" x14ac:dyDescent="0.35">
-      <c r="V37">
-        <v>13</v>
-      </c>
-      <c r="W37" t="b">
+        <v>0</v>
+      </c>
+      <c r="X35" s="3" t="b">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="X37" t="b">
+      <c r="Y35" s="3"/>
+      <c r="Z35" s="3">
         <f t="shared" si="14"/>
+        <v>-0.35697391304347814</v>
+      </c>
+      <c r="AA35" s="3">
+        <f t="shared" si="15"/>
+        <v>-0.16130769230769215</v>
+      </c>
+    </row>
+    <row r="36" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A36" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B36" s="3">
+        <v>4</v>
+      </c>
+      <c r="C36" s="3">
+        <f t="shared" ref="C36:D36" si="29">B5-$I$27</f>
+        <v>454.86649999999997</v>
+      </c>
+      <c r="D36" s="3">
+        <f t="shared" si="29"/>
+        <v>577.26649999999995</v>
+      </c>
+      <c r="E36" s="3">
+        <f t="shared" si="18"/>
+        <v>74.400000000000006</v>
+      </c>
+      <c r="F36" s="3">
+        <f t="shared" si="19"/>
+        <v>65.599999999999994</v>
+      </c>
+      <c r="G36" s="3">
+        <f t="shared" si="20"/>
+        <v>202.2</v>
+      </c>
+      <c r="H36" s="3">
+        <f t="shared" si="21"/>
+        <v>125.8</v>
+      </c>
+      <c r="I36" s="3">
+        <f t="shared" si="22"/>
+        <v>-4.8664999999999736</v>
+      </c>
+      <c r="J36" s="3">
+        <f t="shared" si="23"/>
+        <v>-14.900000000000006</v>
+      </c>
+      <c r="K36" s="3">
+        <f t="shared" si="24"/>
+        <v>-29.199999999999989</v>
+      </c>
+      <c r="L36" t="str">
+        <f t="shared" si="25"/>
+        <v>TRUE</v>
+      </c>
+      <c r="M36" t="str">
+        <f t="shared" si="26"/>
+        <v>False</v>
+      </c>
+      <c r="N36" t="str">
+        <f t="shared" si="27"/>
+        <v>False</v>
+      </c>
+      <c r="P36" s="2"/>
+      <c r="Q36" s="2"/>
+      <c r="U36" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="V36" s="3">
+        <v>8</v>
+      </c>
+      <c r="W36" s="3" t="b">
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="Z37">
-        <f t="shared" si="11"/>
-        <v>-1.235702702702703</v>
-      </c>
-      <c r="AA37">
-        <f t="shared" si="12"/>
-        <v>0.50460869565217381</v>
-      </c>
-    </row>
-    <row r="38" spans="22:27" x14ac:dyDescent="0.35">
-      <c r="V38">
-        <v>14</v>
-      </c>
-      <c r="W38" t="b">
+      <c r="X36" s="3" t="b">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="X38" t="b">
+      <c r="Y36" s="3"/>
+      <c r="Z36" s="3">
         <f t="shared" si="14"/>
+        <v>-0.22838260869565219</v>
+      </c>
+      <c r="AA36" s="3">
+        <f t="shared" si="15"/>
+        <v>-0.19546153846153813</v>
+      </c>
+    </row>
+    <row r="37" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A37" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B37" s="3">
+        <v>5</v>
+      </c>
+      <c r="C37" s="3">
+        <f t="shared" ref="C37:D37" si="30">B6-$I$27</f>
+        <v>455.36649999999997</v>
+      </c>
+      <c r="D37" s="3">
+        <f t="shared" si="30"/>
+        <v>579.9665</v>
+      </c>
+      <c r="E37" s="3">
+        <f t="shared" si="18"/>
+        <v>74</v>
+      </c>
+      <c r="F37" s="3">
+        <f t="shared" si="19"/>
+        <v>65.400000000000006</v>
+      </c>
+      <c r="G37" s="3">
+        <f t="shared" si="20"/>
+        <v>211.7</v>
+      </c>
+      <c r="H37" s="3">
+        <f t="shared" si="21"/>
+        <v>126.2</v>
+      </c>
+      <c r="I37" s="3">
+        <f t="shared" si="22"/>
+        <v>-5.3664999999999736</v>
+      </c>
+      <c r="J37" s="3">
+        <f t="shared" si="23"/>
+        <v>-14.5</v>
+      </c>
+      <c r="K37" s="3">
+        <f t="shared" si="24"/>
+        <v>-38.699999999999989</v>
+      </c>
+      <c r="L37" t="str">
+        <f t="shared" si="25"/>
+        <v>TRUE</v>
+      </c>
+      <c r="M37" t="str">
+        <f t="shared" si="26"/>
+        <v>False</v>
+      </c>
+      <c r="N37" t="str">
+        <f t="shared" si="27"/>
+        <v>False</v>
+      </c>
+      <c r="U37" t="s">
+        <v>19</v>
+      </c>
+      <c r="V37">
+        <v>9</v>
+      </c>
+      <c r="W37" t="b">
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
-      <c r="Z38">
-        <f t="shared" si="11"/>
+      <c r="X37" t="b">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="Z37">
+        <f t="shared" si="14"/>
+        <v>-1.2418513513513512</v>
+      </c>
+      <c r="AA37">
+        <f t="shared" si="15"/>
+        <v>0.50147204968944104</v>
+      </c>
+    </row>
+    <row r="38" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B38" s="3">
+        <v>6</v>
+      </c>
+      <c r="C38" s="3">
+        <f t="shared" ref="C38:D38" si="31">B7-$I$27</f>
+        <v>455.36649999999997</v>
+      </c>
+      <c r="D38" s="3">
+        <f t="shared" si="31"/>
+        <v>584.9665</v>
+      </c>
+      <c r="E38" s="3">
+        <f t="shared" si="18"/>
+        <v>74.099999999999994</v>
+      </c>
+      <c r="F38" s="3">
+        <f t="shared" si="19"/>
+        <v>66.3</v>
+      </c>
+      <c r="G38" s="3">
+        <f t="shared" si="20"/>
+        <v>204.3</v>
+      </c>
+      <c r="H38" s="3">
+        <f t="shared" si="21"/>
+        <v>125.9</v>
+      </c>
+      <c r="I38" s="3">
+        <f t="shared" si="22"/>
+        <v>-5.3664999999999736</v>
+      </c>
+      <c r="J38" s="3">
+        <f t="shared" si="23"/>
+        <v>-14.599999999999994</v>
+      </c>
+      <c r="K38" s="3">
+        <f t="shared" si="24"/>
+        <v>-31.300000000000011</v>
+      </c>
+      <c r="L38" t="str">
+        <f t="shared" si="25"/>
+        <v>TRUE</v>
+      </c>
+      <c r="M38" t="str">
+        <f t="shared" si="26"/>
+        <v>False</v>
+      </c>
+      <c r="N38" t="str">
+        <f t="shared" si="27"/>
+        <v>False</v>
+      </c>
+      <c r="P38" s="2"/>
+      <c r="Q38" s="2"/>
+      <c r="U38" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="V38" s="3">
+        <v>10</v>
+      </c>
+      <c r="W38" s="3" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="X38" s="3" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="Y38" s="3"/>
+      <c r="Z38" s="3" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="AA38" s="3" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="39" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B39" s="3">
+        <v>7</v>
+      </c>
+      <c r="C39" s="3">
+        <f t="shared" ref="C39:D39" si="32">B8-$I$27</f>
+        <v>429.66650000000004</v>
+      </c>
+      <c r="D39" s="3">
+        <f t="shared" si="32"/>
+        <v>577.86649999999997</v>
+      </c>
+      <c r="E39" s="3">
+        <f t="shared" si="18"/>
+        <v>75.5</v>
+      </c>
+      <c r="F39" s="3">
+        <f t="shared" si="19"/>
+        <v>65.099999999999994</v>
+      </c>
+      <c r="G39" s="3">
+        <f t="shared" si="20"/>
+        <v>223</v>
+      </c>
+      <c r="H39" s="3">
+        <f t="shared" si="21"/>
+        <v>125.5</v>
+      </c>
+      <c r="I39" s="3">
+        <f t="shared" si="22"/>
+        <v>20.333499999999958</v>
+      </c>
+      <c r="J39" s="3">
+        <f t="shared" si="23"/>
+        <v>-16</v>
+      </c>
+      <c r="K39" s="3">
+        <f t="shared" si="24"/>
+        <v>-50</v>
+      </c>
+      <c r="L39" t="str">
+        <f t="shared" si="25"/>
+        <v>False</v>
+      </c>
+      <c r="M39" t="str">
+        <f t="shared" si="26"/>
+        <v>False</v>
+      </c>
+      <c r="N39" t="str">
+        <f t="shared" si="27"/>
+        <v>False</v>
+      </c>
+      <c r="U39" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="V39" s="3">
+        <v>11</v>
+      </c>
+      <c r="W39" s="3" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="X39" s="3" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="Y39" s="3"/>
+      <c r="Z39" s="3" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="AA39" s="3" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="40" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A40" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B40" s="3">
+        <v>8</v>
+      </c>
+      <c r="C40" s="3">
+        <f t="shared" ref="C40:D40" si="33">B9-$I$27</f>
+        <v>443.9665</v>
+      </c>
+      <c r="D40" s="3">
+        <f t="shared" si="33"/>
+        <v>584.9665</v>
+      </c>
+      <c r="E40" s="3">
+        <f t="shared" si="18"/>
+        <v>74.2</v>
+      </c>
+      <c r="F40" s="3">
+        <f t="shared" si="19"/>
+        <v>66.900000000000006</v>
+      </c>
+      <c r="G40" s="3">
+        <f t="shared" si="20"/>
+        <v>211.2</v>
+      </c>
+      <c r="H40" s="3">
+        <f t="shared" si="21"/>
+        <v>116.7</v>
+      </c>
+      <c r="I40" s="3">
+        <f t="shared" si="22"/>
+        <v>6.0335000000000036</v>
+      </c>
+      <c r="J40" s="3">
+        <f t="shared" si="23"/>
+        <v>-14.700000000000003</v>
+      </c>
+      <c r="K40" s="3">
+        <f t="shared" si="24"/>
+        <v>-38.199999999999989</v>
+      </c>
+      <c r="L40" t="str">
+        <f t="shared" si="25"/>
+        <v>TRUE</v>
+      </c>
+      <c r="M40" t="str">
+        <f t="shared" si="26"/>
+        <v>False</v>
+      </c>
+      <c r="N40" t="str">
+        <f t="shared" si="27"/>
+        <v>False</v>
+      </c>
+      <c r="P40" s="2"/>
+      <c r="Q40" s="2"/>
+      <c r="U40" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="V40" s="3">
+        <v>12</v>
+      </c>
+      <c r="W40" s="3" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="X40" s="3" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="Y40" s="3"/>
+      <c r="Z40" s="3" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="AA40" s="3" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="41" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>19</v>
+      </c>
+      <c r="B41">
+        <v>9</v>
+      </c>
+      <c r="C41">
+        <f t="shared" ref="C41:D41" si="34">B10-$I$27</f>
+        <v>284.36649999999997</v>
+      </c>
+      <c r="D41">
+        <f t="shared" si="34"/>
+        <v>359.56650000000002</v>
+      </c>
+      <c r="E41">
+        <f t="shared" si="18"/>
+        <v>74.8</v>
+      </c>
+      <c r="F41">
+        <f t="shared" si="19"/>
+        <v>70.900000000000006</v>
+      </c>
+      <c r="G41">
+        <f t="shared" si="20"/>
+        <v>275.5</v>
+      </c>
+      <c r="H41">
+        <f t="shared" si="21"/>
+        <v>113</v>
+      </c>
+      <c r="I41">
+        <f t="shared" si="22"/>
+        <v>0.63350000000002638</v>
+      </c>
+      <c r="J41">
+        <f t="shared" si="23"/>
+        <v>-14.799999999999997</v>
+      </c>
+      <c r="K41">
+        <f t="shared" si="24"/>
+        <v>-29.5</v>
+      </c>
+      <c r="L41" t="str">
+        <f t="shared" si="25"/>
+        <v>TRUE</v>
+      </c>
+      <c r="M41" t="str">
+        <f t="shared" si="26"/>
+        <v>False</v>
+      </c>
+      <c r="N41" t="str">
+        <f t="shared" si="27"/>
+        <v>False</v>
+      </c>
+      <c r="U41" t="s">
+        <v>19</v>
+      </c>
+      <c r="V41">
+        <v>13</v>
+      </c>
+      <c r="W41" t="b">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="X41" t="b">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="Z41">
+        <f t="shared" si="14"/>
+        <v>-1.235702702702703</v>
+      </c>
+      <c r="AA41">
+        <f t="shared" si="15"/>
+        <v>0.50460869565217381</v>
+      </c>
+    </row>
+    <row r="42" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A42" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B42" s="3">
+        <v>10</v>
+      </c>
+      <c r="C42" s="3">
+        <f t="shared" ref="C42:D42" si="35">B11-$I$27</f>
+        <v>283.56650000000002</v>
+      </c>
+      <c r="D42" s="3">
+        <f t="shared" si="35"/>
+        <v>359.06650000000002</v>
+      </c>
+      <c r="E42" s="3">
+        <f t="shared" si="18"/>
+        <v>74.3</v>
+      </c>
+      <c r="F42" s="3">
+        <f t="shared" si="19"/>
+        <v>69.599999999999994</v>
+      </c>
+      <c r="G42" s="3">
+        <f t="shared" si="20"/>
+        <v>275.5</v>
+      </c>
+      <c r="H42" s="3">
+        <f t="shared" si="21"/>
+        <v>149.5</v>
+      </c>
+      <c r="I42" s="3" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="J42" s="3" t="str">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="K42" s="3" t="str">
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="L42" t="e">
+        <f t="shared" si="25"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M42" t="e">
+        <f t="shared" si="26"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N42" t="e">
+        <f t="shared" si="27"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="U42" t="s">
+        <v>19</v>
+      </c>
+      <c r="V42">
+        <v>14</v>
+      </c>
+      <c r="W42" t="b">
+        <f t="shared" si="12"/>
+        <v>0</v>
+      </c>
+      <c r="X42" t="b">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="Z42">
+        <f t="shared" si="14"/>
         <v>-1.2435540540540542</v>
       </c>
-      <c r="AA38">
+      <c r="AA42">
+        <f t="shared" si="15"/>
+        <v>0.50519254658385082</v>
+      </c>
+    </row>
+    <row r="43" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A43" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B43" s="3">
+        <v>11</v>
+      </c>
+      <c r="C43" s="3">
+        <f t="shared" ref="C43:D43" si="36">B12-$I$27</f>
+        <v>283.56650000000002</v>
+      </c>
+      <c r="D43" s="3">
+        <f t="shared" si="36"/>
+        <v>358.9665</v>
+      </c>
+      <c r="E43" s="3">
+        <f t="shared" si="18"/>
+        <v>74</v>
+      </c>
+      <c r="F43" s="3">
+        <f t="shared" si="19"/>
+        <v>70.5</v>
+      </c>
+      <c r="G43" s="3">
+        <f t="shared" si="20"/>
+        <v>275.39999999999998</v>
+      </c>
+      <c r="H43" s="3">
+        <f t="shared" si="21"/>
+        <v>160</v>
+      </c>
+      <c r="I43" s="3" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="J43" s="3" t="str">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="K43" s="3" t="str">
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="L43" t="e">
+        <f t="shared" si="25"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M43" t="e">
+        <f t="shared" si="26"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N43" t="e">
+        <f t="shared" si="27"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="U43" t="s">
+        <v>18</v>
+      </c>
+      <c r="V43">
+        <v>15</v>
+      </c>
+      <c r="W43" t="b">
         <f t="shared" si="12"/>
-        <v>0.50519254658385082</v>
-      </c>
-    </row>
-    <row r="39" spans="22:27" x14ac:dyDescent="0.35">
-      <c r="V39">
-        <v>15</v>
-      </c>
-      <c r="W39" t="b">
+        <v>1</v>
+      </c>
+      <c r="X43" t="b">
         <f t="shared" si="13"/>
         <v>1</v>
       </c>
-      <c r="X39" t="b">
+      <c r="Z43">
         <f t="shared" si="14"/>
+        <v>-5.3058823529410493E-3</v>
+      </c>
+      <c r="AA43">
+        <f t="shared" si="15"/>
+        <v>2.4968000000000101E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A44" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B44" s="3">
+        <v>12</v>
+      </c>
+      <c r="C44" s="3">
+        <f t="shared" ref="C44:D44" si="37">B13-$I$27</f>
+        <v>284.16649999999998</v>
+      </c>
+      <c r="D44" s="3">
+        <f t="shared" si="37"/>
+        <v>359.16650000000004</v>
+      </c>
+      <c r="E44" s="3">
+        <f t="shared" si="18"/>
+        <v>73.599999999999994</v>
+      </c>
+      <c r="F44" s="3">
+        <f t="shared" si="19"/>
+        <v>69.900000000000006</v>
+      </c>
+      <c r="G44" s="3">
+        <f t="shared" si="20"/>
+        <v>275</v>
+      </c>
+      <c r="H44" s="3">
+        <f t="shared" si="21"/>
+        <v>162</v>
+      </c>
+      <c r="I44" s="3" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="J44" s="3" t="str">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="K44" s="3" t="str">
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="L44" t="e">
+        <f t="shared" si="25"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M44" t="e">
+        <f t="shared" si="26"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N44" t="e">
+        <f t="shared" si="27"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="U44" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="V44" s="3">
+        <v>16</v>
+      </c>
+      <c r="W44" s="3" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="X44" s="3" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="Y44" s="3"/>
+      <c r="Z44" s="3" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="AA44" s="3" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="45" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>19</v>
+      </c>
+      <c r="B45">
+        <v>13</v>
+      </c>
+      <c r="C45">
+        <f t="shared" ref="C45:D45" si="38">B14-$I$27</f>
+        <v>284.16649999999998</v>
+      </c>
+      <c r="D45">
+        <f t="shared" si="38"/>
+        <v>359.16650000000004</v>
+      </c>
+      <c r="E45">
+        <f t="shared" si="18"/>
+        <v>74.099999999999994</v>
+      </c>
+      <c r="F45">
+        <f t="shared" si="19"/>
+        <v>69.900000000000006</v>
+      </c>
+      <c r="G45">
+        <f t="shared" si="20"/>
+        <v>274.5</v>
+      </c>
+      <c r="H45">
+        <f t="shared" si="21"/>
+        <v>112.2</v>
+      </c>
+      <c r="I45">
+        <f t="shared" si="22"/>
+        <v>0.83350000000001501</v>
+      </c>
+      <c r="J45">
+        <f t="shared" si="23"/>
+        <v>-14.099999999999994</v>
+      </c>
+      <c r="K45">
+        <f t="shared" si="24"/>
+        <v>-28.5</v>
+      </c>
+      <c r="L45" t="str">
+        <f t="shared" si="25"/>
+        <v>TRUE</v>
+      </c>
+      <c r="M45" t="str">
+        <f t="shared" si="26"/>
+        <v>False</v>
+      </c>
+      <c r="N45" t="str">
+        <f t="shared" si="27"/>
+        <v>False</v>
+      </c>
+      <c r="U45" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="V45" s="3">
+        <v>17</v>
+      </c>
+      <c r="W45" s="3" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="X45" s="3" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="Y45" s="3"/>
+      <c r="Z45" s="3" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="AA45" s="3" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="46" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>19</v>
+      </c>
+      <c r="B46">
+        <v>14</v>
+      </c>
+      <c r="C46">
+        <f t="shared" ref="C46:D46" si="39">B15-$I$27</f>
+        <v>284.16649999999998</v>
+      </c>
+      <c r="D46">
+        <f t="shared" si="39"/>
+        <v>359.16650000000004</v>
+      </c>
+      <c r="E46">
+        <f t="shared" si="18"/>
+        <v>74.099999999999994</v>
+      </c>
+      <c r="F46">
+        <f t="shared" si="19"/>
+        <v>69.900000000000006</v>
+      </c>
+      <c r="G46">
+        <f t="shared" si="20"/>
+        <v>275</v>
+      </c>
+      <c r="H46">
+        <f t="shared" si="21"/>
+        <v>112.3</v>
+      </c>
+      <c r="I46">
+        <f t="shared" si="22"/>
+        <v>0.83350000000001501</v>
+      </c>
+      <c r="J46">
+        <f t="shared" si="23"/>
+        <v>-14.099999999999994</v>
+      </c>
+      <c r="K46">
+        <f t="shared" si="24"/>
+        <v>-29</v>
+      </c>
+      <c r="L46" t="str">
+        <f t="shared" si="25"/>
+        <v>TRUE</v>
+      </c>
+      <c r="M46" t="str">
+        <f t="shared" si="26"/>
+        <v>False</v>
+      </c>
+      <c r="N46" t="str">
+        <f t="shared" si="27"/>
+        <v>False</v>
+      </c>
+      <c r="U46" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="V46" s="3">
+        <v>18</v>
+      </c>
+      <c r="W46" s="3" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="X46" s="3" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+      <c r="Y46" s="3"/>
+      <c r="Z46" s="3" t="str">
+        <f t="shared" si="14"/>
+        <v/>
+      </c>
+      <c r="AA46" s="3" t="str">
+        <f t="shared" si="15"/>
+        <v/>
+      </c>
+    </row>
+    <row r="47" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>18</v>
+      </c>
+      <c r="B47">
+        <v>15</v>
+      </c>
+      <c r="C47">
+        <f t="shared" ref="C47:D47" si="40">B16-$I$27</f>
+        <v>410.16650000000004</v>
+      </c>
+      <c r="D47">
+        <f t="shared" si="40"/>
+        <v>581.26649999999995</v>
+      </c>
+      <c r="E47">
+        <f t="shared" si="18"/>
+        <v>75.099999999999994</v>
+      </c>
+      <c r="F47">
+        <f t="shared" si="19"/>
+        <v>66.7</v>
+      </c>
+      <c r="G47">
+        <f t="shared" si="20"/>
+        <v>349.7</v>
+      </c>
+      <c r="H47">
+        <f t="shared" si="21"/>
+        <v>227.5</v>
+      </c>
+      <c r="I47">
+        <f t="shared" si="22"/>
+        <v>-0.16650000000004184</v>
+      </c>
+      <c r="J47">
+        <f t="shared" si="23"/>
+        <v>-14.599999999999994</v>
+      </c>
+      <c r="K47">
+        <f t="shared" si="24"/>
+        <v>-29.699999999999989</v>
+      </c>
+      <c r="L47" t="str">
+        <f t="shared" si="25"/>
+        <v>TRUE</v>
+      </c>
+      <c r="M47" t="str">
+        <f t="shared" si="26"/>
+        <v>False</v>
+      </c>
+      <c r="N47" t="str">
+        <f t="shared" si="27"/>
+        <v>False</v>
+      </c>
+      <c r="U47" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="V47" s="3">
+        <v>19</v>
+      </c>
+      <c r="W47" s="3" t="b">
+        <f t="shared" si="12"/>
         <v>1</v>
       </c>
-      <c r="Z39">
-        <f t="shared" si="11"/>
-        <v>-5.3058823529410493E-3</v>
-      </c>
-      <c r="AA39">
+      <c r="X47" s="3" t="b">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="Y47" s="3"/>
+      <c r="Z47" s="3">
+        <f t="shared" si="14"/>
+        <v>-6.2411764705883055E-3</v>
+      </c>
+      <c r="AA47" s="3">
+        <f t="shared" si="15"/>
+        <v>2.4391999999999969E-2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A48" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B48" s="3">
+        <v>16</v>
+      </c>
+      <c r="C48" s="3">
+        <f t="shared" ref="C48:D48" si="41">B17-$I$27</f>
+        <v>409.9665</v>
+      </c>
+      <c r="D48" s="3">
+        <f t="shared" si="41"/>
+        <v>572.76649999999995</v>
+      </c>
+      <c r="E48" s="3">
+        <f t="shared" si="18"/>
+        <v>104.80000000000001</v>
+      </c>
+      <c r="F48" s="3">
+        <f t="shared" si="19"/>
+        <v>69.3</v>
+      </c>
+      <c r="G48" s="3">
+        <f t="shared" si="20"/>
+        <v>298.2</v>
+      </c>
+      <c r="H48" s="3">
+        <f t="shared" si="21"/>
+        <v>205.6</v>
+      </c>
+      <c r="I48" s="3" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="J48" s="3" t="str">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="K48" s="3" t="str">
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="L48" t="e">
+        <f t="shared" si="25"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M48" t="e">
+        <f t="shared" si="26"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N48" t="e">
+        <f t="shared" si="27"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="U48" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="V48" s="3">
+        <v>20</v>
+      </c>
+      <c r="W48" s="3" t="b">
         <f t="shared" si="12"/>
-        <v>2.4968000000000101E-2</v>
-      </c>
-    </row>
-    <row r="40" spans="22:27" x14ac:dyDescent="0.35">
-      <c r="V40">
-        <v>16</v>
-      </c>
-      <c r="W40" t="str">
+        <v>1</v>
+      </c>
+      <c r="X48" s="3" t="b">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="X40" t="str">
+        <v>1</v>
+      </c>
+      <c r="Y48" s="3"/>
+      <c r="Z48" s="3">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="Z40" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="AA40" t="str">
+        <v>-3.9882352941176258E-3</v>
+      </c>
+      <c r="AA48" s="3">
+        <f t="shared" si="15"/>
+        <v>2.5887999999999911E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A49" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B49" s="3">
+        <v>17</v>
+      </c>
+      <c r="C49" s="3">
+        <f t="shared" ref="C49:D49" si="42">B18-$I$27</f>
+        <v>409.66650000000004</v>
+      </c>
+      <c r="D49" s="3">
+        <f t="shared" si="42"/>
+        <v>571.9665</v>
+      </c>
+      <c r="E49" s="3">
+        <f t="shared" si="18"/>
+        <v>103.6</v>
+      </c>
+      <c r="F49" s="3">
+        <f t="shared" si="19"/>
+        <v>69.5</v>
+      </c>
+      <c r="G49" s="3">
+        <f t="shared" si="20"/>
+        <v>298.7</v>
+      </c>
+      <c r="H49" s="3">
+        <f t="shared" si="21"/>
+        <v>205.1</v>
+      </c>
+      <c r="I49" s="3" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="J49" s="3" t="str">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="K49" s="3" t="str">
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="L49" t="e">
+        <f t="shared" si="25"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M49" t="e">
+        <f t="shared" si="26"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N49" t="e">
+        <f t="shared" si="27"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="U49" t="s">
+        <v>17</v>
+      </c>
+      <c r="V49" t="s">
+        <v>28</v>
+      </c>
+      <c r="W49" t="b">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-    </row>
-    <row r="41" spans="22:27" x14ac:dyDescent="0.35">
-      <c r="V41">
+        <v>1</v>
+      </c>
+      <c r="X49" t="b">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="Z49">
+        <f t="shared" si="14"/>
+        <v>2.8278260869565086E-2</v>
+      </c>
+      <c r="AA49">
+        <f t="shared" si="15"/>
+        <v>3.606410256410264E-2</v>
+      </c>
+    </row>
+    <row r="50" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A50" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B50" s="3">
+        <v>18</v>
+      </c>
+      <c r="C50" s="3">
+        <f t="shared" ref="C50:D50" si="43">B19-$I$27</f>
+        <v>409.56650000000002</v>
+      </c>
+      <c r="D50" s="3">
+        <f t="shared" si="43"/>
+        <v>572.9665</v>
+      </c>
+      <c r="E50" s="3">
+        <f t="shared" si="18"/>
+        <v>104.6</v>
+      </c>
+      <c r="F50" s="3">
+        <f t="shared" si="19"/>
+        <v>69.5</v>
+      </c>
+      <c r="G50" s="3">
+        <f t="shared" si="20"/>
+        <v>298.7</v>
+      </c>
+      <c r="H50" s="3">
+        <f t="shared" si="21"/>
+        <v>205.2</v>
+      </c>
+      <c r="I50" s="3" t="str">
+        <f t="shared" si="22"/>
+        <v/>
+      </c>
+      <c r="J50" s="3" t="str">
+        <f t="shared" si="23"/>
+        <v/>
+      </c>
+      <c r="K50" s="3" t="str">
+        <f t="shared" si="24"/>
+        <v/>
+      </c>
+      <c r="L50" t="e">
+        <f t="shared" si="25"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="M50" t="e">
+        <f t="shared" si="26"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="N50" t="e">
+        <f t="shared" si="27"/>
+        <v>#VALUE!</v>
+      </c>
+      <c r="U50" t="s">
         <v>17</v>
       </c>
-      <c r="W41" t="str">
+      <c r="V50" t="s">
+        <v>29</v>
+      </c>
+      <c r="W50" t="b">
+        <f t="shared" si="12"/>
+        <v>1</v>
+      </c>
+      <c r="X50" t="b">
         <f t="shared" si="13"/>
-        <v/>
-      </c>
-      <c r="X41" t="str">
+        <v>1</v>
+      </c>
+      <c r="Z50">
         <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="Z41" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="AA41" t="str">
+        <v>1.3930434782608692E-2</v>
+      </c>
+      <c r="AA50">
+        <f t="shared" si="15"/>
+        <v>4.7230769230769187E-2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A51" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B51" s="3">
+        <v>19</v>
+      </c>
+      <c r="C51" s="3">
+        <f t="shared" ref="C51:D51" si="44">B20-$I$27</f>
+        <v>409.16650000000004</v>
+      </c>
+      <c r="D51" s="3">
+        <f t="shared" si="44"/>
+        <v>579.76649999999995</v>
+      </c>
+      <c r="E51" s="3">
+        <f t="shared" si="18"/>
+        <v>76</v>
+      </c>
+      <c r="F51" s="3">
+        <f t="shared" si="19"/>
+        <v>65.099999999999994</v>
+      </c>
+      <c r="G51" s="3">
+        <f t="shared" si="20"/>
+        <v>348.9</v>
+      </c>
+      <c r="H51" s="3">
+        <f t="shared" si="21"/>
+        <v>227.6</v>
+      </c>
+      <c r="I51" s="3">
+        <f t="shared" si="22"/>
+        <v>0.83349999999995816</v>
+      </c>
+      <c r="J51" s="3">
+        <f t="shared" si="23"/>
+        <v>-15.5</v>
+      </c>
+      <c r="K51" s="3">
+        <f t="shared" si="24"/>
+        <v>-28.899999999999977</v>
+      </c>
+      <c r="L51" t="str">
+        <f t="shared" si="25"/>
+        <v>TRUE</v>
+      </c>
+      <c r="M51" t="str">
+        <f t="shared" si="26"/>
+        <v>False</v>
+      </c>
+      <c r="N51" t="str">
+        <f t="shared" si="27"/>
+        <v>False</v>
+      </c>
+      <c r="U51" t="s">
+        <v>17</v>
+      </c>
+      <c r="V51" t="s">
+        <v>30</v>
+      </c>
+      <c r="W51" t="b">
         <f t="shared" si="12"/>
-        <v/>
-      </c>
-    </row>
-    <row r="42" spans="22:27" x14ac:dyDescent="0.35">
-      <c r="V42">
+        <v>1</v>
+      </c>
+      <c r="X51" t="b">
+        <f t="shared" si="13"/>
+        <v>0</v>
+      </c>
+      <c r="Z51">
+        <f t="shared" si="14"/>
+        <v>2.9756521739130459E-2</v>
+      </c>
+      <c r="AA51">
+        <f t="shared" si="15"/>
+        <v>6.9089743589743402E-2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A52" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="W42" t="str">
+      <c r="B52" s="3">
+        <v>20</v>
+      </c>
+      <c r="C52" s="3">
+        <f t="shared" ref="C52:D52" si="45">B21-$I$27</f>
+        <v>409.86649999999997</v>
+      </c>
+      <c r="D52" s="3">
+        <f t="shared" si="45"/>
+        <v>580.86649999999997</v>
+      </c>
+      <c r="E52" s="3">
+        <f t="shared" si="18"/>
+        <v>75</v>
+      </c>
+      <c r="F52" s="3">
+        <f t="shared" si="19"/>
+        <v>67.400000000000006</v>
+      </c>
+      <c r="G52" s="3">
+        <f t="shared" si="20"/>
+        <v>349.3</v>
+      </c>
+      <c r="H52" s="3">
+        <f t="shared" si="21"/>
+        <v>227.8</v>
+      </c>
+      <c r="I52" s="3">
+        <f t="shared" si="22"/>
+        <v>0.13350000000002638</v>
+      </c>
+      <c r="J52" s="3">
+        <f t="shared" si="23"/>
+        <v>-14.5</v>
+      </c>
+      <c r="K52" s="3">
+        <f t="shared" si="24"/>
+        <v>-29.300000000000011</v>
+      </c>
+      <c r="L52" t="str">
+        <f t="shared" si="25"/>
+        <v>TRUE</v>
+      </c>
+      <c r="M52" t="str">
+        <f t="shared" si="26"/>
+        <v>False</v>
+      </c>
+      <c r="N52" t="str">
+        <f t="shared" si="27"/>
+        <v>False</v>
+      </c>
+      <c r="W52" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="X52" t="str">
         <f t="shared" si="13"/>
         <v/>
       </c>
-      <c r="X42" t="str">
-        <f t="shared" si="14"/>
-        <v/>
-      </c>
-      <c r="Z42" t="str">
-        <f t="shared" si="11"/>
-        <v/>
-      </c>
-      <c r="AA42" t="str">
-        <f t="shared" si="12"/>
-        <v/>
-      </c>
-    </row>
-    <row r="43" spans="22:27" x14ac:dyDescent="0.35">
-      <c r="V43">
-        <v>19</v>
-      </c>
-      <c r="W43" t="b">
-        <f>IF(N20="Sblob",
-    AND(S20 &gt;= O$23*(1-0.05), S20 &lt;= O$23*(1+0.05)),
-IF(N20="Lblob",
-    AND(S20 &gt;= O$24*(1-0.05), S20 &lt;= O$24*(1+0.05)),
-IF(N20="Rec",
-    AND(S20 &gt;= O$25*(1-0.05), S20 &lt;= O$25*(1+0.05)),
+    </row>
+    <row r="53" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>17</v>
+      </c>
+      <c r="C53">
+        <f t="shared" ref="C53:D53" si="46">B22-$I$27</f>
+        <v>454.16650000000004</v>
+      </c>
+      <c r="D53">
+        <f t="shared" si="46"/>
+        <v>565.76649999999995</v>
+      </c>
+      <c r="E53">
+        <f t="shared" ref="E53:E55" si="47">ABS(J$27+D22)</f>
+        <v>73.2</v>
+      </c>
+      <c r="F53">
+        <f t="shared" ref="F53:F55" si="48">ABS(J$27+E22)</f>
+        <v>66.3</v>
+      </c>
+      <c r="G53">
+        <f t="shared" ref="G53:G55" si="49">ABS(F22-K$27)</f>
+        <v>199.5</v>
+      </c>
+      <c r="H53">
+        <f t="shared" ref="H53:H55" si="50">ABS(G22-K$27)</f>
+        <v>124.1</v>
+      </c>
+      <c r="I53">
+        <f t="shared" ref="I53:I55" si="51">IF($A53="Sblob", C$28-C53,
+   IF($A53="Lblob", C$29-C53,
+   IF($A53="Rec", C$30-C53,
 ""
 )))</f>
-        <v>1</v>
-      </c>
-      <c r="X43" t="b">
-        <f>IF(N20="Sblob",
-    AND(T20 &gt;= Q$23*(1-0.05), T20 &lt;= Q$23*(1+0.05)),
-IF(N20="Lblob",
-    AND(T20 &gt;= Q$24*(1-0.05), T20 &lt;= Q$24*(1+0.05)),
-IF(N20="Rec",
-    AND(T20 &gt;= Q$25*(1-0.05), T20 &lt;= Q$25*(1+0.05)),
+        <v>-4.1665000000000418</v>
+      </c>
+      <c r="J53">
+        <f t="shared" ref="J53:J55" si="52">IF($A53="Sblob", E$28-E53,
+   IF($A53="Lblob", E$29-E53,
+   IF($A53="Rec", E$30-E53,
 ""
 )))</f>
-        <v>1</v>
-      </c>
-      <c r="Z43">
-        <f t="shared" si="11"/>
-        <v>-6.2411764705883055E-3</v>
-      </c>
-      <c r="AA43">
-        <f t="shared" si="12"/>
-        <v>2.4391999999999969E-2</v>
-      </c>
-    </row>
-    <row r="44" spans="22:27" x14ac:dyDescent="0.35">
-      <c r="V44">
-        <v>20</v>
-      </c>
-      <c r="W44" t="b">
-        <f t="shared" ref="W44:W45" si="15">IF(N21="Sblob",
-    AND(S21 &gt;= O$23*(1-0.05), S21 &lt;= O$23*(1+0.05)),
-IF(N21="Lblob",
-    AND(S21 &gt;= O$24*(1-0.05), S21 &lt;= O$24*(1+0.05)),
-IF(N21="Rec",
-    AND(S21 &gt;= O$25*(1-0.05), S21 &lt;= O$25*(1+0.05)),
+        <v>-13.700000000000003</v>
+      </c>
+      <c r="K53">
+        <f t="shared" ref="K53:K55" si="53">IF($A53="Sblob", G$28-G53,
+   IF($A53="Lblob", G$29-G53,
+   IF($A53="Rec", G$30-G53,
 ""
 )))</f>
-        <v>1</v>
-      </c>
-      <c r="X44" t="b">
-        <f t="shared" ref="X44:X45" si="16">IF(N21="Sblob",
-    AND(T21 &gt;= Q$23*(1-0.05), T21 &lt;= Q$23*(1+0.05)),
-IF(N21="Lblob",
-    AND(T21 &gt;= Q$24*(1-0.05), T21 &lt;= Q$24*(1+0.05)),
-IF(N21="Rec",
-    AND(T21 &gt;= Q$25*(1-0.05), T21 &lt;= Q$25*(1+0.05)),
+        <v>-26.5</v>
+      </c>
+      <c r="L53" t="str">
+        <f t="shared" si="25"/>
+        <v>TRUE</v>
+      </c>
+      <c r="M53" t="str">
+        <f t="shared" si="26"/>
+        <v>False</v>
+      </c>
+      <c r="N53" t="str">
+        <f t="shared" si="27"/>
+        <v>False</v>
+      </c>
+      <c r="W53" t="str">
+        <f t="shared" si="12"/>
+        <v/>
+      </c>
+      <c r="X53" t="str">
+        <f t="shared" si="13"/>
+        <v/>
+      </c>
+    </row>
+    <row r="54" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>17</v>
+      </c>
+      <c r="C54">
+        <f t="shared" ref="C54:D54" si="54">B23-$I$27</f>
+        <v>453.16650000000004</v>
+      </c>
+      <c r="D54">
+        <f t="shared" si="54"/>
+        <v>566.4665</v>
+      </c>
+      <c r="E54">
+        <f t="shared" si="47"/>
+        <v>74.099999999999994</v>
+      </c>
+      <c r="F54">
+        <f t="shared" si="48"/>
+        <v>67.099999999999994</v>
+      </c>
+      <c r="G54">
+        <f t="shared" si="49"/>
+        <v>199</v>
+      </c>
+      <c r="H54">
+        <f t="shared" si="50"/>
+        <v>124</v>
+      </c>
+      <c r="I54">
+        <f t="shared" si="51"/>
+        <v>-3.1665000000000418</v>
+      </c>
+      <c r="J54">
+        <f t="shared" si="52"/>
+        <v>-14.599999999999994</v>
+      </c>
+      <c r="K54">
+        <f t="shared" si="53"/>
+        <v>-26</v>
+      </c>
+      <c r="L54" t="str">
+        <f t="shared" si="25"/>
+        <v>TRUE</v>
+      </c>
+      <c r="M54" t="str">
+        <f t="shared" si="26"/>
+        <v>False</v>
+      </c>
+      <c r="N54" t="str">
+        <f t="shared" si="27"/>
+        <v>False</v>
+      </c>
+      <c r="W54" t="str">
+        <f t="shared" ref="W50:W56" si="55">IF(N31="Sblob",
+    AND(S31 &gt;= O$23*(1-0.05), S31 &lt;= O$23*(1+0.05)),
+IF(N31="Lblob",
+    AND(S31 &gt;= O$24*(1-0.05), S31 &lt;= O$24*(1+0.05)),
+IF(N31="Rec",
+    AND(S31 &gt;= O$25*(1-0.05), S31 &lt;= O$25*(1+0.05)),
 ""
 )))</f>
-        <v>1</v>
-      </c>
-      <c r="Z44">
-        <f t="shared" si="11"/>
-        <v>-3.9882352941176258E-3</v>
-      </c>
-      <c r="AA44">
-        <f t="shared" si="12"/>
-        <v>2.5887999999999911E-2</v>
-      </c>
-    </row>
-    <row r="49" spans="23:24" x14ac:dyDescent="0.35">
-      <c r="W49" t="str">
-        <f>IF(N26="Sblob",
-    AND(S26 &gt;= O$23*(1-0.05), S26 &lt;= O$23*(1+0.05)),
-IF(N26="Lblob",
-    AND(S26 &gt;= O$24*(1-0.05), S26 &lt;= O$24*(1+0.05)),
-IF(N26="Rec",
-    AND(S26 &gt;= O$25*(1-0.05), S26 &lt;= O$25*(1+0.05)),
+        <v/>
+      </c>
+      <c r="X54" t="str">
+        <f t="shared" ref="X50:X56" si="56">IF(N31="Sblob",
+    AND(T31 &gt;= Q$23*(1-0.05), T31 &lt;= Q$23*(1+0.05)),
+IF(N31="Lblob",
+    AND(T31 &gt;= Q$24*(1-0.05), T31 &lt;= Q$24*(1+0.05)),
+IF(N31="Rec",
+    AND(T31 &gt;= Q$25*(1-0.05), T31 &lt;= Q$25*(1+0.05)),
 ""
 )))</f>
         <v/>
       </c>
-      <c r="X49" t="str">
-        <f>IF(N26="Sblob",
-    AND(T26 &gt;= Q$23*(1-0.05), T26 &lt;= Q$23*(1+0.05)),
-IF(N26="Lblob",
-    AND(T26 &gt;= Q$24*(1-0.05), T26 &lt;= Q$24*(1+0.05)),
-IF(N26="Rec",
-    AND(T26 &gt;= Q$25*(1-0.05), T26 &lt;= Q$25*(1+0.05)),
-""
-)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50" spans="23:24" x14ac:dyDescent="0.35">
-      <c r="W50" t="str">
-        <f t="shared" ref="W50:W56" si="17">IF(N27="Sblob",
-    AND(S27 &gt;= O$23*(1-0.05), S27 &lt;= O$23*(1+0.05)),
-IF(N27="Lblob",
-    AND(S27 &gt;= O$24*(1-0.05), S27 &lt;= O$24*(1+0.05)),
-IF(N27="Rec",
-    AND(S27 &gt;= O$25*(1-0.05), S27 &lt;= O$25*(1+0.05)),
-""
-)))</f>
-        <v/>
-      </c>
-      <c r="X50" t="str">
-        <f t="shared" ref="X50:X56" si="18">IF(N27="Sblob",
-    AND(T27 &gt;= Q$23*(1-0.05), T27 &lt;= Q$23*(1+0.05)),
-IF(N27="Lblob",
-    AND(T27 &gt;= Q$24*(1-0.05), T27 &lt;= Q$24*(1+0.05)),
-IF(N27="Rec",
-    AND(T27 &gt;= Q$25*(1-0.05), T27 &lt;= Q$25*(1+0.05)),
-""
-)))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51" spans="23:24" x14ac:dyDescent="0.35">
-      <c r="W51" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="X51" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="52" spans="23:24" x14ac:dyDescent="0.35">
-      <c r="W52" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="X52" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="53" spans="23:24" x14ac:dyDescent="0.35">
-      <c r="W53" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="X53" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="54" spans="23:24" x14ac:dyDescent="0.35">
-      <c r="W54" t="str">
-        <f t="shared" si="17"/>
-        <v/>
-      </c>
-      <c r="X54" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="55" spans="23:24" x14ac:dyDescent="0.35">
+    </row>
+    <row r="55" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>17</v>
+      </c>
+      <c r="C55">
+        <f t="shared" ref="C55:D55" si="57">B24-$I$27</f>
+        <v>454.06650000000002</v>
+      </c>
+      <c r="D55">
+        <f t="shared" si="57"/>
+        <v>565.36649999999997</v>
+      </c>
+      <c r="E55">
+        <f t="shared" si="47"/>
+        <v>74</v>
+      </c>
+      <c r="F55">
+        <f t="shared" si="48"/>
+        <v>67.2</v>
+      </c>
+      <c r="G55">
+        <f t="shared" si="49"/>
+        <v>199</v>
+      </c>
+      <c r="H55">
+        <f t="shared" si="50"/>
+        <v>126</v>
+      </c>
+      <c r="I55">
+        <f t="shared" si="51"/>
+        <v>-4.0665000000000191</v>
+      </c>
+      <c r="J55">
+        <f t="shared" si="52"/>
+        <v>-14.5</v>
+      </c>
+      <c r="K55">
+        <f t="shared" si="53"/>
+        <v>-26</v>
+      </c>
+      <c r="L55" t="str">
+        <f t="shared" si="25"/>
+        <v>TRUE</v>
+      </c>
+      <c r="M55" t="str">
+        <f t="shared" si="26"/>
+        <v>False</v>
+      </c>
+      <c r="N55" t="str">
+        <f t="shared" si="27"/>
+        <v>False</v>
+      </c>
       <c r="W55" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="X55" t="str">
-        <f t="shared" si="18"/>
-        <v/>
-      </c>
-    </row>
-    <row r="56" spans="23:24" x14ac:dyDescent="0.35">
+        <f t="shared" si="56"/>
+        <v/>
+      </c>
+    </row>
+    <row r="56" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="I56" cm="1">
+        <f t="array" ref="I56">AVERAGE(ABS(I33:I34),ABS(I41),ABS(I45:I47),ABS(I53:I55))</f>
+        <v>1.6110555555555821</v>
+      </c>
+      <c r="J56" cm="1">
+        <f t="array" ref="J56">AVERAGE(ABS(J33:J34),ABS(J41),ABS(J45:J47),ABS(J53:J55))</f>
+        <v>14.444444444444445</v>
+      </c>
+      <c r="K56" cm="1">
+        <f t="array" ref="K56">AVERAGE(ABS(K33:K34),ABS(K41),ABS(K45:K47),ABS(K53:K55))</f>
+        <v>28.266666666666669</v>
+      </c>
+      <c r="L56" t="str">
+        <f t="shared" si="25"/>
+        <v>TRUE</v>
+      </c>
+      <c r="M56" t="str">
+        <f t="shared" si="26"/>
+        <v>False</v>
+      </c>
+      <c r="N56" t="str">
+        <f t="shared" si="27"/>
+        <v>False</v>
+      </c>
       <c r="W56" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="55"/>
         <v/>
       </c>
       <c r="X56" t="str">
-        <f t="shared" si="18"/>
-        <v/>
+        <f t="shared" si="56"/>
+        <v/>
+      </c>
+    </row>
+    <row r="59" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>18</v>
+      </c>
+      <c r="B59">
+        <v>15</v>
+      </c>
+      <c r="C59">
+        <v>410.16650000000004</v>
+      </c>
+      <c r="D59">
+        <v>581.26649999999995</v>
+      </c>
+      <c r="E59">
+        <v>75.099999999999994</v>
+      </c>
+      <c r="F59">
+        <v>66.7</v>
+      </c>
+      <c r="G59">
+        <v>349.7</v>
+      </c>
+      <c r="H59">
+        <v>227.5</v>
+      </c>
+      <c r="I59">
+        <v>-0.16650000000004184</v>
+      </c>
+      <c r="J59">
+        <v>-14.599999999999994</v>
+      </c>
+      <c r="K59">
+        <v>-29.699999999999989</v>
+      </c>
+    </row>
+    <row r="61" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>18</v>
+      </c>
+      <c r="B61">
+        <v>1</v>
+      </c>
+      <c r="C61">
+        <v>410.06650000000002</v>
+      </c>
+      <c r="D61">
+        <v>228.7</v>
+      </c>
+      <c r="E61">
+        <v>65.3</v>
+      </c>
+      <c r="F61">
+        <v>-6.6500000000019099E-2</v>
+      </c>
+      <c r="G61">
+        <v>-29.600000000000023</v>
+      </c>
+      <c r="H61">
+        <v>-15.200000000000003</v>
+      </c>
+      <c r="I61" t="s">
+        <v>38</v>
+      </c>
+      <c r="J61" t="s">
+        <v>39</v>
+      </c>
+      <c r="K61" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="62" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>18</v>
+      </c>
+      <c r="B62">
+        <v>2</v>
+      </c>
+      <c r="C62">
+        <v>410.56650000000002</v>
+      </c>
+      <c r="D62">
+        <v>228.2</v>
+      </c>
+      <c r="E62">
+        <v>67.3</v>
+      </c>
+      <c r="F62">
+        <v>-0.5665000000000191</v>
+      </c>
+      <c r="G62">
+        <v>-29.600000000000023</v>
+      </c>
+      <c r="H62">
+        <v>-14.400000000000006</v>
+      </c>
+      <c r="I62" t="s">
+        <v>38</v>
+      </c>
+      <c r="J62" t="s">
+        <v>39</v>
+      </c>
+      <c r="K62" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="63" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>18</v>
+      </c>
+      <c r="B63">
+        <v>15</v>
+      </c>
+      <c r="C63">
+        <v>410.16650000000004</v>
+      </c>
+      <c r="D63">
+        <v>227.5</v>
+      </c>
+      <c r="E63">
+        <v>66.7</v>
+      </c>
+      <c r="F63">
+        <v>-0.16650000000004184</v>
+      </c>
+      <c r="G63">
+        <v>-29.699999999999989</v>
+      </c>
+      <c r="H63">
+        <v>-14.599999999999994</v>
+      </c>
+      <c r="I63" t="s">
+        <v>38</v>
+      </c>
+      <c r="J63" t="s">
+        <v>39</v>
+      </c>
+      <c r="K63" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="64" spans="1:27" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>19</v>
+      </c>
+      <c r="B64">
+        <v>9</v>
+      </c>
+      <c r="C64">
+        <v>284.36649999999997</v>
+      </c>
+      <c r="D64">
+        <v>113</v>
+      </c>
+      <c r="E64">
+        <v>70.900000000000006</v>
+      </c>
+      <c r="F64">
+        <v>0.63350000000002638</v>
+      </c>
+      <c r="G64">
+        <v>-29.5</v>
+      </c>
+      <c r="H64">
+        <v>-14.799999999999997</v>
+      </c>
+      <c r="I64" t="s">
+        <v>38</v>
+      </c>
+      <c r="J64" t="s">
+        <v>39</v>
+      </c>
+      <c r="K64" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>19</v>
+      </c>
+      <c r="B65">
+        <v>13</v>
+      </c>
+      <c r="C65">
+        <v>284.16649999999998</v>
+      </c>
+      <c r="D65">
+        <v>112.2</v>
+      </c>
+      <c r="E65">
+        <v>69.900000000000006</v>
+      </c>
+      <c r="F65">
+        <v>0.83350000000001501</v>
+      </c>
+      <c r="G65">
+        <v>-28.5</v>
+      </c>
+      <c r="H65">
+        <v>-14.099999999999994</v>
+      </c>
+      <c r="I65" t="s">
+        <v>38</v>
+      </c>
+      <c r="J65" t="s">
+        <v>39</v>
+      </c>
+      <c r="K65" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>19</v>
+      </c>
+      <c r="B66">
+        <v>14</v>
+      </c>
+      <c r="C66">
+        <v>284.16649999999998</v>
+      </c>
+      <c r="D66">
+        <v>112.3</v>
+      </c>
+      <c r="E66">
+        <v>69.900000000000006</v>
+      </c>
+      <c r="F66">
+        <v>0.83350000000001501</v>
+      </c>
+      <c r="G66">
+        <v>-29</v>
+      </c>
+      <c r="H66">
+        <v>-14.099999999999994</v>
+      </c>
+      <c r="I66" t="s">
+        <v>38</v>
+      </c>
+      <c r="J66" t="s">
+        <v>39</v>
+      </c>
+      <c r="K66" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>17</v>
+      </c>
+      <c r="C67">
+        <v>454.16650000000004</v>
+      </c>
+      <c r="D67">
+        <v>124.1</v>
+      </c>
+      <c r="E67">
+        <v>66.3</v>
+      </c>
+      <c r="F67">
+        <v>-4.1665000000000418</v>
+      </c>
+      <c r="G67">
+        <v>-26.5</v>
+      </c>
+      <c r="H67">
+        <v>-13.700000000000003</v>
+      </c>
+      <c r="I67" t="s">
+        <v>38</v>
+      </c>
+      <c r="J67" t="s">
+        <v>39</v>
+      </c>
+      <c r="K67" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>17</v>
+      </c>
+      <c r="C68">
+        <v>453.16650000000004</v>
+      </c>
+      <c r="D68">
+        <v>124</v>
+      </c>
+      <c r="E68">
+        <v>67.099999999999994</v>
+      </c>
+      <c r="F68">
+        <v>-3.1665000000000418</v>
+      </c>
+      <c r="G68">
+        <v>-26</v>
+      </c>
+      <c r="H68">
+        <v>-14.599999999999994</v>
+      </c>
+      <c r="I68" t="s">
+        <v>38</v>
+      </c>
+      <c r="J68" t="s">
+        <v>39</v>
+      </c>
+      <c r="K68" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>17</v>
+      </c>
+      <c r="C69">
+        <v>454.06650000000002</v>
+      </c>
+      <c r="D69">
+        <v>126</v>
+      </c>
+      <c r="E69">
+        <v>67.2</v>
+      </c>
+      <c r="F69">
+        <v>-4.0665000000000191</v>
+      </c>
+      <c r="G69">
+        <v>-26</v>
+      </c>
+      <c r="H69">
+        <v>-14.5</v>
+      </c>
+      <c r="I69" t="s">
+        <v>38</v>
+      </c>
+      <c r="J69" t="s">
+        <v>39</v>
+      </c>
+      <c r="K69" t="s">
+        <v>39</v>
       </c>
     </row>
   </sheetData>

--- a/Acceptance_test_corrosion_and_parameterisation_size.xlsx
+++ b/Acceptance_test_corrosion_and_parameterisation_size.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jens1\Documents\GitHub\Robotteknologi-5.-semester\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C139C01-69EB-42E2-B197-7979C1FEB4E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A5FAE64-8EC1-4E76-831F-B55FFED5BB8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{634B6407-AD3C-4DC4-BF9C-C1397938D912}"/>
+    <workbookView xWindow="28695" yWindow="7065" windowWidth="16410" windowHeight="14145" xr2:uid="{634B6407-AD3C-4DC4-BF9C-C1397938D912}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="38">
   <si>
     <t>Test NR</t>
   </si>
@@ -172,12 +172,6 @@
   </si>
   <si>
     <t>Z offset</t>
-  </si>
-  <si>
-    <t>TRUE</t>
-  </si>
-  <si>
-    <t>False</t>
   </si>
 </sst>
 </file>
@@ -802,7 +796,7 @@
         <v>18</v>
       </c>
       <c r="W3" t="b">
-        <f t="shared" ref="W3:W24" si="5">IF(N3="Sblob",
+        <f t="shared" ref="W3:W23" si="5">IF(N3="Sblob",
     AND(O3 &gt;= O$28*(1-0.05), O3 &lt;= O$28*(1+0.05)),
 IF(N3="Lblob",
     AND(O3 &gt;= O$29*(1-0.05), O3 &lt;= O$29*(1+0.05)),
@@ -2585,11 +2579,11 @@
         <v>25</v>
       </c>
       <c r="K27" s="3">
-        <f>(500-364)</f>
+        <f>500-364</f>
         <v>136</v>
       </c>
       <c r="L27" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="28" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
@@ -2615,6 +2609,16 @@
       </c>
       <c r="H28">
         <v>195</v>
+      </c>
+      <c r="I28">
+        <v>-197.8665</v>
+      </c>
+      <c r="J28">
+        <v>35</v>
+      </c>
+      <c r="K28" s="3">
+        <f>(500-364-(240-218))</f>
+        <v>114</v>
       </c>
       <c r="N28" t="s">
         <v>18</v>
@@ -2930,7 +2934,7 @@
         <v>65.3</v>
       </c>
       <c r="G33">
-        <f>ABS(F2-K$27)</f>
+        <f t="shared" ref="G33:G52" si="16">ABS(F2-K$27)</f>
         <v>349.6</v>
       </c>
       <c r="H33">
@@ -2966,11 +2970,11 @@
         <v>TRUE</v>
       </c>
       <c r="M33" t="str">
-        <f t="shared" ref="M33:N33" si="16">IF(ABS(J33)&lt;$L$27,"TRUE","False")</f>
+        <f>IF(ABS(J33)&lt;$L$27,"TRUE","False")</f>
         <v>False</v>
       </c>
       <c r="N33" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" ref="N33" si="17">IF(ABS(K33)&lt;$L$27,"TRUE","False")</f>
         <v>False</v>
       </c>
       <c r="U33" s="3" t="s">
@@ -3005,31 +3009,31 @@
         <v>2</v>
       </c>
       <c r="C34">
-        <f t="shared" ref="C34:D34" si="17">B3-$I$27</f>
+        <f t="shared" ref="C34:D34" si="18">B3-$I$27</f>
         <v>410.56650000000002</v>
       </c>
       <c r="D34">
-        <f t="shared" si="17"/>
+        <f t="shared" si="18"/>
         <v>581.36649999999997</v>
       </c>
       <c r="E34">
-        <f t="shared" ref="E34:E52" si="18">ABS(J$27+D3)</f>
+        <f t="shared" ref="E34:E52" si="19">ABS(J$27+D3)</f>
         <v>74.900000000000006</v>
       </c>
       <c r="F34">
-        <f t="shared" ref="F34:F52" si="19">ABS(J$27+E3)</f>
+        <f>ABS(J$27+E3)</f>
         <v>67.3</v>
       </c>
       <c r="G34">
-        <f t="shared" ref="G34:G52" si="20">ABS(F3-K$27)</f>
+        <f t="shared" si="16"/>
         <v>349.6</v>
       </c>
       <c r="H34">
-        <f t="shared" ref="H34:H52" si="21">ABS(G3-K$27)</f>
+        <f t="shared" ref="H34:H52" si="20">ABS(G3-K$27)</f>
         <v>228.2</v>
       </c>
       <c r="I34">
-        <f t="shared" ref="I34:I52" si="22">IF($A34="Sblob", C$28-C34,
+        <f t="shared" ref="I34:I52" si="21">IF($A34="Sblob", C$28-C34,
    IF($A34="Lblob", C$29-C34,
    IF($A34="Rec", C$30-C34,
 ""
@@ -3037,7 +3041,7 @@
         <v>-0.5665000000000191</v>
       </c>
       <c r="J34">
-        <f t="shared" ref="J34:J52" si="23">IF($A34="Sblob", E$28-E34,
+        <f t="shared" ref="J34:J52" si="22">IF($A34="Sblob", E$28-E34,
    IF($A34="Lblob", E$29-E34,
    IF($A34="Rec", E$30-E34,
 ""
@@ -3045,7 +3049,7 @@
         <v>-14.400000000000006</v>
       </c>
       <c r="K34">
-        <f t="shared" ref="K34:K52" si="24">IF($A34="Sblob", G$28-G34,
+        <f t="shared" ref="K34:K52" si="23">IF($A34="Sblob", G$28-G34,
    IF($A34="Lblob", G$29-G34,
    IF($A34="Rec", G$30-G34,
 ""
@@ -3053,16 +3057,28 @@
         <v>-29.600000000000023</v>
       </c>
       <c r="L34" t="str">
-        <f t="shared" ref="L34:L56" si="25">IF(ABS(I34)&lt;$L$27,"TRUE","False")</f>
+        <f t="shared" ref="L34:L56" si="24">IF(ABS(I34)&lt;$L$27,"TRUE","False")</f>
         <v>TRUE</v>
       </c>
       <c r="M34" t="str">
-        <f t="shared" ref="M34:M56" si="26">IF(ABS(J34)&lt;$L$27,"TRUE","False")</f>
+        <f t="shared" ref="M34:M56" si="25">IF(ABS(J34)&lt;$L$27,"TRUE","False")</f>
         <v>False</v>
       </c>
       <c r="N34" t="str">
-        <f t="shared" ref="N34:N56" si="27">IF(ABS(K34)&lt;$L$27,"TRUE","False")</f>
-        <v>False</v>
+        <f t="shared" ref="N34:N56" si="26">IF(ABS(K34)&lt;$L$27,"TRUE","False")</f>
+        <v>False</v>
+      </c>
+      <c r="P34">
+        <f>212-$I$27</f>
+        <v>409.86649999999997</v>
+      </c>
+      <c r="Q34">
+        <f>ABS(J$27+-65.1)</f>
+        <v>40.099999999999994</v>
+      </c>
+      <c r="R34">
+        <f>ABS(-190.7-K$27)</f>
+        <v>326.7</v>
       </c>
       <c r="U34" s="3" t="s">
         <v>17</v>
@@ -3096,52 +3112,68 @@
         <v>3</v>
       </c>
       <c r="C35" s="3">
-        <f t="shared" ref="C35:D35" si="28">B4-$I$27</f>
+        <f t="shared" ref="C35:D35" si="27">B4-$I$27</f>
         <v>447.36649999999997</v>
       </c>
       <c r="D35" s="3">
-        <f t="shared" si="28"/>
+        <f t="shared" si="27"/>
         <v>572.26649999999995</v>
       </c>
       <c r="E35" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>74.400000000000006</v>
       </c>
       <c r="F35" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" ref="F35:F52" si="28">ABS(J$27+E4)</f>
         <v>65.400000000000006</v>
       </c>
       <c r="G35" s="3">
+        <f t="shared" si="16"/>
+        <v>198.8</v>
+      </c>
+      <c r="H35" s="3">
         <f t="shared" si="20"/>
-        <v>198.8</v>
-      </c>
-      <c r="H35" s="3">
+        <v>125.3</v>
+      </c>
+      <c r="I35" s="3">
         <f t="shared" si="21"/>
-        <v>125.3</v>
-      </c>
-      <c r="I35" s="3">
-        <f t="shared" si="22"/>
         <v>2.6335000000000264</v>
       </c>
       <c r="J35" s="3">
+        <f>IF($A35="Sblob", E$28-E35,
+   IF($A35="Lblob", E$29-E35,
+   IF($A35="Rec", E$30-E35,
+""
+)))</f>
+        <v>-14.900000000000006</v>
+      </c>
+      <c r="K35" s="3">
         <f t="shared" si="23"/>
-        <v>-14.900000000000006</v>
-      </c>
-      <c r="K35" s="3">
+        <v>-25.800000000000011</v>
+      </c>
+      <c r="L35" t="str">
         <f t="shared" si="24"/>
-        <v>-25.800000000000011</v>
-      </c>
-      <c r="L35" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="M35" t="str">
         <f t="shared" si="25"/>
-        <v>TRUE</v>
-      </c>
-      <c r="M35" t="str">
+        <v>False</v>
+      </c>
+      <c r="N35" t="str">
         <f t="shared" si="26"/>
         <v>False</v>
       </c>
-      <c r="N35" t="str">
-        <f t="shared" si="27"/>
-        <v>False</v>
+      <c r="P35">
+        <f>C28-P34</f>
+        <v>0.13350000000002638</v>
+      </c>
+      <c r="Q35">
+        <f>E28-Q34</f>
+        <v>20.400000000000006</v>
+      </c>
+      <c r="R35">
+        <f>G28-R34</f>
+        <v>-6.6999999999999886</v>
       </c>
       <c r="U35" s="3" t="s">
         <v>17</v>
@@ -3183,43 +3215,43 @@
         <v>577.26649999999995</v>
       </c>
       <c r="E36" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>74.400000000000006</v>
       </c>
       <c r="F36" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="28"/>
         <v>65.599999999999994</v>
       </c>
       <c r="G36" s="3">
+        <f t="shared" si="16"/>
+        <v>202.2</v>
+      </c>
+      <c r="H36" s="3">
         <f t="shared" si="20"/>
-        <v>202.2</v>
-      </c>
-      <c r="H36" s="3">
+        <v>125.8</v>
+      </c>
+      <c r="I36" s="3">
         <f t="shared" si="21"/>
-        <v>125.8</v>
-      </c>
-      <c r="I36" s="3">
+        <v>-4.8664999999999736</v>
+      </c>
+      <c r="J36" s="3">
         <f t="shared" si="22"/>
-        <v>-4.8664999999999736</v>
-      </c>
-      <c r="J36" s="3">
+        <v>-14.900000000000006</v>
+      </c>
+      <c r="K36" s="3">
         <f t="shared" si="23"/>
-        <v>-14.900000000000006</v>
-      </c>
-      <c r="K36" s="3">
+        <v>-29.199999999999989</v>
+      </c>
+      <c r="L36" t="str">
         <f t="shared" si="24"/>
-        <v>-29.199999999999989</v>
-      </c>
-      <c r="L36" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="M36" t="str">
         <f t="shared" si="25"/>
-        <v>TRUE</v>
-      </c>
-      <c r="M36" t="str">
+        <v>False</v>
+      </c>
+      <c r="N36" t="str">
         <f t="shared" si="26"/>
-        <v>False</v>
-      </c>
-      <c r="N36" t="str">
-        <f t="shared" si="27"/>
         <v>False</v>
       </c>
       <c r="P36" s="2"/>
@@ -3264,43 +3296,43 @@
         <v>579.9665</v>
       </c>
       <c r="E37" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>74</v>
       </c>
       <c r="F37" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="28"/>
         <v>65.400000000000006</v>
       </c>
       <c r="G37" s="3">
+        <f t="shared" si="16"/>
+        <v>211.7</v>
+      </c>
+      <c r="H37" s="3">
         <f t="shared" si="20"/>
-        <v>211.7</v>
-      </c>
-      <c r="H37" s="3">
+        <v>126.2</v>
+      </c>
+      <c r="I37" s="3">
         <f t="shared" si="21"/>
-        <v>126.2</v>
-      </c>
-      <c r="I37" s="3">
+        <v>-5.3664999999999736</v>
+      </c>
+      <c r="J37" s="3">
         <f t="shared" si="22"/>
-        <v>-5.3664999999999736</v>
-      </c>
-      <c r="J37" s="3">
+        <v>-14.5</v>
+      </c>
+      <c r="K37" s="3">
         <f t="shared" si="23"/>
-        <v>-14.5</v>
-      </c>
-      <c r="K37" s="3">
+        <v>-38.699999999999989</v>
+      </c>
+      <c r="L37" t="str">
         <f t="shared" si="24"/>
-        <v>-38.699999999999989</v>
-      </c>
-      <c r="L37" t="str">
+        <v>False</v>
+      </c>
+      <c r="M37" t="str">
         <f t="shared" si="25"/>
-        <v>TRUE</v>
-      </c>
-      <c r="M37" t="str">
+        <v>False</v>
+      </c>
+      <c r="N37" t="str">
         <f t="shared" si="26"/>
-        <v>False</v>
-      </c>
-      <c r="N37" t="str">
-        <f t="shared" si="27"/>
         <v>False</v>
       </c>
       <c r="U37" t="s">
@@ -3342,43 +3374,43 @@
         <v>584.9665</v>
       </c>
       <c r="E38" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>74.099999999999994</v>
       </c>
       <c r="F38" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="28"/>
         <v>66.3</v>
       </c>
       <c r="G38" s="3">
+        <f t="shared" si="16"/>
+        <v>204.3</v>
+      </c>
+      <c r="H38" s="3">
         <f t="shared" si="20"/>
-        <v>204.3</v>
-      </c>
-      <c r="H38" s="3">
+        <v>125.9</v>
+      </c>
+      <c r="I38" s="3">
         <f t="shared" si="21"/>
-        <v>125.9</v>
-      </c>
-      <c r="I38" s="3">
+        <v>-5.3664999999999736</v>
+      </c>
+      <c r="J38" s="3">
         <f t="shared" si="22"/>
-        <v>-5.3664999999999736</v>
-      </c>
-      <c r="J38" s="3">
+        <v>-14.599999999999994</v>
+      </c>
+      <c r="K38" s="3">
         <f t="shared" si="23"/>
-        <v>-14.599999999999994</v>
-      </c>
-      <c r="K38" s="3">
+        <v>-31.300000000000011</v>
+      </c>
+      <c r="L38" t="str">
         <f t="shared" si="24"/>
-        <v>-31.300000000000011</v>
-      </c>
-      <c r="L38" t="str">
+        <v>False</v>
+      </c>
+      <c r="M38" t="str">
         <f t="shared" si="25"/>
-        <v>TRUE</v>
-      </c>
-      <c r="M38" t="str">
+        <v>False</v>
+      </c>
+      <c r="N38" t="str">
         <f t="shared" si="26"/>
-        <v>False</v>
-      </c>
-      <c r="N38" t="str">
-        <f t="shared" si="27"/>
         <v>False</v>
       </c>
       <c r="P38" s="2"/>
@@ -3423,43 +3455,43 @@
         <v>577.86649999999997</v>
       </c>
       <c r="E39" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>75.5</v>
       </c>
       <c r="F39" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="28"/>
         <v>65.099999999999994</v>
       </c>
       <c r="G39" s="3">
+        <f t="shared" si="16"/>
+        <v>223</v>
+      </c>
+      <c r="H39" s="3">
         <f t="shared" si="20"/>
-        <v>223</v>
-      </c>
-      <c r="H39" s="3">
+        <v>125.5</v>
+      </c>
+      <c r="I39" s="3">
         <f t="shared" si="21"/>
-        <v>125.5</v>
-      </c>
-      <c r="I39" s="3">
+        <v>20.333499999999958</v>
+      </c>
+      <c r="J39" s="3">
         <f t="shared" si="22"/>
-        <v>20.333499999999958</v>
-      </c>
-      <c r="J39" s="3">
+        <v>-16</v>
+      </c>
+      <c r="K39" s="3">
         <f t="shared" si="23"/>
-        <v>-16</v>
-      </c>
-      <c r="K39" s="3">
+        <v>-50</v>
+      </c>
+      <c r="L39" t="str">
         <f t="shared" si="24"/>
-        <v>-50</v>
-      </c>
-      <c r="L39" t="str">
+        <v>False</v>
+      </c>
+      <c r="M39" t="str">
         <f t="shared" si="25"/>
         <v>False</v>
       </c>
-      <c r="M39" t="str">
+      <c r="N39" t="str">
         <f t="shared" si="26"/>
-        <v>False</v>
-      </c>
-      <c r="N39" t="str">
-        <f t="shared" si="27"/>
         <v>False</v>
       </c>
       <c r="U39" s="3" t="s">
@@ -3502,43 +3534,43 @@
         <v>584.9665</v>
       </c>
       <c r="E40" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>74.2</v>
       </c>
       <c r="F40" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="28"/>
         <v>66.900000000000006</v>
       </c>
       <c r="G40" s="3">
+        <f t="shared" si="16"/>
+        <v>211.2</v>
+      </c>
+      <c r="H40" s="3">
         <f t="shared" si="20"/>
-        <v>211.2</v>
-      </c>
-      <c r="H40" s="3">
+        <v>116.7</v>
+      </c>
+      <c r="I40" s="3">
         <f t="shared" si="21"/>
-        <v>116.7</v>
-      </c>
-      <c r="I40" s="3">
+        <v>6.0335000000000036</v>
+      </c>
+      <c r="J40" s="3">
         <f t="shared" si="22"/>
-        <v>6.0335000000000036</v>
-      </c>
-      <c r="J40" s="3">
+        <v>-14.700000000000003</v>
+      </c>
+      <c r="K40" s="3">
         <f t="shared" si="23"/>
-        <v>-14.700000000000003</v>
-      </c>
-      <c r="K40" s="3">
+        <v>-38.199999999999989</v>
+      </c>
+      <c r="L40" t="str">
         <f t="shared" si="24"/>
-        <v>-38.199999999999989</v>
-      </c>
-      <c r="L40" t="str">
+        <v>False</v>
+      </c>
+      <c r="M40" t="str">
         <f t="shared" si="25"/>
-        <v>TRUE</v>
-      </c>
-      <c r="M40" t="str">
+        <v>False</v>
+      </c>
+      <c r="N40" t="str">
         <f t="shared" si="26"/>
-        <v>False</v>
-      </c>
-      <c r="N40" t="str">
-        <f t="shared" si="27"/>
         <v>False</v>
       </c>
       <c r="P40" s="2"/>
@@ -3583,43 +3615,43 @@
         <v>359.56650000000002</v>
       </c>
       <c r="E41">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>74.8</v>
       </c>
       <c r="F41">
-        <f t="shared" si="19"/>
+        <f t="shared" si="28"/>
         <v>70.900000000000006</v>
       </c>
       <c r="G41">
+        <f t="shared" si="16"/>
+        <v>275.5</v>
+      </c>
+      <c r="H41">
         <f t="shared" si="20"/>
-        <v>275.5</v>
-      </c>
-      <c r="H41">
+        <v>113</v>
+      </c>
+      <c r="I41">
         <f t="shared" si="21"/>
-        <v>113</v>
-      </c>
-      <c r="I41">
+        <v>0.63350000000002638</v>
+      </c>
+      <c r="J41">
         <f t="shared" si="22"/>
-        <v>0.63350000000002638</v>
-      </c>
-      <c r="J41">
+        <v>-14.799999999999997</v>
+      </c>
+      <c r="K41">
         <f t="shared" si="23"/>
-        <v>-14.799999999999997</v>
-      </c>
-      <c r="K41">
+        <v>-29.5</v>
+      </c>
+      <c r="L41" t="str">
         <f t="shared" si="24"/>
-        <v>-29.5</v>
-      </c>
-      <c r="L41" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="M41" t="str">
         <f t="shared" si="25"/>
-        <v>TRUE</v>
-      </c>
-      <c r="M41" t="str">
+        <v>False</v>
+      </c>
+      <c r="N41" t="str">
         <f t="shared" si="26"/>
-        <v>False</v>
-      </c>
-      <c r="N41" t="str">
-        <f t="shared" si="27"/>
         <v>False</v>
       </c>
       <c r="U41" t="s">
@@ -3661,43 +3693,43 @@
         <v>359.06650000000002</v>
       </c>
       <c r="E42" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>74.3</v>
       </c>
       <c r="F42" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="28"/>
         <v>69.599999999999994</v>
       </c>
       <c r="G42" s="3">
+        <f t="shared" si="16"/>
+        <v>275.5</v>
+      </c>
+      <c r="H42" s="3">
         <f t="shared" si="20"/>
-        <v>275.5</v>
-      </c>
-      <c r="H42" s="3">
+        <v>149.5</v>
+      </c>
+      <c r="I42" s="3" t="str">
         <f t="shared" si="21"/>
-        <v>149.5</v>
-      </c>
-      <c r="I42" s="3" t="str">
+        <v/>
+      </c>
+      <c r="J42" s="3" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="J42" s="3" t="str">
+      <c r="K42" s="3" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="K42" s="3" t="str">
+      <c r="L42" t="e">
         <f t="shared" si="24"/>
-        <v/>
-      </c>
-      <c r="L42" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="M42" t="e">
         <f t="shared" si="25"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M42" t="e">
+      <c r="N42" t="e">
         <f t="shared" si="26"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N42" t="e">
-        <f t="shared" si="27"/>
         <v>#VALUE!</v>
       </c>
       <c r="U42" t="s">
@@ -3739,43 +3771,43 @@
         <v>358.9665</v>
       </c>
       <c r="E43" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>74</v>
       </c>
       <c r="F43" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="28"/>
         <v>70.5</v>
       </c>
       <c r="G43" s="3">
+        <f t="shared" si="16"/>
+        <v>275.39999999999998</v>
+      </c>
+      <c r="H43" s="3">
         <f t="shared" si="20"/>
-        <v>275.39999999999998</v>
-      </c>
-      <c r="H43" s="3">
+        <v>160</v>
+      </c>
+      <c r="I43" s="3" t="str">
         <f t="shared" si="21"/>
-        <v>160</v>
-      </c>
-      <c r="I43" s="3" t="str">
+        <v/>
+      </c>
+      <c r="J43" s="3" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="J43" s="3" t="str">
+      <c r="K43" s="3" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="K43" s="3" t="str">
+      <c r="L43" t="e">
         <f t="shared" si="24"/>
-        <v/>
-      </c>
-      <c r="L43" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="M43" t="e">
         <f t="shared" si="25"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M43" t="e">
+      <c r="N43" t="e">
         <f t="shared" si="26"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N43" t="e">
-        <f t="shared" si="27"/>
         <v>#VALUE!</v>
       </c>
       <c r="U43" t="s">
@@ -3817,43 +3849,43 @@
         <v>359.16650000000004</v>
       </c>
       <c r="E44" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>73.599999999999994</v>
       </c>
       <c r="F44" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="28"/>
         <v>69.900000000000006</v>
       </c>
       <c r="G44" s="3">
+        <f t="shared" si="16"/>
+        <v>275</v>
+      </c>
+      <c r="H44" s="3">
         <f t="shared" si="20"/>
-        <v>275</v>
-      </c>
-      <c r="H44" s="3">
+        <v>162</v>
+      </c>
+      <c r="I44" s="3" t="str">
         <f t="shared" si="21"/>
-        <v>162</v>
-      </c>
-      <c r="I44" s="3" t="str">
+        <v/>
+      </c>
+      <c r="J44" s="3" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="J44" s="3" t="str">
+      <c r="K44" s="3" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="K44" s="3" t="str">
+      <c r="L44" t="e">
         <f t="shared" si="24"/>
-        <v/>
-      </c>
-      <c r="L44" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="M44" t="e">
         <f t="shared" si="25"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M44" t="e">
+      <c r="N44" t="e">
         <f t="shared" si="26"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N44" t="e">
-        <f t="shared" si="27"/>
         <v>#VALUE!</v>
       </c>
       <c r="U44" s="3" t="s">
@@ -3896,43 +3928,43 @@
         <v>359.16650000000004</v>
       </c>
       <c r="E45">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>74.099999999999994</v>
       </c>
       <c r="F45">
-        <f t="shared" si="19"/>
+        <f t="shared" si="28"/>
         <v>69.900000000000006</v>
       </c>
       <c r="G45">
+        <f t="shared" si="16"/>
+        <v>274.5</v>
+      </c>
+      <c r="H45">
         <f t="shared" si="20"/>
-        <v>274.5</v>
-      </c>
-      <c r="H45">
+        <v>112.2</v>
+      </c>
+      <c r="I45">
         <f t="shared" si="21"/>
-        <v>112.2</v>
-      </c>
-      <c r="I45">
+        <v>0.83350000000001501</v>
+      </c>
+      <c r="J45">
         <f t="shared" si="22"/>
-        <v>0.83350000000001501</v>
-      </c>
-      <c r="J45">
+        <v>-14.099999999999994</v>
+      </c>
+      <c r="K45">
         <f t="shared" si="23"/>
-        <v>-14.099999999999994</v>
-      </c>
-      <c r="K45">
+        <v>-28.5</v>
+      </c>
+      <c r="L45" t="str">
         <f t="shared" si="24"/>
-        <v>-28.5</v>
-      </c>
-      <c r="L45" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="M45" t="str">
         <f t="shared" si="25"/>
-        <v>TRUE</v>
-      </c>
-      <c r="M45" t="str">
+        <v>False</v>
+      </c>
+      <c r="N45" t="str">
         <f t="shared" si="26"/>
-        <v>False</v>
-      </c>
-      <c r="N45" t="str">
-        <f t="shared" si="27"/>
         <v>False</v>
       </c>
       <c r="U45" s="3" t="s">
@@ -3975,43 +4007,43 @@
         <v>359.16650000000004</v>
       </c>
       <c r="E46">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>74.099999999999994</v>
       </c>
       <c r="F46">
-        <f t="shared" si="19"/>
+        <f t="shared" si="28"/>
         <v>69.900000000000006</v>
       </c>
       <c r="G46">
+        <f t="shared" si="16"/>
+        <v>275</v>
+      </c>
+      <c r="H46">
         <f t="shared" si="20"/>
-        <v>275</v>
-      </c>
-      <c r="H46">
+        <v>112.3</v>
+      </c>
+      <c r="I46">
         <f t="shared" si="21"/>
-        <v>112.3</v>
-      </c>
-      <c r="I46">
+        <v>0.83350000000001501</v>
+      </c>
+      <c r="J46">
         <f t="shared" si="22"/>
-        <v>0.83350000000001501</v>
-      </c>
-      <c r="J46">
+        <v>-14.099999999999994</v>
+      </c>
+      <c r="K46">
         <f t="shared" si="23"/>
-        <v>-14.099999999999994</v>
-      </c>
-      <c r="K46">
+        <v>-29</v>
+      </c>
+      <c r="L46" t="str">
         <f t="shared" si="24"/>
-        <v>-29</v>
-      </c>
-      <c r="L46" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="M46" t="str">
         <f t="shared" si="25"/>
-        <v>TRUE</v>
-      </c>
-      <c r="M46" t="str">
+        <v>False</v>
+      </c>
+      <c r="N46" t="str">
         <f t="shared" si="26"/>
-        <v>False</v>
-      </c>
-      <c r="N46" t="str">
-        <f t="shared" si="27"/>
         <v>False</v>
       </c>
       <c r="U46" s="3" t="s">
@@ -4054,43 +4086,43 @@
         <v>581.26649999999995</v>
       </c>
       <c r="E47">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>75.099999999999994</v>
       </c>
       <c r="F47">
-        <f t="shared" si="19"/>
+        <f t="shared" si="28"/>
         <v>66.7</v>
       </c>
       <c r="G47">
+        <f t="shared" si="16"/>
+        <v>349.7</v>
+      </c>
+      <c r="H47">
         <f t="shared" si="20"/>
-        <v>349.7</v>
-      </c>
-      <c r="H47">
+        <v>227.5</v>
+      </c>
+      <c r="I47">
         <f t="shared" si="21"/>
-        <v>227.5</v>
-      </c>
-      <c r="I47">
+        <v>-0.16650000000004184</v>
+      </c>
+      <c r="J47">
         <f t="shared" si="22"/>
-        <v>-0.16650000000004184</v>
-      </c>
-      <c r="J47">
+        <v>-14.599999999999994</v>
+      </c>
+      <c r="K47">
         <f t="shared" si="23"/>
-        <v>-14.599999999999994</v>
-      </c>
-      <c r="K47">
+        <v>-29.699999999999989</v>
+      </c>
+      <c r="L47" t="str">
         <f t="shared" si="24"/>
-        <v>-29.699999999999989</v>
-      </c>
-      <c r="L47" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="M47" t="str">
         <f t="shared" si="25"/>
-        <v>TRUE</v>
-      </c>
-      <c r="M47" t="str">
+        <v>False</v>
+      </c>
+      <c r="N47" t="str">
         <f t="shared" si="26"/>
-        <v>False</v>
-      </c>
-      <c r="N47" t="str">
-        <f t="shared" si="27"/>
         <v>False</v>
       </c>
       <c r="U47" s="3" t="s">
@@ -4133,43 +4165,43 @@
         <v>572.76649999999995</v>
       </c>
       <c r="E48" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>104.80000000000001</v>
       </c>
       <c r="F48" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="28"/>
         <v>69.3</v>
       </c>
       <c r="G48" s="3">
+        <f t="shared" si="16"/>
+        <v>298.2</v>
+      </c>
+      <c r="H48" s="3">
         <f t="shared" si="20"/>
-        <v>298.2</v>
-      </c>
-      <c r="H48" s="3">
+        <v>205.6</v>
+      </c>
+      <c r="I48" s="3" t="str">
         <f t="shared" si="21"/>
-        <v>205.6</v>
-      </c>
-      <c r="I48" s="3" t="str">
+        <v/>
+      </c>
+      <c r="J48" s="3" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="J48" s="3" t="str">
+      <c r="K48" s="3" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="K48" s="3" t="str">
+      <c r="L48" t="e">
         <f t="shared" si="24"/>
-        <v/>
-      </c>
-      <c r="L48" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="M48" t="e">
         <f t="shared" si="25"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M48" t="e">
+      <c r="N48" t="e">
         <f t="shared" si="26"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N48" t="e">
-        <f t="shared" si="27"/>
         <v>#VALUE!</v>
       </c>
       <c r="U48" s="3" t="s">
@@ -4212,43 +4244,43 @@
         <v>571.9665</v>
       </c>
       <c r="E49" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>103.6</v>
       </c>
       <c r="F49" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="28"/>
         <v>69.5</v>
       </c>
       <c r="G49" s="3">
+        <f t="shared" si="16"/>
+        <v>298.7</v>
+      </c>
+      <c r="H49" s="3">
         <f t="shared" si="20"/>
-        <v>298.7</v>
-      </c>
-      <c r="H49" s="3">
+        <v>205.1</v>
+      </c>
+      <c r="I49" s="3" t="str">
         <f t="shared" si="21"/>
-        <v>205.1</v>
-      </c>
-      <c r="I49" s="3" t="str">
+        <v/>
+      </c>
+      <c r="J49" s="3" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="J49" s="3" t="str">
+      <c r="K49" s="3" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="K49" s="3" t="str">
+      <c r="L49" t="e">
         <f t="shared" si="24"/>
-        <v/>
-      </c>
-      <c r="L49" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="M49" t="e">
         <f t="shared" si="25"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M49" t="e">
+      <c r="N49" t="e">
         <f t="shared" si="26"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N49" t="e">
-        <f t="shared" si="27"/>
         <v>#VALUE!</v>
       </c>
       <c r="U49" t="s">
@@ -4290,43 +4322,43 @@
         <v>572.9665</v>
       </c>
       <c r="E50" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>104.6</v>
       </c>
       <c r="F50" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="28"/>
         <v>69.5</v>
       </c>
       <c r="G50" s="3">
+        <f t="shared" si="16"/>
+        <v>298.7</v>
+      </c>
+      <c r="H50" s="3">
         <f t="shared" si="20"/>
-        <v>298.7</v>
-      </c>
-      <c r="H50" s="3">
+        <v>205.2</v>
+      </c>
+      <c r="I50" s="3" t="str">
         <f t="shared" si="21"/>
-        <v>205.2</v>
-      </c>
-      <c r="I50" s="3" t="str">
+        <v/>
+      </c>
+      <c r="J50" s="3" t="str">
         <f t="shared" si="22"/>
         <v/>
       </c>
-      <c r="J50" s="3" t="str">
+      <c r="K50" s="3" t="str">
         <f t="shared" si="23"/>
         <v/>
       </c>
-      <c r="K50" s="3" t="str">
+      <c r="L50" t="e">
         <f t="shared" si="24"/>
-        <v/>
-      </c>
-      <c r="L50" t="e">
+        <v>#VALUE!</v>
+      </c>
+      <c r="M50" t="e">
         <f t="shared" si="25"/>
         <v>#VALUE!</v>
       </c>
-      <c r="M50" t="e">
+      <c r="N50" t="e">
         <f t="shared" si="26"/>
-        <v>#VALUE!</v>
-      </c>
-      <c r="N50" t="e">
-        <f t="shared" si="27"/>
         <v>#VALUE!</v>
       </c>
       <c r="U50" t="s">
@@ -4368,43 +4400,43 @@
         <v>579.76649999999995</v>
       </c>
       <c r="E51" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>76</v>
       </c>
       <c r="F51" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="28"/>
         <v>65.099999999999994</v>
       </c>
       <c r="G51" s="3">
+        <f t="shared" si="16"/>
+        <v>348.9</v>
+      </c>
+      <c r="H51" s="3">
         <f t="shared" si="20"/>
-        <v>348.9</v>
-      </c>
-      <c r="H51" s="3">
+        <v>227.6</v>
+      </c>
+      <c r="I51" s="3">
         <f t="shared" si="21"/>
-        <v>227.6</v>
-      </c>
-      <c r="I51" s="3">
+        <v>0.83349999999995816</v>
+      </c>
+      <c r="J51" s="3">
         <f t="shared" si="22"/>
-        <v>0.83349999999995816</v>
-      </c>
-      <c r="J51" s="3">
+        <v>-15.5</v>
+      </c>
+      <c r="K51" s="3">
         <f t="shared" si="23"/>
-        <v>-15.5</v>
-      </c>
-      <c r="K51" s="3">
+        <v>-28.899999999999977</v>
+      </c>
+      <c r="L51" t="str">
         <f t="shared" si="24"/>
-        <v>-28.899999999999977</v>
-      </c>
-      <c r="L51" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="M51" t="str">
         <f t="shared" si="25"/>
-        <v>TRUE</v>
-      </c>
-      <c r="M51" t="str">
+        <v>False</v>
+      </c>
+      <c r="N51" t="str">
         <f t="shared" si="26"/>
-        <v>False</v>
-      </c>
-      <c r="N51" t="str">
-        <f t="shared" si="27"/>
         <v>False</v>
       </c>
       <c r="U51" t="s">
@@ -4446,43 +4478,43 @@
         <v>580.86649999999997</v>
       </c>
       <c r="E52" s="3">
-        <f t="shared" si="18"/>
+        <f t="shared" si="19"/>
         <v>75</v>
       </c>
       <c r="F52" s="3">
-        <f t="shared" si="19"/>
+        <f t="shared" si="28"/>
         <v>67.400000000000006</v>
       </c>
       <c r="G52" s="3">
+        <f t="shared" si="16"/>
+        <v>349.3</v>
+      </c>
+      <c r="H52" s="3">
         <f t="shared" si="20"/>
-        <v>349.3</v>
-      </c>
-      <c r="H52" s="3">
+        <v>227.8</v>
+      </c>
+      <c r="I52" s="3">
         <f t="shared" si="21"/>
-        <v>227.8</v>
-      </c>
-      <c r="I52" s="3">
+        <v>0.13350000000002638</v>
+      </c>
+      <c r="J52" s="3">
         <f t="shared" si="22"/>
-        <v>0.13350000000002638</v>
-      </c>
-      <c r="J52" s="3">
+        <v>-14.5</v>
+      </c>
+      <c r="K52" s="3">
         <f t="shared" si="23"/>
-        <v>-14.5</v>
-      </c>
-      <c r="K52" s="3">
+        <v>-29.300000000000011</v>
+      </c>
+      <c r="L52" t="str">
         <f t="shared" si="24"/>
-        <v>-29.300000000000011</v>
-      </c>
-      <c r="L52" t="str">
+        <v>TRUE</v>
+      </c>
+      <c r="M52" t="str">
         <f t="shared" si="25"/>
-        <v>TRUE</v>
-      </c>
-      <c r="M52" t="str">
+        <v>False</v>
+      </c>
+      <c r="N52" t="str">
         <f t="shared" si="26"/>
-        <v>False</v>
-      </c>
-      <c r="N52" t="str">
-        <f t="shared" si="27"/>
         <v>False</v>
       </c>
       <c r="W52" t="str">
@@ -4547,15 +4579,15 @@
         <v>-26.5</v>
       </c>
       <c r="L53" t="str">
+        <f t="shared" si="24"/>
+        <v>TRUE</v>
+      </c>
+      <c r="M53" t="str">
         <f t="shared" si="25"/>
-        <v>TRUE</v>
-      </c>
-      <c r="M53" t="str">
+        <v>False</v>
+      </c>
+      <c r="N53" t="str">
         <f t="shared" si="26"/>
-        <v>False</v>
-      </c>
-      <c r="N53" t="str">
-        <f t="shared" si="27"/>
         <v>False</v>
       </c>
       <c r="W53" t="str">
@@ -4608,19 +4640,19 @@
         <v>-26</v>
       </c>
       <c r="L54" t="str">
+        <f t="shared" si="24"/>
+        <v>TRUE</v>
+      </c>
+      <c r="M54" t="str">
         <f t="shared" si="25"/>
-        <v>TRUE</v>
-      </c>
-      <c r="M54" t="str">
+        <v>False</v>
+      </c>
+      <c r="N54" t="str">
         <f t="shared" si="26"/>
         <v>False</v>
       </c>
-      <c r="N54" t="str">
-        <f t="shared" si="27"/>
-        <v>False</v>
-      </c>
       <c r="W54" t="str">
-        <f t="shared" ref="W50:W56" si="55">IF(N31="Sblob",
+        <f t="shared" ref="W54:W56" si="55">IF(N31="Sblob",
     AND(S31 &gt;= O$23*(1-0.05), S31 &lt;= O$23*(1+0.05)),
 IF(N31="Lblob",
     AND(S31 &gt;= O$24*(1-0.05), S31 &lt;= O$24*(1+0.05)),
@@ -4631,7 +4663,7 @@
         <v/>
       </c>
       <c r="X54" t="str">
-        <f t="shared" ref="X50:X56" si="56">IF(N31="Sblob",
+        <f t="shared" ref="X54:X56" si="56">IF(N31="Sblob",
     AND(T31 &gt;= Q$23*(1-0.05), T31 &lt;= Q$23*(1+0.05)),
 IF(N31="Lblob",
     AND(T31 &gt;= Q$24*(1-0.05), T31 &lt;= Q$24*(1+0.05)),
@@ -4683,15 +4715,15 @@
         <v>-26</v>
       </c>
       <c r="L55" t="str">
+        <f t="shared" si="24"/>
+        <v>TRUE</v>
+      </c>
+      <c r="M55" t="str">
         <f t="shared" si="25"/>
-        <v>TRUE</v>
-      </c>
-      <c r="M55" t="str">
+        <v>False</v>
+      </c>
+      <c r="N55" t="str">
         <f t="shared" si="26"/>
-        <v>False</v>
-      </c>
-      <c r="N55" t="str">
-        <f t="shared" si="27"/>
         <v>False</v>
       </c>
       <c r="W55" t="str">
@@ -4717,15 +4749,15 @@
         <v>28.266666666666669</v>
       </c>
       <c r="L56" t="str">
+        <f t="shared" si="24"/>
+        <v>TRUE</v>
+      </c>
+      <c r="M56" t="str">
         <f t="shared" si="25"/>
-        <v>TRUE</v>
-      </c>
-      <c r="M56" t="str">
+        <v>False</v>
+      </c>
+      <c r="N56" t="str">
         <f t="shared" si="26"/>
-        <v>False</v>
-      </c>
-      <c r="N56" t="str">
-        <f t="shared" si="27"/>
         <v>False</v>
       </c>
       <c r="W56" t="str">
@@ -4783,28 +4815,36 @@
         <v>410.06650000000002</v>
       </c>
       <c r="D61">
-        <v>228.7</v>
+        <f>G33</f>
+        <v>349.6</v>
       </c>
       <c r="E61">
-        <v>65.3</v>
+        <f>E33</f>
+        <v>75.7</v>
       </c>
       <c r="F61">
+        <f>I33</f>
         <v>-6.6500000000019099E-2</v>
       </c>
       <c r="G61">
+        <f>K33</f>
         <v>-29.600000000000023</v>
       </c>
       <c r="H61">
+        <f>J33</f>
         <v>-15.200000000000003</v>
       </c>
-      <c r="I61" t="s">
-        <v>38</v>
-      </c>
-      <c r="J61" t="s">
-        <v>39</v>
-      </c>
-      <c r="K61" t="s">
-        <v>39</v>
+      <c r="I61" t="str">
+        <f t="shared" ref="I61:K62" si="58">L33</f>
+        <v>TRUE</v>
+      </c>
+      <c r="J61" t="str">
+        <f t="shared" si="58"/>
+        <v>False</v>
+      </c>
+      <c r="K61" t="str">
+        <f t="shared" si="58"/>
+        <v>False</v>
       </c>
     </row>
     <row r="62" spans="1:27" x14ac:dyDescent="0.25">
@@ -4818,28 +4858,36 @@
         <v>410.56650000000002</v>
       </c>
       <c r="D62">
-        <v>228.2</v>
+        <f>G34</f>
+        <v>349.6</v>
       </c>
       <c r="E62">
-        <v>67.3</v>
+        <f>E34</f>
+        <v>74.900000000000006</v>
       </c>
       <c r="F62">
+        <f>I34</f>
         <v>-0.5665000000000191</v>
       </c>
       <c r="G62">
+        <f>K34</f>
         <v>-29.600000000000023</v>
       </c>
       <c r="H62">
+        <f>J34</f>
         <v>-14.400000000000006</v>
       </c>
-      <c r="I62" t="s">
-        <v>38</v>
-      </c>
-      <c r="J62" t="s">
-        <v>39</v>
-      </c>
-      <c r="K62" t="s">
-        <v>39</v>
+      <c r="I62" t="str">
+        <f t="shared" si="58"/>
+        <v>TRUE</v>
+      </c>
+      <c r="J62" t="str">
+        <f t="shared" si="58"/>
+        <v>False</v>
+      </c>
+      <c r="K62" t="str">
+        <f t="shared" si="58"/>
+        <v>False</v>
       </c>
     </row>
     <row r="63" spans="1:27" x14ac:dyDescent="0.25">
@@ -4853,28 +4901,36 @@
         <v>410.16650000000004</v>
       </c>
       <c r="D63">
-        <v>227.5</v>
+        <f>G47</f>
+        <v>349.7</v>
       </c>
       <c r="E63">
-        <v>66.7</v>
+        <f>E47</f>
+        <v>75.099999999999994</v>
       </c>
       <c r="F63">
+        <f>I47</f>
         <v>-0.16650000000004184</v>
       </c>
       <c r="G63">
+        <f>K47</f>
         <v>-29.699999999999989</v>
       </c>
       <c r="H63">
+        <f>J47</f>
         <v>-14.599999999999994</v>
       </c>
-      <c r="I63" t="s">
-        <v>38</v>
-      </c>
-      <c r="J63" t="s">
-        <v>39</v>
-      </c>
-      <c r="K63" t="s">
-        <v>39</v>
+      <c r="I63" t="str">
+        <f>L47</f>
+        <v>TRUE</v>
+      </c>
+      <c r="J63" t="str">
+        <f>M47</f>
+        <v>False</v>
+      </c>
+      <c r="K63" t="str">
+        <f>N47</f>
+        <v>False</v>
       </c>
     </row>
     <row r="64" spans="1:27" x14ac:dyDescent="0.25">
@@ -4888,28 +4944,36 @@
         <v>284.36649999999997</v>
       </c>
       <c r="D64">
-        <v>113</v>
+        <f>G41</f>
+        <v>275.5</v>
       </c>
       <c r="E64">
-        <v>70.900000000000006</v>
+        <f>E41</f>
+        <v>74.8</v>
       </c>
       <c r="F64">
+        <f>I41</f>
         <v>0.63350000000002638</v>
       </c>
       <c r="G64">
+        <f>K41</f>
         <v>-29.5</v>
       </c>
       <c r="H64">
+        <f>J41</f>
         <v>-14.799999999999997</v>
       </c>
-      <c r="I64" t="s">
-        <v>38</v>
-      </c>
-      <c r="J64" t="s">
-        <v>39</v>
-      </c>
-      <c r="K64" t="s">
-        <v>39</v>
+      <c r="I64" t="str">
+        <f>L41</f>
+        <v>TRUE</v>
+      </c>
+      <c r="J64" t="str">
+        <f>M41</f>
+        <v>False</v>
+      </c>
+      <c r="K64" t="str">
+        <f>N41</f>
+        <v>False</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.25">
@@ -4923,28 +4987,36 @@
         <v>284.16649999999998</v>
       </c>
       <c r="D65">
-        <v>112.2</v>
+        <f>G45</f>
+        <v>274.5</v>
       </c>
       <c r="E65">
-        <v>69.900000000000006</v>
+        <f>E45</f>
+        <v>74.099999999999994</v>
       </c>
       <c r="F65">
+        <f>I45</f>
         <v>0.83350000000001501</v>
       </c>
       <c r="G65">
+        <f>K45</f>
         <v>-28.5</v>
       </c>
       <c r="H65">
+        <f>J45</f>
         <v>-14.099999999999994</v>
       </c>
-      <c r="I65" t="s">
-        <v>38</v>
-      </c>
-      <c r="J65" t="s">
-        <v>39</v>
-      </c>
-      <c r="K65" t="s">
-        <v>39</v>
+      <c r="I65" t="str">
+        <f t="shared" ref="I65:K66" si="59">L45</f>
+        <v>TRUE</v>
+      </c>
+      <c r="J65" t="str">
+        <f t="shared" si="59"/>
+        <v>False</v>
+      </c>
+      <c r="K65" t="str">
+        <f t="shared" si="59"/>
+        <v>False</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.25">
@@ -4958,28 +5030,36 @@
         <v>284.16649999999998</v>
       </c>
       <c r="D66">
-        <v>112.3</v>
+        <f>G46</f>
+        <v>275</v>
       </c>
       <c r="E66">
-        <v>69.900000000000006</v>
+        <f>E46</f>
+        <v>74.099999999999994</v>
       </c>
       <c r="F66">
+        <f>I46</f>
         <v>0.83350000000001501</v>
       </c>
       <c r="G66">
+        <f>K46</f>
         <v>-29</v>
       </c>
       <c r="H66">
+        <f>J46</f>
         <v>-14.099999999999994</v>
       </c>
-      <c r="I66" t="s">
-        <v>38</v>
-      </c>
-      <c r="J66" t="s">
-        <v>39</v>
-      </c>
-      <c r="K66" t="s">
-        <v>39</v>
+      <c r="I66" t="str">
+        <f t="shared" si="59"/>
+        <v>TRUE</v>
+      </c>
+      <c r="J66" t="str">
+        <f t="shared" si="59"/>
+        <v>False</v>
+      </c>
+      <c r="K66" t="str">
+        <f t="shared" si="59"/>
+        <v>False</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.25">
@@ -4990,28 +5070,36 @@
         <v>454.16650000000004</v>
       </c>
       <c r="D67">
-        <v>124.1</v>
+        <f>G53</f>
+        <v>199.5</v>
       </c>
       <c r="E67">
-        <v>66.3</v>
+        <f>E53</f>
+        <v>73.2</v>
       </c>
       <c r="F67">
+        <f>I53</f>
         <v>-4.1665000000000418</v>
       </c>
       <c r="G67">
+        <f>K53</f>
         <v>-26.5</v>
       </c>
       <c r="H67">
+        <f>J53</f>
         <v>-13.700000000000003</v>
       </c>
-      <c r="I67" t="s">
-        <v>38</v>
-      </c>
-      <c r="J67" t="s">
-        <v>39</v>
-      </c>
-      <c r="K67" t="s">
-        <v>39</v>
+      <c r="I67" t="str">
+        <f>L53</f>
+        <v>TRUE</v>
+      </c>
+      <c r="J67" t="str">
+        <f>M53</f>
+        <v>False</v>
+      </c>
+      <c r="K67" t="str">
+        <f>N53</f>
+        <v>False</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.25">
@@ -5022,28 +5110,36 @@
         <v>453.16650000000004</v>
       </c>
       <c r="D68">
-        <v>124</v>
+        <f>G54</f>
+        <v>199</v>
       </c>
       <c r="E68">
-        <v>67.099999999999994</v>
+        <f>E54</f>
+        <v>74.099999999999994</v>
       </c>
       <c r="F68">
+        <f t="shared" ref="F68:F69" si="60">I54</f>
         <v>-3.1665000000000418</v>
       </c>
       <c r="G68">
+        <f t="shared" ref="G68:G69" si="61">K54</f>
         <v>-26</v>
       </c>
       <c r="H68">
+        <f t="shared" ref="H68:H69" si="62">J54</f>
         <v>-14.599999999999994</v>
       </c>
-      <c r="I68" t="s">
-        <v>38</v>
-      </c>
-      <c r="J68" t="s">
-        <v>39</v>
-      </c>
-      <c r="K68" t="s">
-        <v>39</v>
+      <c r="I68" t="str">
+        <f t="shared" ref="I68:K68" si="63">L54</f>
+        <v>TRUE</v>
+      </c>
+      <c r="J68" t="str">
+        <f t="shared" si="63"/>
+        <v>False</v>
+      </c>
+      <c r="K68" t="str">
+        <f t="shared" si="63"/>
+        <v>False</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.25">
@@ -5054,28 +5150,36 @@
         <v>454.06650000000002</v>
       </c>
       <c r="D69">
-        <v>126</v>
+        <f>G55</f>
+        <v>199</v>
       </c>
       <c r="E69">
-        <v>67.2</v>
+        <f>E55</f>
+        <v>74</v>
       </c>
       <c r="F69">
+        <f t="shared" si="60"/>
         <v>-4.0665000000000191</v>
       </c>
       <c r="G69">
+        <f t="shared" si="61"/>
         <v>-26</v>
       </c>
       <c r="H69">
+        <f t="shared" si="62"/>
         <v>-14.5</v>
       </c>
-      <c r="I69" t="s">
-        <v>38</v>
-      </c>
-      <c r="J69" t="s">
-        <v>39</v>
-      </c>
-      <c r="K69" t="s">
-        <v>39</v>
+      <c r="I69" t="str">
+        <f t="shared" ref="I69:K69" si="64">L55</f>
+        <v>TRUE</v>
+      </c>
+      <c r="J69" t="str">
+        <f t="shared" si="64"/>
+        <v>False</v>
+      </c>
+      <c r="K69" t="str">
+        <f t="shared" si="64"/>
+        <v>False</v>
       </c>
     </row>
   </sheetData>
